--- a/verification_sample_v3.xlsx
+++ b/verification_sample_v3.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="validation_sample" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="known_issues" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="annotation_guide" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:AA51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,17 +483,87 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>single_tf_flag</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>pubmed_url</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>evidence_sentence</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>comment</t>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>recipe_valid</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>source_cell_valid</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>target_cell_valid</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>factors_valid</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>standalone_recipe</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>duplicate_status</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>preferred_pmid</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>error_category</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>corrected_source_cell</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>corrected_target_cell</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>corrected_factors</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>annotation_notes</t>
         </is>
       </c>
     </row>
@@ -501,32 +573,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26503743</t>
+          <t>34977272</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Generation of integration-free induced hepatocyte-like cells from mouse fibroblasts.</t>
+          <t>miRNA-mediated control of exogenous &lt;i&gt;OCT4&lt;/i&gt; during mesenchymal-epithelial transition increases measles vector reprogramming efficiency.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>mouse embryonic fibroblast (MEF)</t>
+          <t>human neonatal fibroblast (NHF) or adult human fibroblast (AHF)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>induced hepatocyte (iHep)</t>
+          <t>induced pluripotent stem cell (iPSC)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GATA4, HNF1A, FOXA3</t>
+          <t>OCT4, SOX2, KLF4, c-MYC</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>TF, TF, TF</t>
+          <t>TF, TF, TF, TF</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -546,11 +618,37 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>We next transfected the MEFs with three distinct combinations of TFs, Hnf4a/Foxa1 (4a1), Hnf4a/Foxa3 (4a3), and Gata4/Hnf1a/Foxa3 (GHF), which were previously shown to elicit the direct conversion of somatic fibroblasts into iHeps (Fig. 1A)9,10.</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/34977272</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>We have previously produced a single-cycle MeV expressing the four RFs, MV4FN, to produce iPSCs.</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>&lt;i&gt;OCT4&lt;/i&gt; is a key mediator of induced pluripotent stem cell (iPSC) reprogramming, but the mechanistic insights into the role of exogenous &lt;i&gt;OCT4&lt;/i&gt; and timelines that initiate pluripotency remain to be resolved. Here, using measles reprogramming vectors, we present microRNA (miRNA) targeting of exogenous &lt;i&gt;OCT4&lt;/i&gt; to shut down its expression during the mesenchymal to the epithelial transition phase of reprogramming. We showed that exogenous &lt;i&gt;OCT4&lt;/i&gt; is required only for the initiation of reprogramming and is dispensable for the maturation stage. However, the continuous expression of &lt;i&gt;SOX2&lt;/i&gt;, &lt;i&gt;KLF4&lt;/i&gt;, and &lt;i&gt;c-MYC&lt;/i&gt; is necessary for the maturation stage of the iPSC. Additionally, we demonstrate a novel application of miRNA targeting in a viral vector to contextually control the vector/transgene, ultimately leading to an improved reprogramming efficiency. This novel approach could be applied to other systems for improving the efficiency of vector-induced processes.</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -558,32 +656,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>26354680</t>
+          <t>38903080</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>High-efficiency reprogramming of fibroblasts into cardiomyocytes requires suppression of pro-fibrotic signalling.</t>
+          <t>Generation of hiPSC-derived brain microvascular endothelial cells using a combination of directed differentiation and transcriptional reprogramming strategies.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>mouse embryonic fibroblast (MEF)</t>
+          <t>induced pluripotent stem cell (iPSC)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>cardiomyocyte</t>
+          <t>brain microvascular endothelial cell (BMEC)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GATA4, HAND2, MEF2C, TBX5, A83-01</t>
+          <t>FOXF2, ZIC3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>TF, TF, TF, TF, small_molecule</t>
+          <t>TF, TF</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -598,16 +696,42 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fulltext</t>
+          <t>abstract</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Spontaneously beating cells in GHMT-MEFs treated with A83-01 by 3 weeks.</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/38903080</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Here, we report generation, transcriptomic and functional characterization of reprogrammed BMECs (rBMECs) by combining hiPSC differentiation into BBB-primed endothelial cells and reprogramming with two BBB transcription factors FOXF2 and ZIC3.</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>The blood-brain barrier (BBB), formed by specialized brain microvascular endothelial cells (BMECs), regulates brain function in health and disease. &lt;i&gt;In vitro&lt;/i&gt; modeling of the human BBB is limited by the lack of robust hiPSC protocols to generate BMECs. Here, we report generation, transcriptomic and functional characterization of reprogrammed BMECs (rBMECs) by combining hiPSC differentiation into BBB-primed endothelial cells and reprogramming with two BBB transcription factors FOXF2 and ZIC3. rBMECs express a subset of the BBB gene repertoire including tight junctions and transporters, exhibit stronger paracellular barrier properties, lower caveolar-mediated transcytosis, and similar p-Glycoprotein activity compared to primary HBMECs. They can acquire an inflammatory phenotype when treated with oligomeric Aβ42. rBMECs integrate with hiPSC-derived pericytes and astrocytes to form a 3D neurovascular system using the MIMETAS microfluidics platform. This novel 3D system resembles the &lt;i&gt;in vivo&lt;/i&gt; BBB at structural and functional levels to enable investigation of pathogenic mechanisms of neurological diseases.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -615,32 +739,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>41163067</t>
+          <t>28514439</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chemical direct conversion of human fibroblasts to mesenchymal stem cells that can alleviate inflammation in vivo.</t>
+          <t>Haematopoietic stem and progenitor cells from human pluripotent stem cells.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>human fibroblast</t>
+          <t>CD34+FLK1+CD235A−CD43− hemogenic endothelium derived from human pluripotent stem cells</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>mesenchymal stem cell</t>
+          <t>hematopoietic stem/progenitor cells with multi-lineage engraftment potential</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ALK5iII, KU-60019, Fasudil</t>
+          <t>RUNX1, LCOR, SPI1, ERG, HOXA5, HOXA9, HOXA10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>small_molecule, small_molecule, small_molecule</t>
+          <t>TF, TF, TF, TF, TF, TF, TF</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -660,11 +784,37 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Based on these findings, the HDFs/AKF were brought to further detailed analyses as representative chemical compounds-driven directly converted MSCs (cdMSCs).</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/28514439</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Conversion of haemogenic endothelium (HE) into haematopoietic stem/progenitor cells by seven transcription factors requires EHT.</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>A variety of tissue lineages can be differentiated from pluripotent stem cells by mimicking embryonic development through stepwise exposure to morphogens, or by conversion of one differentiated cell type into another by enforced expression of master transcription factors. Here, to yield functional human haematopoietic stem cells, we perform morphogen-directed differentiation of human pluripotent stem cells into haemogenic endothelium followed by screening of 26 candidate haematopoietic stem-cell-specifying transcription factors for their capacity to promote multi-lineage haematopoietic engraftment in mouse hosts. We recover seven transcription factors (ERG, HOXA5, HOXA9, HOXA10, LCOR, RUNX1 and SPI1) that are sufficient to convert haemogenic endothelium into haematopoietic stem and progenitor cells that engraft myeloid, B and T cells in primary and secondary mouse recipients. Our combined approach of morphogen-driven differentiation and transcription-factor-mediated cell fate conversion produces haematopoietic stem and progenitor cells from pluripotent stem cells and holds promise for modelling haematopoietic disease in humanized mice and for therapeutic strategies in genetic blood disorders.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -672,12 +822,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31019211</t>
+          <t>26418476</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>OVOL2 induces mesenchymal-to-epithelial transition in fibroblasts and enhances cell-state reprogramming towards epithelial lineages.</t>
+          <t>Brief Report: Inhibition of miR-145 Enhances Reprogramming of Human Dermal Fibroblasts to Induced Pluripotent Stem Cells.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -687,22 +837,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>keratinocyte-like cell</t>
+          <t>induced pluripotent stem cell (iPSC)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>OVOL2, HNF1A, TP63, KLF4</t>
+          <t>OCT4, KLF4, SOX2, c-MYC, miR-145 inhibitor</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>TF, TF, TF, TF</t>
+          <t>TF, TF, TF, TF, knockdown</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -712,16 +862,42 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>abstract</t>
+          <t>fulltext</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>In TP63/KLF4-induced keratinocyte-like cell-state reprogramming, OVOL2 greatly facilitated the activation of epithelial and keratinocyte-specific genes.</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/26418476</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>To assess how inhibition of miR‐145 affects iPSCs generation efficiency, we transiently transfected DFs with miR‐145 inhibitor at day 0. The next day cells were transduced with OKSM and 23 days later the efficiency of iPSCs generation was determined by counting of AP‐positive and TRA‐1‐60‐positive colonies.</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>MicroRNA (miRNAs) are short noncoding RNA molecules involved in many cellular processes and shown to play a key role in somatic cell induced reprogramming. We performed an array based screening to identify candidates that are differentially expressed between dermal skin fibroblasts (DFs) and induced pluripotent stem cells (iPSCs). We focused our investigations on miR-145 and showed that this candidate is highly expressed in DFs relative to iPSCs and significantly downregulated during reprogramming process. Inhibition of miR-145 in DFs led to the induction of "cellular plasticity" demonstrated by: (a) alteration of cell morphology associated with downregulation of mesenchymal and upregulation of epithelial markers; (b) upregulation of pluripotency-associated genes including SOX2, KLF4, C-MYC; (c) downregulation of miRNA let-7b known to inhibit reprogramming; and (iv) increased efficiency of reprogramming to iPSCs in the presence of reprogramming factors. Together, our results indicate a direct functional link between miR-145 and molecular pathways underlying reprogramming of somatic cells to iPSCs.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -729,32 +905,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>41237238</t>
+          <t>28223284</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Blocking nuclear receptor Nr4a3 unlocks the senescence barrier to promote direct cardiac reprogramming.</t>
+          <t>Mafa Enables Pdx1 to Effectively Convert Pancreatic Islet Progenitors and Committed Islet α-Cells Into β-Cells In Vivo.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>tail tip fibroblast</t>
+          <t>pancreatic islet Ngn3-positive progenitors</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>cardiomyocyte</t>
+          <t>β-cell</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MEF2C, GATA4, TBX5</t>
+          <t>Mafa, PDX1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>TF, TF, TF</t>
+          <t>TF, TF</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -769,16 +945,42 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fulltext</t>
+          <t>abstract</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Again, we found that both MGT and MGTH successfully induced iCMs in neonatal TTFs but rarely induced cTnT+ iCMs in adult and aged TTFs by flow cytometry and ICC.</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/28223284</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Here we have generated transgenic mice conditionally expressing the islet β-cell-enriched Mafa and/or Pdx1 transcription factors to examine their potential to transdifferentiate embryonic pan-islet cell Ngn3-positive progenitors and the later glucagon-positive α-cell population into β-cells.</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Among the therapeutic avenues being explored for replacement of the functional islet β-cell mass lost in type 1 diabetes (T1D), reprogramming of adult cell types into new β-cells has been actively pursued. Notably, mouse islet α-cells will transdifferentiate into β-cells under conditions of near β-cell loss, a condition similar to T1D. Moreover, human islet α-cells also appear to poised for reprogramming into insulin-positive cells. Here we have generated transgenic mice conditionally expressing the islet β-cell-enriched Mafa and/or Pdx1 transcription factors to examine their potential to transdifferentiate embryonic pan-islet cell Ngn3-positive progenitors and the later glucagon-positive α-cell population into β-cells. Mafa was found to both potentiate the ability of Pdx1 to induce β-cell formation from Ngn3-positive endocrine precursors and enable Pdx1 to produce β-cells from α-cells. These results provide valuable insight into the fundamental mechanisms influencing islet cell plasticity in vivo.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -786,37 +988,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24481283</t>
+          <t>29286621</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Small molecule cardiogenol C upregulates cardiac markers and induces cardiac functional properties in lineage-committed progenitor cells.</t>
+          <t>Quasi-Stem Cells Derived from Human Somatic Cells by Chemically Modified Carbon Nanotubes.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>skeletal myoblast</t>
+          <t>human fibroblast</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>cardiac-like cell</t>
+          <t>induced pluripotent stem cell (iPSC)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>cardiogenol C</t>
+          <t>OCT4, NANOG, SOX2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>small_molecule</t>
+          <t>TF, TF, TF</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -831,11 +1033,37 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Treatment with CgC up-regulated cardiac marker expression in skeletal myoblasts.</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/29286621</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>We obtained encouraging results showing that PLL-SWCNT treatment transformed fibroblast cells, and the transformed cells expressed the pluripotency-associated factors OCT4, NANOG, and SOX2 in addition to TRA-1-60 and SSEA-4, which are characteristic stem cell markers.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Surface modification of micro- and nanotopography was employed to alter the surface properties of scaffolds for controlling cell attachment, proliferation, and differentiation. This study reports a method for generating multinucleated colonies as evidenced by spherical colony formation through nanotopography-induced expression of reprogramming factors in human dermal fibroblasts. Colony formation was achieved by subjecting the cells to specific environments such as culturing with single-walled carbon nanotubes and poly-l-lysine (PLL-SWCNTs). We obtained encouraging results showing that PLL-SWCNT treatment transformed fibroblast cells, and the transformed cells expressed the pluripotency-associated factors OCT4, NANOG, and SOX2 in addition to TRA-1-60 and SSEA-4, which are characteristic stem cell markers. Downregulation of lamin A/C, HDAC1, HDAC6, Bcl2, cytochrome c, p-FAK, p-ERK, and p-JNK and upregulation of H3K4me3 and p-p38 were confirmed in the generated colonies, indicating reprogramming of cells. This protocol increases the possibility of successfully reprogramming somatic cells into induced pluripotent stem cells (iPSCs), thereby overcoming the difficulties in iPSC generation such as genetic mutations, carcinogenesis, and undetermined risk factors.</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -843,32 +1071,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>29768476</t>
+          <t>34331868</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Treatment with specific soluble factors promotes the functional maturation of transcription factor-mediated, pancreatic transdifferentiated cells.</t>
+          <t>Enhancer decommissioning imposes an epigenetic barrier to sensory hair cell regeneration.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>adult liver-derived progenitor cell</t>
+          <t>perinatal supporting cells</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>endocrine pancreatic cell (insulin-producing)</t>
+          <t>hair cell</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GLP-1 receptor agonist, Notch inhibitor, TGF-β inhibitor</t>
+          <t>Notch signaling blockade</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>small_molecule, small_molecule, small_molecule</t>
+          <t>other</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -888,11 +1116,37 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Treatment with an N2 supplement in combination with three soluble factors (glucagon-like peptide-1 [GLP-1] receptor agonist, notch inhibitor, and transforming growth factor-β [TGF-β] inhibitor) enhanced liver-to-pancreas transdifferentiation based on the following findings: i) the incidence of c-peptide-positive cells increased by approximately 1.2-fold after the aforementioned treatment; ii) the c-peptide expression level in the treated cells increased by approximately 12-fold as compared with the level in the untreated cells; iii) the treated cells secreted insulin in a glucose-dependent manner, whereas the untreated cells did not; and iv) transplantation of treated-transdifferentiated cells into streptozotocin-induced immunodeficient diabetic mice led to the amelioration of hyperglycemia.</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/34331868</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Blocking Notch signaling during the perinatal period of plasticity rapidly eliminates epigenetic silencing and allows supporting cells to transdifferentiate into hair cells.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Adult mammalian tissues such as heart, brain, retina, and the sensory structures of the inner ear do not effectively regenerate, although a latent capacity for regeneration exists at embryonic and perinatal times. We explored the epigenetic basis for this latent regenerative potential in the mouse inner ear and its rapid loss during maturation. In perinatal supporting cells, whose fate is maintained by Notch-mediated lateral inhibition, the hair cell enhancer network is epigenetically primed (H3K4me1) but silenced (active H3K27 de-acetylation and trimethylation). Blocking Notch signaling during the perinatal period of plasticity rapidly eliminates epigenetic silencing and allows supporting cells to transdifferentiate into hair cells. Importantly, H3K4me1 priming of the hair cell enhancers in supporting cells is removed during the first post-natal week, coinciding with the loss of transdifferentiation potential. We hypothesize that enhancer decommissioning during cochlear maturation contributes to the failure of hair cell regeneration in the mature organ of Corti.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -900,32 +1154,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>23821545</t>
+          <t>34209429</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Activation of aryl hydrocarbon receptor (ahr) by tranilast, an anti-allergy drug, promotes miR-302 expression and cell reprogramming.</t>
+          <t>Human Trisomic iPSCs from Down Syndrome Fibroblasts Manifest Mitochondrial Alterations Early during Neuronal Differentiation.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>somatic cell</t>
+          <t>iPSC (induced pluripotent stem cell)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>induced pluripotent stem cell (iPSC)</t>
+          <t>NPC (neural precursor cell)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>tranilast, miR-302</t>
+          <t>dual-SMAD inhibition</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>small_molecule, miRNA</t>
+          <t>other</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -940,16 +1194,42 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>abstract</t>
+          <t>fulltext</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>These results elucidate that miR-302 expression can be regulated by AhR and thus provide a strategy for promoting somatic cell reprogramming by AhR ligands.</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/34209429</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>The differentiation of euploid and isogenic trisomic iPSCs into neural precursor cells, Eu-NPCs and T21-NPCs respectively, was obtained by the dual-SMAD inhibition protocol [9] in monolayer cultures (see Matherial and Methods).</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>The presence of mitochondrial alterations in Down syndrome suggests that it might affect neuronal differentiation. We established a model of trisomic iPSCs, differentiating into neural precursor cells (NPCs) to monitor the occurrence of differentiation defects and mitochondrial dysfunction. Isogenic trisomic and euploid iPSCs were differentiated into NPCs in monolayer cultures using the dual-SMAD inhibition protocol. Expression of pluripotency and neural differentiation genes was assessed by qRT-PCR and immunofluorescence. Meta-analysis of expression data was performed on iPSCs. Mitochondrial Ca&lt;sup&gt;2+&lt;/sup&gt;, reactive oxygen species (ROS) and ATP production were investigated using fluorescent probes. Oxygen consumption rate (OCR) was determined by Seahorse Analyzer. NPCs at day 7 of induction uniformly expressed the differentiation markers PAX6, SOX2 and NESTIN but not the stemness marker OCT4. At day 21, trisomic NPCs expressed higher levels of typical glial differentiation genes. Expression profiles indicated that mitochondrial genes were dysregulated in trisomic iPSCs. Trisomic NPCs showed altered mitochondrial Ca&lt;sup&gt;2+&lt;/sup&gt;, reduced OCR and ATP synthesis, and elevated ROS production. Human trisomic iPSCs can be rapidly and efficiently differentiated into NPC monolayers. The trisomic NPCs obtained exhibit greater glial-like differentiation potential than their euploid counterparts and manifest mitochondrial dysfunction as early as day 7 of neuronal differentiation.</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -957,32 +1237,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>33182285</t>
+          <t>38133504</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Exosome-Mediated Differentiation of Mouse Embryonic Fibroblasts and Exocrine Cells into β-Like Cells and the Identification of Key miRNAs for Differentiation.</t>
+          <t>Retinal Ganglion Cell Fate Induction by Ngn-Family Transcription Factors.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>exocrine cell</t>
+          <t>late-stage retinal progenitor cell (RPC)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>β-like cell</t>
+          <t>retinal ganglion cell</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>exosomes, miR-127, miR-709</t>
+          <t>Ngn1, NGN2, NGN3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>other, miRNA, miRNA</t>
+          <t>TF, TF, TF</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1002,11 +1282,37 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>We also confirmed that exocrine cells can be differentiated into β-like cells by exosomes and the exosome-identified miRNAs.</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/38133504</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>In vivo, Ngn-TFs reprogrammed the differentiation-competent state of late-stage RPCs to generate RGCs.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Retinal ganglion cells (RGCs) are the projection neurons of the retina. Loss of RGCs is the cellular basis for vision loss in patients with glaucoma. Finding ways to regenerate RGCs will aid in the development of regenerative therapies for patients with glaucoma. The aim of this study was to examine the ability of Ngn-family transcription factors (TFs) to induce RGC regeneration through reprogramming in vitro and in vivo. In vitro, lentiviruses were used to deliver Ngn-TFs into mouse embryonic fibroblasts (MEFs). In vivo, mouse pup retina electroporation was used to deliver Ngn-TFs into late-stage retinal progenitor cells (RPCs). Immunofluorescence staining and RNA sequencing were used to examine cell fate reprogramming; patch-clamp recording was used to examine neuronal electrophysiologic functions. In vitro, all three Ngn-TFs, Ngn1, Ngn2, and Ngn3, were able to work alone to reprogram MEFs into RGC-like neurons that resembled RGCs at the transcriptome level, exhibited typical neuronal membrane electrophysiologic properties, and formed functional synaptic communications with retinal neurons. In vivo, Ngn-TFs reprogrammed the differentiation-competent state of late-stage RPCs to generate RGCs. Ngn-TFs are effective in inducing an RGC-like fate both in vitro and in vivo and might be explored further in the future for glaucoma translational applications.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1014,37 +1320,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>37856222</t>
+          <t>21445094</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Localized T3 production modifies the transcriptome and promotes the hepatocyte-like lineage in iPSC-derived hepatic organoids.</t>
+          <t>Rational optimization of reprogramming culture conditions for the generation of induced pluripotent stem cells with ultra-high efficiency and fast kinetics.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>somatic cell</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>induced pluripotent stem cell (iPSC)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>hepatic organoid (hepatocyte and cholangiocyte)</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BMP4, BMP7, FGF7, CHIR99021</t>
+          <t>OCT4, SOX2, KLF4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>cytokine, cytokine, cytokine, small_molecule</t>
+          <t>TF, TF, TF</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1054,16 +1360,42 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fulltext</t>
+          <t>abstract</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>On day 10, the 2D cultures were disrupted by dissociation, and subsequently, the cells self-reestablished into a 3D structure that grew progressively under stimulation of key reagents in the differentiation cocktails — i.e., BMP4, BMP7, FGF7, and the WNT agonist CHIR99021 — to promote the hepatic specification (Figure 1D) (17).</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/21445094</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>First, we developed an optimized defined medium, iCD1, which allows Oct4/Sox2/Klf4 (OSK)-mediated reprogramming to achieve ultra-high efficiency (~10% at day 8).</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>The ectopic expression of several transcription factors can restore embryonic cell fate to cultured somatic cells and generate induced pluripotent stem cells (iPSCs), revealing a previously unknown pathway to pluripotency. However, this technology is currently limited by low efficiency, slow kinetics and multi-factorial requirement. Here we show that reprogramming can be improved and dramatically accelerated by optimizing culture conditions. First, we developed an optimized defined medium, iCD1, which allows Oct4/Sox2/Klf4 (OSK)-mediated reprogramming to achieve ultra-high efficiency (~10% at day 8). We also found that this optimized condition renders both Sox2 and Klf4 dispensable, although the elimination of these two factors leads to lower efficiency and slower kinetics. Our studies define a shortened route, both in timing and factor requirement, toward pluripotency. This new paradigm not only provides a rationale to further improve iPSC generation but also simplifies the conceptual understanding of reprogramming by defined factors.</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1071,37 +1403,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>31980369</t>
+          <t>37315521</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Glycogen synthase kinase 3β inhibitor- CHIR 99021 augments the differentiation potential of mesenchymal stem cells.</t>
+          <t>MEF2C/p300-mediated epigenetic remodeling promotes the maturation of induced cardiomyocytes.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>mesenchymal stem cell (MSC)</t>
+          <t>fibroblast</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>neural cell</t>
+          <t>cardiomyocyte</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CHIR99021</t>
+          <t>MEF2C, GATA4, TBX5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>small_molecule</t>
+          <t>TF, TF, TF</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1116,11 +1448,37 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>CHIR 99021 treatment of MSCs resulted in enhanced transdifferentiation into neurological, hepatogenic and cardiomyocyte lineages with standardized protocols of differentiation.</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/37315521</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Cardiac transcription factors (TFs) directly reprogram fibroblasts into induced cardiomyocytes (iCMs), where MEF2C acts as a pioneer factor with GATA4 and TBX5 (GT).</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Cardiac transcription factors (TFs) directly reprogram fibroblasts into induced cardiomyocytes (iCMs), where MEF2C acts as a pioneer factor with GATA4 and TBX5 (GT). However, the generation of functional and mature iCMs is inefficient, and the molecular mechanisms underlying this process remain largely unknown. Here, we found that the overexpression of transcriptionally activated MEF2C via fusion of the powerful MYOD transactivation domain combined with GT increased the generation of beating iCMs by 30-fold. Activated MEF2C with GT generated iCMs that were transcriptionally, structurally, and functionally more mature than those generated by native MEF2C with GT. Mechanistically, activated MEF2C recruited p300 and multiple cardiogenic TFs to cardiac loci to induce chromatin remodeling. In contrast, p300 inhibition suppressed cardiac gene expression, inhibited iCM maturation, and decreased the beating iCM numbers. Splicing isoforms of MEF2C with similar transcriptional activities did not promote functional iCM generation. Thus, MEF2C/p300-mediated epigenetic remodeling promotes iCM maturation.</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1128,37 +1486,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>25345580</t>
+          <t>21390254</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PDX-1 mRNA-induced reprogramming of mouse pancreas-derived mesenchymal stem cells into insulin-producing cells in vitro.</t>
+          <t>Efficient feeder-free episomal reprogramming with small molecules.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>pancreas-derived mesenchymal stem cell (pMSC)</t>
+          <t>fibroblast</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>insulin-producing cell (IPC)</t>
+          <t>footprint-free human iPSC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PDX-1 mRNA</t>
+          <t>PD0325901, CHIR99021, A83-01, HA-100, human leukemia inhibitory factor</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>TF</t>
+          <t>small_molecule, small_molecule, small_molecule, small_molecule, cytokine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1173,11 +1531,37 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Our results demonstrated that mouse pMSCs can be transdifferentiated into effective glucose-responsive insulin-producing cells through transfecting synthetic modified PDX-1 mRNA in vitro.</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/21390254</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>These improvements enabled the routine derivation of footprint-free human iPSCs from skin fibroblasts, adipose tissue-derived cells and cord blood cells.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Genetic reprogramming of human somatic cells to induced pluripotent stem cells (iPSCs) could offer replenishable cell sources for transplantation therapies. To fulfill their promises, human iPSCs will ideally be free of exogenous DNA (footprint-free), and be derived and cultured in chemically defined media free of feeder cells. Currently, methods are available to enable efficient derivation of footprint-free human iPSCs. However, each of these methods has its limitations. We have previously derived footprint-free human iPSCs by employing episomal vectors for transgene delivery, but the process was inefficient and required feeder cells. Here, we have greatly improved the episomal reprogramming efficiency using a cocktail containing MEK inhibitor PD0325901, GSK3β inhibitor CHIR99021, TGF-β/Activin/Nodal receptor inhibitor A-83-01, ROCK inhibitor HA-100 and human leukemia inhibitory factor. Moreover, we have successfully established a feeder-free reprogramming condition using chemically defined medium with bFGF and N2B27 supplements and chemically defined human ESC medium mTeSR1 for the derivation of footprint-free human iPSCs. These improvements enabled the routine derivation of footprint-free human iPSCs from skin fibroblasts, adipose tissue-derived cells and cord blood cells. This technology will likely be valuable for the production of clinical-grade human iPSCs.</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1185,32 +1569,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>38243869</t>
+          <t>34206684</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LINC MIR503HG Controls SC-β Cell Differentiation and Insulin Production by Targeting CDH1 and HES1.</t>
+          <t>Inhibition of CREB-CBP Signaling Improves Fibroblast Plasticity for Direct Cardiac Reprogramming.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>stem cell-derived pancreatic progenitor (SC-PP)</t>
+          <t>mouse neonatal tail-tip fibroblast</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SC-β cell (stem cell-derived β cell)</t>
+          <t>cardiomyocyte</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MIR503HG knockdown</t>
+          <t>GATA4, MEF2C, TBX5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>knockdown</t>
+          <t>TF, TF, TF</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1225,16 +1609,42 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>abstract</t>
+          <t>fulltext</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>The comprehensive evaluation of functionality demonstrated that manipulating LINC MIR503HG using CRISPR in PP cell fate decision can improve insulin synthesis and secretion in mature SC-β cells, without effects on liver lineage specification.</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/34206684</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Although proper expression of reprogramming factors (e.g., GMT: Gata4, Mef2c, and Tbx5) in fibroblasts is essential to epigenetic reprogramming, the quality or status of fibroblasts prior to the induction of reprogramming is an important factor for successful and efficient reprogramming.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Direct cardiac reprogramming of fibroblasts into induced cardiomyocytes (iCMs) is a promising approach but remains a challenge in heart regeneration. Efforts have focused on improving the efficiency by understanding fundamental mechanisms. One major challenge is that the plasticity of cultured fibroblast varies batch to batch with unknown mechanisms. Here, we noticed a portion of in vitro cultured fibroblasts have been activated to differentiate into myofibroblasts, marked by the expression of αSMA, even in primary cell cultures. Both forskolin, which increases cAMP levels, and TGFβ inhibitor SB431542 can efficiently suppress myofibroblast differentiation of cultured fibroblasts. However, SB431542 improved but forskolin blocked iCM reprogramming of fibroblasts that were infected with retroviruses of Gata4, Mef2c, and Tbx5 (GMT). Moreover, inhibitors of cAMP downstream signaling pathways, PKA or CREB-CBP, significantly improved the efficiency of reprogramming. Consistently, inhibition of p38/MAPK, another upstream regulator of CREB-CBP, also improved reprogramming efficiency. We then investigated if inhibition of these signaling pathways in primary cultured fibroblasts could improve their plasticity for reprogramming and found that preconditioning of cultured fibroblasts with CREB-CBP inhibitor significantly improved the cellular plasticity of fibroblasts to be reprogrammed, yielding ~2-fold more iCMs than untreated control cells. In conclusion, suppression of CREB-CBP signaling improves fibroblast plasticity for direct cardiac reprogramming.</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1242,37 +1652,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21995449</t>
+          <t>41163067</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nuclear Ago2/HSP60 contributes to broad spectrum of hATSCs function via Oct4 regulation.</t>
+          <t>Chemical direct conversion of human fibroblasts to mesenchymal stem cells that can alleviate inflammation in vivo.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>human adipose tissue-derived stem cell</t>
+          <t>human fibroblast</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>induced neuron (iN)</t>
+          <t>mesenchymal stem cell</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ago2, HSP60</t>
+          <t>ALK5iII, KU-60019, Fasudil</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>other, other</t>
+          <t>small_molecule, small_molecule, small_molecule</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1282,16 +1692,42 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>abstract</t>
+          <t>fulltext</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Furthermore, HSP60-mediated regulation of Oct4 contributes to neuronal and endodermal β-cell differentiation of hATSCs in vitro and in vivo and downregulates mesoderm-specific gene expression.</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41163067</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Based on these findings, the HDFs/AKF were brought to further detailed analyses as representative chemical compounds-driven directly converted MSCs (cdMSCs).</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Mesenchymal stem cell (MSC) transplantation may significantly benefit patients with some inflammatory diseases. However, invasive procedures are required to collect autologous MSCs from patients, while in vitro expansion of MSCs may spoil their stemness. In this study, we aimed to induce MSC-like phenotypes in human dermal fibroblasts (HDFs). HDFs were cultured with some chemical compounds. The resultant cells were examined for their gene expression and multi-differentiation abilities in vitro. Anti-inflammatory functions in vivo were tested using two types of disease models in mice. Exosomes derived from the cells were also characterized. A combination of a TGF-β receptor inhibitor, a ROCK inhibitor, and an ATM inhibitor provoked HDFs to strongly express MSC markers. The chemical compound-driven directly converted MSCs (cdMSCs) had multilineage differentiation potentials to osteogenic, chondrogenic, and adipogenic lineages in vitro. The genes related to TGF-β, MAPK, Hedgehog and WNT signaling pathways were remarkably changed in expression levels, while CpG DNA methylation statuses were also altered, during the cell type transition. The cdMSCs ameliorated both acute and chronic inflammatory diseases after transplantation into murine models of LPS-induced lung injury and autoimmune arthritis. The cdMSCs secreted exosomes that promoted polarization of M0 macrophages to M2 phenotype while suppressing M1 macrophage induction in vitro. The three compounds successfully converted HDFs into MSC-like cells with high anti-inflammatory activities, which would be useful in regenerative medicine for inflammatory disease.</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1299,32 +1735,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>37060562</t>
+          <t>28771465</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>YTHDF1 phase separation triggers the fate transition of spermatogonial stem cells by activating the IκB-NF-κB-CCND1 axis.</t>
+          <t>EBV epigenetically suppresses the B cell-to-plasma cell differentiation pathway while establishing long-term latency.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>spermatogonial stem cell</t>
+          <t>mature human B cell</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>neural stem cell-like cells</t>
+          <t>lymphoblastoid cell line (LCL)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>YTHDF1</t>
+          <t>EBNA3A, EBNA3C</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>TF, TF</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1344,11 +1780,37 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Here, we show that liquid-liquid phase separation (LLPS) of YTH N&lt;sup&gt;6&lt;/sup&gt;-methyladenosine RNA binding protein 1 (YTHDF1), a pivotal m&lt;sup&gt;6&lt;/sup&gt;A "reader" protein, promotes the transdifferentiation of spermatogonial stem cells (SSCs) into neural stem cell-like cells by activating the IκB-nuclear factor κB (NF-κB)-CCND1 axis.</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/28771465</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Consistent with the binding of EBNA3A and/or EBNA3C leading to irreversible epigenetic changes, cells become committed to a B-blast fate &lt;12 days post-infection and are unable to de-repress p18INK4c or BLIMP-1-in either newly infected cells or conditional LCLs-by inactivating EBNA3A and EBNA3C.</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Mature human B cells infected by Epstein-Barr virus (EBV) become activated, grow, and proliferate. If the cells are infected ex vivo, they are transformed into continuously proliferating lymphoblastoid cell lines (LCLs) that carry EBV DNA as extra-chromosomal episomes, express 9 latency-associated EBV proteins, and phenotypically resemble antigen-activated B-blasts. In vivo similar B-blasts can differentiate to become memory B cells (MBC), in which EBV persistence is established. Three related latency-associated viral proteins EBNA3A, EBNA3B, and EBNA3C are transcription factors that regulate a multitude of cellular genes. EBNA3B is not necessary to establish LCLs, but EBNA3A and EBNA3C are required to sustain proliferation, in part, by repressing the expression of tumour suppressor genes. Here we show, using EBV-recombinants in which both EBNA3A and EBNA3C can be conditionally inactivated or using virus completely lacking the EBNA3 gene locus, that-after a phase of rapid proliferation-infected primary B cells express elevated levels of factors associated with plasma cell (PC) differentiation. These include the cyclin-dependent kinase inhibitor (CDKI) p18INK4c, the master transcriptional regulator of PC differentiation B lymphocyte-induced maturation protein-1 (BLIMP-1), and the cell surface antigens CD38 and CD138/Syndecan-1. Chromatin immunoprecipitation sequencing (ChIP-seq) and chromatin immunoprecipitation quantitative PCR (ChIP-qPCR) indicate that in LCLs inhibition of CDKN2C (p18INK4c) and PRDM1 (BLIMP-1) transcription results from direct binding of EBNA3A and EBNA3C to regulatory elements at these loci, producing stable reprogramming. Consistent with the binding of EBNA3A and/or EBNA3C leading to irreversible epigenetic changes, cells become committed to a B-blast fate &lt;12 days post-infection and are unable to de-repress p18INK4c or BLIMP-1-in either newly infected cells or conditional LCLs-by inactivating EBNA3A and EBNA3C. In vitro, about 20 days after infection with EBV lacking functional EBNA3A and EBNA3C, cells develop a PC-like phenotype. Together, these data suggest that EBNA3A and EBNA3C have evolved to prevent differentiation to PCs after infection by EBV, thus favouring long-term latency in MBC and asymptomatic persistence.</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1356,32 +1818,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>26418476</t>
+          <t>24753644</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brief Report: Inhibition of miR-145 Enhances Reprogramming of Human Dermal Fibroblasts to Induced Pluripotent Stem Cells.</t>
+          <t>Cardiomyocyte marker expression in mouse embryonic fibroblasts by cell-free cardiomyocyte extract and epigenetic manipulation.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>fibroblast</t>
+          <t>mouse embryonic fibroblast (MEF)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>induced pluripotent stem cell (iPSC)</t>
+          <t>cardiomyocyte</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>OCT4, KLF4, SOX2, c-MYC, miR-145 inhibitor</t>
+          <t>cardiomyocyte extract, 5-aza-dC, TSA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>TF, TF, TF, TF, knockdown</t>
+          <t>other, small_molecule, small_molecule</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1401,11 +1863,37 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>To assess how inhibition of miR‐145 affects iPSCs generation efficiency, we transiently transfected DFs with miR‐145 inhibitor at day 0. The next day cells were transduced with OKSM and 23 days later the efficiency of iPSCs generation was determined by counting of AP‐positive and TRA‐1‐60‐positive colonies.</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/24753644</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Immunofluorescence detected the existence of cardiomyocyte markers in the fibroblasts that were exposed to chromatin-modifying agents and permeabilized in the presence of the cardiac extract.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>The regenerative capacity of the mammalian heart is quite limited. Recent reports have focused on reprogramming mesenchymal stem cells into cardiomyocytes. We investigated whether fibroblasts could transdifferentiate into myocardium. Mouse embryonic fibroblasts were treated with Trichostatin A (TSA) and 5-Aza-2-Deoxycytidine (5-aza-dC). The treated cells were permeabilized with streptolysin O and exposed to the mouse cardiomyocyte extract and cultured for 1, 10, and 21 days. Cardiomyocyte markers were detected by immunohistochemistry. Alkaline phosphatase activity and OCT4 were also detected in cells treated by chromatin-modifying agents. The cells exposed to a combination of 5-aza-dC and TSA and permeabilized in the presence of the cardiomyocyte extract showed morphological changes. The cells were unable to express cardiomyocyte markers after 24 h. Immunocytochemical assays showed a notable degree of myosin heavy chain and α-actinin expressions after 10 days. The expression of the natriuretic factor and troponin T occurred after 21 days in these cells. The cells exposed to chromatin-modifying agents also expressed cardiomyocyte markers; however, the proportion of reprogrammed cells was clearly smaller than that in the cultures exposed to 5-aza-dC , TSA, and extract. It seems that the fibroblasts were able to eliminate the previous epigenetic markers and form new ones according to the factors existing in the extract. Since no beating was observed, at least up to 21 days, the cells may need an appropriate extracellular matrix for their function.</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1413,27 +1901,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>36717582</t>
+          <t>26503743</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B1 SINE-binding ZFP266 impedes mouse iPSC generation through suppression of chromatin opening mediated by reprogramming factors.</t>
+          <t>Generation of integration-free induced hepatocyte-like cells from mouse fibroblasts.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>mouse fibroblast</t>
+          <t>mouse embryonic fibroblast (MEF)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>induced pluripotent stem cell (iPSC)</t>
+          <t>induced hepatocyte (iHep)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>OCT4 (POU5F1), SOX2, KLF4</t>
+          <t>GATA4, HNF1A, FOXA3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1443,7 +1931,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1453,16 +1941,42 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>abstract</t>
+          <t>fulltext</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>We show that ZFP266 binds Short Interspersed Nuclear Elements (SINEs) adjacent to binding sites of pioneering factors, OCT4 (POU5F1), SOX2, and KLF4, and impedes chromatin opening.</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/26503743</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>We next transfected the MEFs with three distinct combinations of TFs, Hnf4a/Foxa1 (4a1), Hnf4a/Foxa3 (4a3), and Gata4/Hnf1a/Foxa3 (GHF), which were previously shown to elicit the direct conversion of somatic fibroblasts into iHeps (Fig. 1A)9,10.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>The ability to generate integration-free induced hepatocyte-like cells (iHeps) from somatic fibroblasts has the potential to advance their clinical application. Here, we have generated integration-free, functional, and expandable iHeps from mouse somatic fibroblasts. To elicit this direct conversion, we took advantage of an oriP/EBNA1-based episomal system to deliver a set of transcription factors, Gata4, Hnf1a, and Foxa3, to the fibroblasts. The established iHeps exhibit similar morphology, marker expression, and functional properties to primary hepatocytes. Furthermore, integration-free iHeps prolong the survival of fumarylacetoacetate-hydrolase-deficient (Fah(-/-)) mice after cell transplantation. Our study provides a novel concept for generating functional and expandable iHeps using a non-viral, non-integrating, plasmid-based system that could facilitate their pharmaceutical and biomedical application.</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1470,32 +1984,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>40531848</t>
+          <t>39689498</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nanopore-Based Electroporation Enables High-Efficiency, Rapid RNA-Mediated Reprogramming of Primary Fibroblasts into Human iPSCs.</t>
+          <t>Sox17 and Erg synergistically activate endothelial cell fate in reprogramming fibroblasts.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>human fibroblast</t>
+          <t>lung fibroblast</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>induced pluripotent stem cell (iPSC)</t>
+          <t>arterial-like induced-endothelial cell</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>OCT4, SOX2, KLF4, c-MYC, LIN28A, NANOG</t>
+          <t>Sox17, Erg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>TF, TF, TF, TF, TF, TF</t>
+          <t>TF, TF</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1515,11 +2029,37 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>We present a nanopore electroporation (NanoEP) system for efficient delivery of circular RNA (circRNA) encoding six reprogramming factors (OCT4, SOX2, KLF4, c-MYC, LIN28A, and NANOG) into human fibroblasts.</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/39689498</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Sox17-Erg direct reprogramming is a potent tool for the in vitro and in vivo generation of arterial-like induced-endothelial cells from fibroblasts.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Sox17-Erg direct reprogramming is a potent tool for the in vitro and in vivo generation of arterial-like induced-endothelial cells from fibroblasts. In this study, we illustrate the pioneering roles of both Sox17 and Erg in the endothelial cell reprogramming process and demonstrate that emergent gene expression only occurs when both factors are co-expressed. Bioinformatic analyses and molecular validation reveal both Bach2 and Etv4 as integral mediators of Sox17-Erg reprogramming with different roles in lung and heart fibroblast reprogramming. The generated organ-specific induced endothelial cells express molecular signatures similar to vasculature found in the starting cell's organ of origin and the starting chromatin architecture plays a role in the acquisition of this organ-specific identity. Overall, the Sox17-Erg reprogramming mechanism provides foundational knowledge for the future recapitulation of vascular heterogeneity through direct reprogramming.</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1527,32 +2067,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>41379378</t>
+          <t>35245086</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vav1 Sustains the Expression of Insulin, PDX1 and miR-375 During Differentiation of hiPSCs to β Cells: A Potential Target to Improve the In Vitro Generation of Insulin-Producing Cells.</t>
+          <t>Single-cell transcriptional profiling informs efficient reprogramming of human somatic cells to cross-presenting dendritic cells.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CD34-enriched blood cells</t>
+          <t>human embryonic fibroblast</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>induced pluripotent stem cell (iPSC)</t>
+          <t>induced type 1 conventional dendritic cell (hiDC1)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sendai virus</t>
+          <t>PU.1, IRF8, BATF3, IFN-γ, IFN-β, TNF-α</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>TF, TF, TF, cytokine, cytokine, cytokine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1567,16 +2107,42 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fulltext</t>
+          <t>abstract</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Human iPSC clones were generated by reprogramming CD34-enriched blood cells from healthy subjects using the Sendai virus technology (CytoTune-iPS Sendai Reprogramming Kit, Thermo Fisher Scientific, Waltham, MA, USA) [38, 39].</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/35245086</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Combining IFN-γ, IFN-β, and TNF-α with constitutive expression of cDC1-inducing transcription factors led to improvement of reprogramming efficiency by 190-fold.</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Type 1 conventional dendritic cells (cDC1s) are rare immune cells critical for the induction of antigen-specific cytotoxic CD8&lt;sup&gt;+&lt;/sup&gt; T cells, although the genetic program driving human cDC1 specification remains largely unexplored. We previously identified PU.1, IRF8, and BATF3 transcription factors as sufficient to induce cDC1 fate in mouse fibroblasts, but reprogramming of human somatic cells was limited by low efficiency. Here, we investigated single-cell transcriptional dynamics during human cDC1 reprogramming. Human induced cDC1s (hiDC1s) generated from embryonic fibroblasts gradually acquired a global cDC1 transcriptional profile and expressed antigen presentation signatures, whereas other DC subsets were not induced at the single-cell level during the reprogramming process. We extracted gene modules associated with successful reprogramming and identified inflammatory signaling and the cDC1-inducing transcription factor network as key drivers of the process. Combining IFN-γ, IFN-β, and TNF-α with constitutive expression of cDC1-inducing transcription factors led to improvement of reprogramming efficiency by 190-fold. hiDC1s engulfed dead cells, secreted inflammatory cytokines, and performed antigen cross-presentation, key cDC1 functions. This approach allowed efficient hiDC1 generation from adult fibroblasts and mesenchymal stromal cells. Mechanistically, PU.1 showed dominant and independent chromatin targeting at early phases of reprogramming, recruiting IRF8 and BATF3 to shared binding sites. The cooperative binding at open enhancers and promoters led to silencing of fibroblast genes and activation of a cDC1 program. These findings provide mechanistic insights into human cDC1 specification and reprogramming and represent a platform for generating patient-tailored cDC1s, a long-sought DC subset for vaccination strategies in cancer immunotherapy.</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1584,37 +2150,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>40913769</t>
+          <t>24672757</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chemogenetic tuning reveals optimal MAPK signaling for cell-fate programming.</t>
+          <t>Counteracting activities of OCT4 and KLF4 during reprogramming to pluripotency.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>mouse embryonic fibroblast (MEF)</t>
+          <t>murine somatic cells</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>motor neuron</t>
+          <t>induced pluripotent stem cell (iPSC)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NGN2, Isl1, Lhx3, p53DD, HRASG12V, RepSox</t>
+          <t>OCT4, KLF4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>TF, TF, TF, other, other, small_molecule</t>
+          <t>TF, TF</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1624,16 +2190,42 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fulltext</t>
+          <t>abstract</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>In this model system, the transduction of mouse embryonic fibroblasts with a single cassette of transcription factors (Ngn2, Isl1, and Lhx3 [NIL]) drives their conversion to motor neurons (Figure 1B).</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/24672757</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Differentiated cells can be reprogrammed into induced pluripotent stem cells (iPSCs) after overexpressing four transcription factors, of which Oct4 is essential.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Differentiated cells can be reprogrammed into induced pluripotent stem cells (iPSCs) after overexpressing four transcription factors, of which Oct4 is essential. To elucidate the role of Oct4 during reprogramming, we investigated the immediate transcriptional response to inducible Oct4 overexpression in various somatic murine cell types using microarray analysis. By downregulating somatic-specific genes, Oct4 induction influenced each transcriptional program in a unique manner. A significant upregulation of pluripotent markers could not be detected. Therefore, OCT4 facilitates reprogramming by interfering with the somatic transcriptional network rather than by directly initiating a pluripotent gene-expression program. Finally, Oct4 overexpression upregulated the gene Mgarp in all the analyzed cell types. Strikingly, Mgarp expression decreases during the first steps of reprogramming due to a KLF4-dependent inhibition. At later stages, OCT4 counteracts the repressive activity of KLF4, thereby enhancing Mgarp expression. We show that this temporal expression pattern is crucial for the efficient generation of iPSCs.</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1641,32 +2233,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>28186702</t>
+          <t>24672749</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Direct Conversion of Human Fibroblasts into Schwann Cells that Facilitate Regeneration of Injured Peripheral Nerve In Vivo.</t>
+          <t>Coordination of engineered factors with TET1/2 promotes early-stage epigenetic modification during somatic cell reprogramming.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>normal human fibroblast</t>
+          <t>mouse embryonic fibroblast (MEF)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Schwann cell</t>
+          <t>induced pluripotent stem cell (iPSC)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SOX10, Krox20</t>
+          <t>OCT4, SOX2, NANOG, KLF4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>TF, TF</t>
+          <t>TF, TF, TF, TF</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1681,16 +2273,42 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>abstract</t>
+          <t>fulltext</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Normal human fibroblasts were phenotypically converted into SCs by transducing SOX10 and Krox20 genes followed by culturing for 10 days resulting in approximately 43% directly converted Schwann cells (dSCs).</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/24672749</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>When wild-type OSNK were introduced into MEFs carrying the Oct4-GFP transgene, we obtained 69 ± 7 GFP-positive colonies from 2.5 × 10^4 transduced MEFs at day 16 (Figure 1D).</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Somatic cell reprogramming toward induced pluripotent stem cells (iPSCs) holds great promise in future regenerative medicine. However, the reprogramming process mediated by the traditional defined factors (OSMK) is slow and extremely inefficient. Here, we develop a combination of modified reprogramming factors (OySyNyK) in which the transactivation domain of the Yes-associated protein is fused to defined factors and establish a highly efficient and rapid reprogramming system. We show that the efficiency of OySyNyK-induced iPSCs is up to 100-fold higher than the OSNK and the reprogramming by OySyNyK is very rapid and is initiated in 24 hr. We find that OySyNyK factors significantly increase Tet1 expression at the early stage and interact with Tet1/2 to promote reprogramming. Our studies not only establish a rapid and highly efficient iPSC reprogramming system but also uncover a mechanism by which engineered factors coordinate with TETs to regulate 5hmC-mediated epigenetic control.</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1698,32 +2316,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>35791490</t>
+          <t>31849638</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MiR-106b-5p Regulates the Reprogramming of Spermatogonial Stem Cells into iPSC (Induced Pluripotent Stem Cell)-Like Cells.</t>
+          <t>Very Low Efficiency of Direct Reprogramming of Astrocytes Into Neurons in the Brains of Young and Aged Mice After Cerebral Ischemia.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>spermatogonial stem cell</t>
+          <t>proliferating astrocyte (neocortex)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>induced pluripotent stem cell (iPSC)</t>
+          <t>neuron (neuroblast and mature neuron)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>miR-106b-5p</t>
+          <t>NGN2, Bcl-2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>miRNA</t>
+          <t>TF, other</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1738,16 +2356,42 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>fulltext</t>
+          <t>abstract</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Interestingly, the induced SSC experimental groups showed similar properties to the iPS groups regarding the expression of OSKMN genes (Fig. 3).</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/31849638</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>To this end, we used a retroviral delivery system encoding the transcription factor &lt;i&gt;Ngn2&lt;/i&gt; alone or in combination with the antiapoptotic factor &lt;i&gt;Bcl-2&lt;/i&gt; to target proliferating astrocytes in the neocortex of young and aged mice after cerebral ischemia.</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>After cerebral ischemia, the ratio between astroglial cells and neurons in the neurovascular unit is disrupted in the perilesional area. We hypothesized that restoring the balance within the neurovascular unit may lead to an improved neurorestoration after focal ischemia. Recently, an innovative technology has been invented to efficiently convert proliferating astroglial cells into neurons in the injured young brain. However, the conversion efficacy of this technology has not been explored in the post-stroke brains of the aged rodents. To this end, we used a retroviral delivery system encoding the transcription factor &lt;i&gt;Ngn2&lt;/i&gt; alone or in combination with the antiapoptotic factor &lt;i&gt;Bcl-2&lt;/i&gt; to target proliferating astrocytes in the neocortex of young and aged mice after cerebral ischemia. Successful direct &lt;i&gt;in vivo&lt;/i&gt; reprogramming of reactive glia into neuroblasts and mature neurons was assessed by cellular phenotyping. We found that the conversion efficacy of proliferating astrocytes into neurons after cerebral ischemia in young and aged mice is disappointingly low, most likely because the therapeutic vectors carrying the conversion gene are engulfed by phagocytes shortly after intracortical administration. We conclude that other viral vectors and combinations of transcription factors should be employed to improve the efficacy of glia-to-neuron conversion after stroke in young and aged rodents.</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1755,37 +2399,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>33718351</t>
+          <t>34514853</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sall4 and Myocd Empower Direct Cardiac Reprogramming From Adult Cardiac Fibroblasts After Injury.</t>
+          <t>MUC1-C Contributes to the Maintenance of Human Embryonic Stem Cells and Promotes Somatic Cell Reprogramming.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>adult cardiac fibroblast (ACF)</t>
+          <t>fibroblast</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>cardiomyocyte-like cell (iCM)</t>
+          <t>induced pluripotent stem cell (iPSC)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GATA4, MEF2C, TBX5</t>
+          <t>MUC1-CD</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>TF, TF, TF</t>
+          <t>other</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1795,16 +2439,42 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fulltext</t>
+          <t>abstract</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>For NCFs and ACFs reprogramming, many mCherry+ cells were observed after a 3 week induction and some mCherry-negative cells also expressed cardiac troponin I (cTnI) and cardiac troponin T (cTnT) in the two kinds of fibroblasts (Figures 1B,C and Supplementary Figure 4).</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/34514853</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>In addition, forced overexpression of MUC1-CD increased the efficiency of reprogramming from fibroblast cells to induced pluripotent stem cells, suggesting that MUC1-C expression can contribute to the reprogramming process.</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Mucin 1 (MUC1) is a transmembrane glycoprotein overexpressed in several cancer cells in which it regulates cell surface properties, tumor invasion, and cell death. Recently, we reported that MUC1-C, the C-terminal subunit of MUC1, is involved in the growth of mouse embryonic stem (ES) cells. However, the functional significance of MUC1-C in human ES cells remains unclear. In this study, we investigated the expression and function of MUC1-C in human ES cells. Based on reverse transcription-polymerase chain reaction, western blotting, and confocal microscopy following immunostaining, undifferentiated human ES cells expressed MUC1-C and the expression level decreased during differentiation. Inhibition of MUC1-C, by the peptide inhibitor GO201 that targets the cytoplasmic domain of MUC1-C (MUC1-CD), reduced cell proliferation and OCT4 protein expression, and promoted cell death. Moreover, the inhibition of MUC1-C increased the intracellular reactive oxygen species (ROS) levels and downregulated expression of glycolysis-related enzymes. These findings indicate that expression and function of MUC1-C are required for stem cell properties involved in cell proliferation, maintenance of pluripotency and optimal ROS levels, and a high glycolytic flux in human ES cells. In addition, forced overexpression of MUC1-CD increased the efficiency of reprogramming from fibroblast cells to induced pluripotent stem cells, suggesting that MUC1-C expression can contribute to the reprogramming process.</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1812,32 +2482,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>31226809</t>
+          <t>35801179</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Enhanced Hepatogenic Differentiation of Human Wharton's Jelly-Derived Mesenchymal Stem Cells by Using Three-Step Protocol.</t>
+          <t>Foxa2 and Pet1 Direct and Indirect Synergy Drive Serotonergic Neuronal Differentiation.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>human Wharton's jelly-derived mesenchymal stem cells</t>
+          <t>mouse embryonic stem cell (mESC)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>hepatocyte</t>
+          <t>serotonergic neuron</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>sodium butyrate, EGF, bFGF</t>
+          <t>ASCL1, Lmx1b, FOXA2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>small_molecule, cytokine, cytokine</t>
+          <t>TF, TF, TF</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1852,16 +2522,42 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>abstract</t>
+          <t>fulltext</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>NaBu, at 1 mM, optimally promoted endodermal differentiation of hWJ-MSCs, along with epidermal growth factor (EGF) and basic fibroblast growth factor (bFGF) supplementation (EGF + bFGF + 1 mM NaBu).</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/35801179</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>The addition of Pet1 or Foxa2 to iAL (iALP and iALF, respectively) was sufficient to induce serotonergic staining and TPH expression.</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Neuronal programming by forced expression of transcription factors (TFs) holds promise for clinical applications of regenerative medicine. However, the mechanisms by which TFs coordinate their activities on the genome and control distinct neuronal fates remain obscure. Using direct neuronal programming of embryonic stem cells, we dissected the contribution of a series of TFs to specific neuronal regulatory programs. We deconstructed the Ascl1-Lmx1b-Foxa2-Pet1 TF combination that has been shown to generate serotonergic neurons and found that stepwise addition of TFs to Ascl1 canalizes the neuronal fate into a diffuse monoaminergic fate. The addition of pioneer factor Foxa2 represses Phox2b to induce serotonergic fate, similar to &lt;i&gt;in vivo&lt;/i&gt; regulatory networks. Foxa2 and Pet1 appear to act synergistically to upregulate serotonergic fate. Foxa2 and Pet1 co-bind to a small fraction of genomic regions but mostly bind to different regulatory sites. In contrast to the combinatorial binding activities of other programming TFs, Pet1 does not strictly follow the Foxa2 pioneer. These findings highlight the challenges in formulating generalizable rules for describing the behavior of TF combinations that program distinct neuronal subtypes.</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1869,37 +2565,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>31976351</t>
+          <t>34488017</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Highly efficient induced pluripotent stem cell reprogramming of cryopreserved lymphoblastoid cell lines.</t>
+          <t>E2A ablation enhances proportion of nodal-like cardiomyocytes in cardiac-specific differentiation of human embryonic stem cells.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>cryopreserved lymphoblastoid cell line (LCL)</t>
+          <t>human embryonic stem cell (hESC)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>induced pluripotent stem cell (iPSC)</t>
+          <t>nodal-like cardiomyocyte</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>OCT4, SOX2, KLF4, LMYC, LIN28, mp53DD</t>
+          <t>E2A knockout</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>TF, TF, TF, TF, TF, TF</t>
+          <t>knockdown</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1909,16 +2605,42 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fulltext</t>
+          <t>abstract</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>For iPSC reprogramming of cryopreserved LCLs, the LCLs are propagated and while still in logarithmic growth phase, nucleofected with episomal plasmids (pCEhOCT3/4, pCE-hSK, pCE-hUL, and pCE-mp53DD), encoding reprogramming factors (i.e., OCT3/4, SOX2, KLF4, LMYC, and LIN28), and a mouse p53 carboxy-terminal dominant-negative fragment using 4D-Nucleofector X Kit and 4D-Nucleofector system.</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/34488017</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>We found that knockout of the transcription factor E2A substantially increased the proportion of nodal-like cells in hESC-derived CMs.</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Human sinoatrial cardiomyocytes are essential building blocks for cell therapies of conduction system disorders. However, current differentiation protocols for deriving nodal cardiomyocytes from human pluripotent stem cells (hPSCs) are very inefficient. By employing the hPSCs to cardiomyocyte (CM) in vitro differentiation system and generating E2A-knockout hESCs using CRISPR/Cas9 gene editing technology, we analyze the functions of E2A in CM differentiation. We found that knockout of the transcription factor E2A substantially increased the proportion of nodal-like cells in hESC-derived CMs. The E2A ablated CMs displayed smaller cell size, increased beating rates, weaker contractile force, and other functional characteristics similar to sinoatrial node (SAN) cells. Transcriptomic analyses indicated that ion channel-encoding genes were up-regulated in E2A ablated CMs. E2A directly bounded to the promoters of genes key to SAN development via conserved E-box motif, and promoted their expression. Unexpect enhanced activity of NOTCH pathway after E2A ablation could also facilate to induct ventricle workingtype CMs reprogramming into SAN-like cells. Our study revealed a new role for E2A during directed cardiac differentiation of hESCs and may provide new clues for enhancing induction efficiency of SAN-like cardiomyocytes from hPSCs in the future. This work was supported by the NSFC (No.82070391, N.S.; No.81870175 and 81922006, P.L.), the National Key R&amp;D Program of China (2018YFC2000202, N.S.; 2017YFA0103700, P.L.), the Haiju program of National Children's Medical Center EK1125180102, and Innovative research team of high-level local universities in Shanghai and a key laboratory program of the Education Commission of Shanghai Municipality (ZDSYS14005).</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1926,37 +2648,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>22143343</t>
+          <t>30611717</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Suppression of NANOG induces efficient differentiation of human embryonic stem cells to pancreatic endoderm.</t>
+          <t>Reversion of in vivo fibrogenesis by novel chromone scaffolds.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>human embryonic stem cell (hESC)</t>
+          <t>myofibroblast (from mouse hepatic stellate cell line)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>pancreatic endoderm</t>
+          <t>intermediate HSC-like cell</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NANOG suppression (siRNA)</t>
+          <t>eupatilin</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>knockdown</t>
+          <t>small_molecule</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1966,16 +2688,42 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>abstract</t>
+          <t>fulltext</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>The suppression of NANOG displayed an effective differentiation toward endoderm and pancreatic progenitors.</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/30611717</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Eupatilin induced myofibroblasts to dedifferentiate into intermediate HCS-like cells.</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Myofibroblasts are known to play a key role in the development of idiopathic pulmonary fibrosis (IPF). Two drugs, pirfenidone and nintedanib, are the only approved therapeutic options for IPF, but their applications are limited due to their side effects. Thus, curative IPF drugs represent a huge unmet medical need. A mouse hepatic stellate cell (HSC) line was established that could robustly differentiate into myofibroblasts upon treatment with TGF-β. Eupatilin was assessed in diseased human lung fibroblasts from IPF patients (DHLFs) as well as in human lung epithelial cells (HLECs). The drug's performance was extensively tested in a bleomycin-induced lung fibrosis model (BLM). Global gene expression studies and proteome analysis were performed. Eupatilin attenuated disease severity of BLM in both preventative and therapeutic studies. The drug inhibited the in vitro transdifferantiation of DHLFs to myofibroblasts upon stimulation with TGF-β. No such induction of the in vitro transdifferantiation was observed in TGF-β treated HLECs. Specific carbons of eupatilin were essential for its anti-fibrotic activity. Eupatilin was capable of dismantling latent TGF-β complex, specifically by eliminating expression of the latent TGF-β binding protein 1 (LTBP1), in ECM upon actin depolymerization. Unlike eupatilin, pirfenidone was unable to block fibrosis of DHLFs or HSCs stimulated with TGF-β. Eupatilin attenuated phosphorylation of Smad3 by TGF-β. Eupatilin induced myofibroblasts to dedifferentiate into intermediate HCS-like cells. Eupatilin may act directly on pathogenic myofibroblasts, disarming them, whereas the anti-fibrotic effect of pirfenidone may be indirect. Eupatilin could increase the efficacy of IPF treatment to curative levels.</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1983,32 +2731,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>34028444</t>
+          <t>37992523</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>An Efficient Method for Directed Hepatocyte-Like Cell Induction from Human Embryonic Stem Cells.</t>
+          <t>Cardiac reprogramming reduces inflammatory macrophages and improves cardiac function in chronic myocardial infarction.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>human embryonic stem cell (hESC)</t>
+          <t>cardiac fibroblast</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>hepatocyte-like cell</t>
+          <t>cardiomyocyte</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Activin A, CHIR99021</t>
+          <t>MEF2C, GATA4, TBX5, HAND2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>cytokine, small_molecule</t>
+          <t>TF, TF, TF, TF</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2028,11 +2776,37 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>By our method, we regulate the key signaling pathways by continuously supplementing Activin A and CHIR99021 during hESC differentiation into definitive endoderm (DE), followed by generation of hepatic progenitor cells, and finally HLCs with typical hepatocyte morphology in a stagewise method with completely defined reagents.</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/37992523</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Cardiac reprogramming converts CFs into induced CMs, reduces fibrosis, and improves cardiac function in chronic MI through the overexpression of Mef2c/Gata4/Tbx5/Hand2 (MGTH).</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Cardiomyocytes (CMs) have little regenerative capacity. After myocardial infarction (MI), scar formation and myocardial remodeling proceed in the infarct and non-infarct areas, respectively, leading to heart failure (HF). Prolonged activation of cardiac fibroblasts (CFs) and inflammatory cells may contribute to this process; however, therapies targeting these cell types remain lacking. Cardiac reprogramming converts CFs into induced CMs, reduces fibrosis, and improves cardiac function in chronic MI through the overexpression of Mef2c/Gata4/Tbx5/Hand2 (MGTH). However, whether cardiac reprogramming reduces inflammation in infarcted hearts remains unclear. Moreover, the mechanism through which MGTH overexpression in CFs affects inflammatory cells remains unknown. Here, we showed that inflammation persists in the myocardium until three months after MI, which can be reversed with cardiac reprogramming. Single-cell RNA sequencing demonstrated that CFs expressed pro-inflammatory genes and exhibited strong intercellular communication with inflammatory cells, including macrophages, in chronic MI. Cardiac reprogramming suppressed the inflammatory profiles of CFs and reduced the relative ratios and pro-inflammatory signatures of cardiac macrophages. Moreover, fluorescence-activated cell sorting analysis (FACS) revealed that cardiac reprogramming reduced the number of chemokine receptor type 2 (CCR2)-positive inflammatory macrophages in the non-infarct areas in chronic MI, thereby restoring myocardial remodeling. Thus, cardiac reprogramming reduced the number of inflammatory macrophages to exacerbate cardiac function after MI.</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2040,32 +2814,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>24753644</t>
+          <t>33239022</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cardiomyocyte marker expression in mouse embryonic fibroblasts by cell-free cardiomyocyte extract and epigenetic manipulation.</t>
+          <t>Macrophage to myofibroblast transition contributes to subretinal fibrosis secondary to neovascular age-related macular degeneration.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>mouse embryonic fibroblast (MEF)</t>
+          <t>bone marrow-derived macrophage (BMDM) from C57BL/6J mice</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>cardiomyocyte</t>
+          <t>myofibroblast (α-SMA+ cell)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>cardiomyocyte extract, 5-aza-dC, TSA</t>
+          <t>TGF-β1, C3a</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>other, small_molecule, small_molecule</t>
+          <t>cytokine, cytokine</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2085,11 +2859,37 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Immunofluorescence detected the existence of cardiomyocyte markers in the fibroblasts that were exposed to chromatin-modifying agents and permeabilized in the presence of the cardiac extract.</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/33239022</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Together, these data suggest that TGF-β and complement C3a can induce MMT.</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Macular fibrosis causes irreparable vision loss in neovascular age-related macular degeneration (nAMD) even with anti-vascular endothelial growth factor (VEGF) therapy. Inflammation is known to play an important role in macular fibrosis although the underlying mechanism remains poorly defined. The aim of this study was to understand how infiltrating macrophages and complement proteins may contribute to macular fibrosis. Subretinal fibrosis was induced in C57BL/6J mice using the two-stage laser protocol developed by our group. The eyes were collected at 10, 20, 30 and 40 days after the second laser and processed for immunohistochemistry for infiltrating macrophages (F4/80 and Iba-1), complement components (C3a and C3aR) and fibrovascular lesions (collagen-1, Isolectin B4 and α-SMA). Human retinal sections with macular fibrosis were also used in the study. Bone marrow-derived macrophages (BMDMs) from C57BL/6J mice were treated with recombinant C3a, C5a or TGF-β for 48 and 96 h. qPCR, Western blot and immunohistochemistry were used to examine the expression of myofibroblast markers. The involvement of C3a-C3aR pathway in macrophage to myofibroblast transition (MMT) and subretinal fibrosis was further investigated using a C3aR antagonist (C3aRA) and a C3a blocking antibody in vitro and in vivo. Approximately 20~30% of F4/80&lt;sup&gt;+&lt;/sup&gt; (or Iba-1&lt;sup&gt;+&lt;/sup&gt;) infiltrating macrophages co-expressed α-SMA in subretinal fibrotic lesions both in human nAMD eyes and in the mouse model. TGF-β and C3a, but not C5a treatment, significantly upregulated expression of α-SMA, fibronectin and collagen-1 in BMDMs. C3a-induced upregulation of α-SMA, fibronectin and collagen-1 in BMDMs was prevented by C3aRA treatment. In the two-stage laser model of induced subretinal fibrosis, treatment with C3a blocking antibody but not C3aRA significantly reduced vascular leakage and Isolectin B4&lt;sup&gt;+&lt;/sup&gt; lesions. The treatment did not significantly alter collagen-1&lt;sup&gt;+&lt;/sup&gt; fibrotic lesions. MMT plays a role in macular fibrosis secondary to nAMD. MMT can be induced by TGF-β and C3a but not C5a. Further research is required to fully understand the role of MMT in macular fibrosis. Macrophage to myofibroblast transition (MMT) contributes to subretinal fibrosis. Subretinal fibrosis lesions contain various cell types, including macrophages and myofibroblasts, and are fibrovascular. Myofibroblasts are key cells driving pathogenic fibrosis, and they do so by producing excessive amount of extracellular matrix proteins. We have found that infiltrating macrophages can transdifferentiate into myofibroblasts, a phenomenon termed macrophage to myofibroblast transition (MMT) in macular fibrosis. In addition to TGF-β1, C3a generated during complement activation in CNV can also induce MMT contributing to macular fibrosis. RPE = retinal pigment epithelium. BM = Bruch's membrane. MMT = macrophage to myofibroblast transition. TGFB = transforming growth factor β. a-SMA = alpha smooth muscle actin. C3a = complement C3a.</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2097,23 +2897,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>40885192</t>
+          <t>41237238</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Anchored screening identifies transcription factor blueprints underlying dendritic cell diversity and subset-specific anti-tumor immunity.</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>Blocking nuclear receptor Nr4a3 unlocks the senescence barrier to promote direct cardiac reprogramming.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>tail tip fibroblast</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>pro-inflammatory cDC2B-like dendritic cell</t>
+          <t>cardiomyocyte</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PU.1, IRF4, PRDM1</t>
+          <t>MEF2C, GATA4, TBX5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2123,7 +2927,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2133,16 +2937,42 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>abstract</t>
+          <t>fulltext</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>We identified PU.1, IRF4, and PRDM1 as inducers of a pro-inflammatory cDC2B-like fate</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41237238</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Again, we found that both MGT and MGTH successfully induced iCMs in neonatal TTFs but rarely induced cTnT+ iCMs in adult and aged TTFs by flow cytometry and ICC.</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Direct reprogramming of fibroblasts into induced cardiomyocytes (iCMs) offers a regenerative strategy for heart repair, but efficiency declines in adult and aged cells. Transcriptomic and epigenetic profiling identified cellular senescence as a major barrier limiting cardiac fibroblast (CF) plasticity and cardiogenic conversion. Postneonatal fibroblasts exhibited impaired activation of cardiac gene programs and persistent expression of fibrotic and inflammatory signatures. A loss-of-function screen identified Nr4a3 as a central repressor. Nr4a3 overexpression promoted senescence and suppressed iCM induction, whereas knockdown enhanced reprogramming in murine and human senescent CFs. Mechanistically, Nr4a3 depletion remodeled the chromatin landscape from a fibrotic and inflammatory state to a regenerative cardiac program. Blocking downstream Cxcl14 restored reprogramming in refractory fibroblasts. In vivo, Nr4a3 knockdown improved heart function following myocardial infarction. These findings established cellular senescence as a major barrier to cardiac reprogramming and identified Nr4a3 and its effectors as potential targets to enhance heart regeneration.</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2150,32 +2980,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>33239022</t>
+          <t>41645083</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Macrophage to myofibroblast transition contributes to subretinal fibrosis secondary to neovascular age-related macular degeneration.</t>
+          <t>Conjoining cell reprogramming and mass spectrometry to identify the proteomic variations in the reprogrammed bladder cancer cells: finding cues of normalisation.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>bone marrow-derived macrophage (BMDM) from C57BL/6J mice</t>
+          <t>bladder cancer cell line HTB-5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>myofibroblast (α-SMA+ cell)</t>
+          <t>iPSC-like reprogrammed bladder cancer cells</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>TGF-β1, C3a</t>
+          <t>OCT4, SOX2, KLF4, c-MYC</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>cytokine, cytokine</t>
+          <t>TF, TF, TF, TF</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2190,16 +3020,42 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>fulltext</t>
+          <t>abstract</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Together, these data suggest that TGF-β and complement C3a can induce MMT.</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41645083</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Sendai virus-based reprogramming was utilised to reprogram the bladder cancer cell line HTB-5.</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Cancer cell reprogramming is a critical area of research that holds the power to transform malignancies into benign states while revealing key mechanisms of carcinogenesis. This study aimed to develop a more effective in vitro bladder cancer model using induced pluripotent stem cell technology and identify potential diagnostic and therapeutic biomarkers for bladder cancer. Sendai virus-based reprogramming was utilised to reprogram the bladder cancer cell line HTB-5. The reprogrammed cells were characterised by expressing pluripotency-associated markers, colony formation abilities, cell migration, and drug responses. LC-MS/MS reveals changes in protein composition among parental cancer cells, reprogrammed cancer cells, and normal uroepithelial cells. Reprogrammed bladder cancer cells display the expression of pluripotency-associated markers and demonstrate altered behaviours, including cell migration and responses to anticancer therapies. The genome-wide regulation by Sendai-virus delivery of Yamanaka factors resulted in distinctive protein expression patterns in reprogrammed bladder cancer cells, indicative of the pluripotency as well as spontaneous differentiation. A total of 297 dysregulated proteins in bladder cancer cells were normalised upon reprogramming. We proposed 25 potential biomarker candidates for diagnostic and therapeutic purposes, of which 12 candidates were demonstrated for the first time at the protein level. Differentially regulated proteins in parental bladder cancer cells and reprogrammed bladder cancer cells highlighted the critical protein-protein interactions that indicate the normalisation process of the parental bladder cancer cells. These cues could be used to pinpoint the candidate proteins to optimise the controlled partial/full reprogramming, to discover the therapeutic potential of reprogramming and to propose clinically relevant biomarker candidates. [Figure: see text] The online version contains supplementary material available at 10.1186/s12885-026-15634-x.</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2207,37 +3063,37 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>24572354</t>
+          <t>20663865</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mouse liver repopulation with hepatocytes generated from human fibroblasts.</t>
+          <t>The Necdin-Wnt pathway causes epigenetic peroxisome proliferator-activated receptor gamma repression in hepatic stellate cells.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>human fibroblast</t>
+          <t>activated hepatic stellate cell</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>hepatocyte</t>
+          <t>quiescent hepatic stellate cell</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>small molecules</t>
+          <t>necdin silencing (shRNA)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>small_molecule</t>
+          <t>knockdown</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2252,11 +3108,37 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Here, as a solution to this problem, we report the generation of human fibroblast-derived hepatocytes that can repopulate mouse livers.</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/20663865</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Silencing of necdin with adenovirally expressed shRNA, reverses activated HSCs to quiescent cells in a manner dependent on PPARγ and suppressed canonical Wnt signaling.</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Hepatic stellate cells (HSCs), vitamin A-storing liver pericytes, undergo myofibroblastic trans-differentiation or "activation" to participate in liver wound healing. This cellular process involves loss of regulation by adipogenic transcription factors such as peroxisome proliferator-activated receptor γ (PPARγ). Necdin, a melanoma antigen family protein, promotes neuronal and myogenic differentiation while inhibiting adipogenesis. The present study demonstrates that necdin is selectively expressed in HSCs among different liver cell types and induced during their activation in vitro and in vivo. Silencing of necdin with adenovirally expressed shRNA, reverses activated HSCs to quiescent cells in a manner dependent on PPARγ and suppressed canonical Wnt signaling. Promoter analysis, site-directed mutagenesis, and chromatin immunoprecipitation demonstrate that Wnt10b, a canonical Wnt induced in activated HSCs, is a direct target of necdin. Necdin silencing abrogates three epigenetic signatures implicated in repression of PPARγ: increased MeCP2 (methyl CpG binding protein 2) and HP-1α co-repressor recruitments to Pparγ promoter and enhanced H3K27 dimethylation at the exon 5 locus, again in a manner dependent on suppressed canonical Wnt. These epigenetic effects are reproduced by antagonism of canonical Wnt signaling with Dikkopf-1. Our results demonstrate a novel necdin-Wnt pathway, which serves to mediate antiadipogenic HSC trans-differentiation via epigenetic repression of PPARγ.</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2264,32 +3146,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>24672749</t>
+          <t>34171285</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Coordination of engineered factors with TET1/2 promotes early-stage epigenetic modification during somatic cell reprogramming.</t>
+          <t>Reprogramming astrocytes to motor neurons by activation of endogenous Ngn2 and Isl1.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>mouse embryonic fibroblast (MEF)</t>
+          <t>mouse spinal astrocyte</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>induced pluripotent stem cell (iPSC)</t>
+          <t>motor neuron</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>OCT4, SOX2, NANOG, KLF4</t>
+          <t>NGN2, Isl1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>TF, TF, TF, TF</t>
+          <t>TF, TF</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2304,16 +3186,42 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>fulltext</t>
+          <t>abstract</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>When wild-type OSNK were introduced into MEFs carrying the Oct4-GFP transgene, we obtained 69 ± 7 GFP-positive colonies from 2.5 × 10^4 transduced MEFs at day 16 (Figure 1D).</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/34171285</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Here, we showed that the activation of endogenous genes Ngn2 and Isl1 by CRISPRa enabled reprogramming of mouse spinal astrocytes and embryonic fibroblasts to motor neurons.</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Central nervous system injury and neurodegenerative diseases cause irreversible loss of neurons. Overexpression of exogenous specific transcription factors can reprogram somatic cells into functional neurons for regeneration and functional reconstruction. However, these practices are potentially problematic due to the integration of vectors into the host genome. Here, we showed that the activation of endogenous genes Ngn2 and Isl1 by CRISPRa enabled reprogramming of mouse spinal astrocytes and embryonic fibroblasts to motor neurons. These induced neurons showed motor neuronal morphology and exhibited electrophysiological activities. Furthermore, astrocytes in the spinal cord of the adult mouse can be converted into motor neurons by this approach with high efficiency. These results demonstrate that the activation of endogenous genes is sufficient to induce astrocytes into functional motor neurons in vitro and in vivo. This direct neuronal reprogramming approach may provide a novel potential therapeutic strategy for treating neurodegenerative diseases and spinal cord injury.</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2321,17 +3229,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>23144723</t>
+          <t>26354680</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cardiac gene activation analysis in mammalian non-myoblasic cells by Nkx2-5, Tbx5, Gata4 and Myocd.</t>
+          <t>High-efficiency reprogramming of fibroblasts into cardiomyocytes requires suppression of pro-fibrotic signalling.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>mouse 10T1/2 fibroblast</t>
+          <t>mouse embryonic fibroblast (MEF)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2341,12 +3249,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TBX5, GATA4, Myocd</t>
+          <t>GATA4, HAND2, MEF2C, TBX5, A83-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>TF, TF, TF</t>
+          <t>TF, TF, TF, TF, small_molecule</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2361,16 +3269,42 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>abstract</t>
+          <t>fulltext</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>By infecting 10T1/2 fibroblasts with Nkx2-5, Tbx5, Gata4 or Myocd cardiac transcription factor lentivirus alone or different combinations, we found that only Tbx5+Myocd and Tbx5+Gata4+Myocd combinations induced Myh6 and Tnnt2 cardiac marker protein expression.</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/26354680</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Spontaneously beating cells in GHMT-MEFs treated with A83-01 by 3 weeks.</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Direct reprogramming of fibroblasts into cardiomyocytes by forced expression of cardiomyogenic factors, GMT (GATA4, Mef2C, Tbx5) or GHMT (GATA4, Hand2, Mef2C, Tbx5), has recently been demonstrated, suggesting a novel therapeutic strategy for cardiac repair. However, current approaches are inefficient. Here we demonstrate that pro-fibrotic signalling potently antagonizes cardiac reprogramming. Remarkably, inhibition of pro-fibrotic signalling using small molecules that target the transforming growth factor-β or Rho-associated kinase pathways converts embryonic fibroblasts into functional cardiomyocyte-like cells, with the efficiency up to 60%. Conversely, overactivation of these pro-fibrotic signalling networks attenuates cardiac reprogramming. Furthermore, inhibition of pro-fibrotic signalling dramatically enhances the kinetics of cardiac reprogramming, with spontaneously contracting cardiomyocytes emerging in less than 2 weeks, as opposed to 4 weeks with GHMT alone. These findings provide new insights into the molecular mechanisms underlying cardiac conversion of fibroblasts and would enhance efforts to generate cardiomyocytes for clinical applications.</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2378,32 +3312,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>34206684</t>
+          <t>35791490</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Inhibition of CREB-CBP Signaling Improves Fibroblast Plasticity for Direct Cardiac Reprogramming.</t>
+          <t>MiR-106b-5p Regulates the Reprogramming of Spermatogonial Stem Cells into iPSC (Induced Pluripotent Stem Cell)-Like Cells.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>mouse neonatal tail-tip fibroblast</t>
+          <t>spermatogonial stem cell</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>cardiomyocyte</t>
+          <t>induced pluripotent stem cell (iPSC)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>GATA4, MEF2C, TBX5</t>
+          <t>miR-106b-5p</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>TF, TF, TF</t>
+          <t>miRNA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2423,11 +3357,37 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Although proper expression of reprogramming factors (e.g., GMT: Gata4, Mef2c, and Tbx5) in fibroblasts is essential to epigenetic reprogramming, the quality or status of fibroblasts prior to the induction of reprogramming is an important factor for successful and efficient reprogramming.</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/35791490</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Interestingly, the induced SSC experimental groups showed similar properties to the iPS groups regarding the expression of OSKMN genes (Fig. 3).</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Recent years have brought notable progress in raising the efficiency of the reprogramming technique so that approaches have evolved from known transgenic factors to only a few miRNAs. Nevertheless, there is a poor understanding of both the key factors and biological networks underlying this reprogramming. The present study aimed to investigate the potential of miR-106b-5p in regulating spermatogonial stem cells (SSCs) to induced pluripotent stem cell (iPSC)-like cells. We used SSCs because pluripotency is inducible in SSCs under defined culture conditions, and they have a few issues compared to other adult stem cells. As both signaling and post-transcriptional gene controls are critical for pluripotency regulation, we traced the expression of Oct-4, Sox-2, Klf-4, c-Myc, and Nanog (OSKMN). Besides, we considered miR-106b-5p targets using bioinformatic methods. Our results showed that transfected SSCs with miR-106b-5p increased the expression of the OSKMN factors, which was significantly more than negative control groups. Moreover, using the functional miRNA enrichment analysis, online tools, and databases, we predicted that miR-106b-5p targeted a signaling pathway gene named MAPK1/ERK2, related to regulating stem cell pluripotency. Together, our data suggest that miR-106b-5p regulates the reprogramming of SSCs into iPSC-like cells. Furthermore, noteworthy progress in the in vitro development of SSCs indicates promise reservoirs and opportunities for future clinical trials.</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2435,17 +3395,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>34977272</t>
+          <t>41379378</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>miRNA-mediated control of exogenous &lt;i&gt;OCT4&lt;/i&gt; during mesenchymal-epithelial transition increases measles vector reprogramming efficiency.</t>
+          <t>Vav1 Sustains the Expression of Insulin, PDX1 and miR-375 During Differentiation of hiPSCs to β Cells: A Potential Target to Improve the In Vitro Generation of Insulin-Producing Cells.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>human neonatal fibroblast (NHF) or adult human fibroblast (AHF)</t>
+          <t>CD34-enriched blood cells</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2455,12 +3415,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>OCT4, SOX2, KLF4, c-MYC</t>
+          <t>Sendai virus</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>TF, TF, TF, TF</t>
+          <t>other</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2480,11 +3440,37 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>We have previously produced a single-cycle MeV expressing the four RFs, MV4FN, to produce iPSCs.</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41379378</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Human iPSC clones were generated by reprogramming CD34-enriched blood cells from healthy subjects using the Sendai virus technology (CytoTune-iPS Sendai Reprogramming Kit, Thermo Fisher Scientific, Waltham, MA, USA) [38, 39].</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Human-induced pluripotent stem cells (hiPSCs) have emerged as a promising source of transplantable insulinproducing cells (IPCs) to restore insulin levels in Type 1 Diabetes (T1D) patients. Despite progress, obtaining fully functional β cells from hiPSCs remains challenging, underscoring the need to better understand the intracellular mechanisms involved. We investigated here the potential role of Vav1, a multidomain protein that we identified as crucial for the maturation of human biliary stem cells (hBTSCs) into β-like cells and in the trans-differentiation of pancreatic adenocarcinoma (PDAC) cells into IPCs; METHODS: Levels and subcellular localization of Vav1 were investigated throughout a seven-step differentiation process of hiPSCs to β cells. Vav1expression was forcedly modulated in pancreatic progenitors, and the potential effects were evaluated on insulin production and on PDX1, miR-375, and Akt, key regulators of β cells generation; RESULTS. Vav1 showed dynamic modulation, with pancreatic precursor cells requiring adequate levels of the protein to generate IPCs. Vav1 sustains the expression of PDX1, a primary regulator of insulin expression, and of its target miR-375, essential for determining β cell mass. Furthermore, Vav1 reduction correlated with increased activation of Akt, which regulates cell survival and insulin secretion in β cells and is down-regulated by miR- 375. Our findings suggest the existence of a Vav1/PDX1/miR-375/Akt axis as part of the complex network orchestrating the generation of functional β cells. These insights indicate that strategies aimed at specifically modulating Vav1 levels may positively impact the generation of IPCs in vitro and, ultimately, β cell replacement therapy for T1D.</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2492,32 +3478,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>28514439</t>
+          <t>40715046</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Haematopoietic stem and progenitor cells from human pluripotent stem cells.</t>
+          <t>Direct transdifferentiation of tumorigenic melanoma cells induces tumor cell reversion.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CD34+FLK1+CD235A−CD43− hemogenic endothelium derived from human pluripotent stem cells</t>
+          <t>human melanoma cells (BRAF-mutated and NRAS-mutated lines)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>hematopoietic stem/progenitor cells with multi-lineage engraftment potential</t>
+          <t>induced neuron (iN)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>RUNX1, LCOR, SPI1, ERG, HOXA5, HOXA9, HOXA10</t>
+          <t>ASCL1, BRN2, MYT1L, NEUROD1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>TF, TF, TF, TF, TF, TF, TF</t>
+          <t>TF, TF, TF, TF</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2537,11 +3523,37 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Conversion of haemogenic endothelium (HE) into haematopoietic stem/progenitor cells by seven transcription factors requires EHT.</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/40715046</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>In order to examine if melanoma cells can be transdifferentiated into neurons, the neuron-specific transcription factors ASCL1, BRN2, MYT1L, and NEUROD1 were ectopically overexpressed in different melanoma cell lines (Figs. 1B, C and S1A, B).</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Melanoma is an aggressive skin cancer and highly lethal at advanced stages due to its high tumorigenicity and metastatic capacity. Changing the phenotype of cancer cells from one lineage to another, a process called transdifferentiation, leads to tumor cell reversion, which goes along with a drastic reduction of their tumorigenicity. Via ectopic overexpression of four neuronal transcription factors, we transdifferentiated melanoma cells into neuron-like cells expressing neuronal markers and showing a neuron-like morphology. Moreover, the tumorigenic and metastatic potential of transdifferentiated cells in vitro and in vivo was significantly reduced. Transdifferentiated cells were also more sensitive to radiotherapy compared with their parental counterparts. We conclude that transdifferentiation of cancer cells into terminally differentiated neuron-like cells might represent a prospective new therapeutic approach for the treatment of melanoma.</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2549,12 +3561,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>25254342</t>
+          <t>30635054</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Generation of induced neuronal cells by the single reprogramming factor ASCL1.</t>
+          <t>The therapeutic potential of induced hepatocyte-like cells generated by direct reprogramming on hepatic fibrosis.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2564,22 +3576,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>induced neuronal cell (iN cell)</t>
+          <t>induced hepatocyte-like cells (iHeps)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ASCL1</t>
+          <t>HNF1A, small molecules</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>TF</t>
+          <t>TF, small_molecule</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2589,16 +3601,42 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>fulltext</t>
+          <t>abstract</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>These data show that the single factor ASCL1 alone is sufficient to convert MEFs into iN cells with intrinsic membrane properties of mature neurons when the cells are cultured in optimized conditions.</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/30635054</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>In this study, we generated iHEPs by direct reprogramming from mouse embryonic fibroblast (MEF) either using specific transcription factors such as c-Myc and Klf-4 (type A), or adding small molecules to HNF1α (type B).</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Until now, there is no effective anti-fibrotic therapy available for liver cirrhosis. Stem cell therapies have been studied for the treatment of hepatic fibrosis. However, the use of embryonic stem cells or induced pluripotent stem cells (iPSC) has limitations such as ethical concern or malignancy potential. Induced hepatocyte-like cells (iHEPs) generated by direct reprogramming technology may overcome these limitations. In this study, we generated iHEPs by direct reprogramming from mouse embryonic fibroblast (MEF) either using specific transcription factors such as c-Myc and Klf-4 (type A), or adding small molecules to HNF1α (type B). We investigated the effect of iHEPs on acute liver injury and chronic hepatic fibrosis animal models induced by CCl&lt;sub&gt;4&lt;/sub&gt; intra-peritoneal injection in BALB/C nude mice. In acute liver injury model, serum AST/ALT levels peaked at 24 h after CCl&lt;sub&gt;4&lt;/sub&gt; injection. Intra-splenic transplantation of iHEPs significantly attenuated CCl&lt;sub&gt;4&lt;/sub&gt;-induced acute liver injury. GFP-labeled iHEPs (type A) migrated to the liver after intra-splenic transplantation that was confirmed by Western blotting and immunofluorescence staining. We found that GFP and albumin were co-localized in migrated iHEPs in the liver suggesting migrated iHEPs were functional. In chronic hepatic fibrosis mice experiment, transplantation of either type A or type B iHEPs significantly attenuated liver fibrosis induced by CCl&lt;sub&gt;4&lt;/sub&gt; injection for 10 weeks. Our study suggests that iHEPs may be used as a novel therapeutic strategy for the treatment of hepatic fibrosis.</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2606,32 +3644,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>34051011</t>
+          <t>28587331</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Generation of combined hepatocellular-cholangiocarcinoma through transdifferentiation and dedifferentiation in p53-knockout mice.</t>
+          <t>Directly reprogramming fibroblasts into adipogenic, neurogenic and hepatogenic differentiation lineages by defined factors.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>hepatocyte</t>
+          <t>human fibroblast</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>combined hepatocellular-cholangiocarcinoma (cHCC-CCA)</t>
+          <t>neurocyte</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>HRAS, Trp53 disruption</t>
+          <t>SOX2, GATA-3, NEUROD1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>other, knockdown</t>
+          <t>TF, TF, TF</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2651,11 +3689,37 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>The HRAS-induced and HRAS/Myc-induced tumors in the wild-type mice demonstrated histological features of HCC, whereas the phenotype of the tumors generated in the p53-KO mice was consistent with cHCC-CCA.</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/28587331</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Similarly, direct reprogramming of the transcription factors sex determining region-box 2, trans-acting T-cell specific transcription factor (GATA-3) and neurogenic differentiation 1 in fibroblasts may induce neurogenic differentiation through hemagglutinating virus of Japan envelope (HVJ-E) transfection.</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>The reprogramming of adult cells into pluripotent cells or directly into alternative adult cell types represents a great potential technology for regenerative medicine. In the present study, the potential of key developmental adipogenic, neurogenic and hepatogenic regulators to reprogram human fibroblasts into adipocytes, neurocytes and hepatocytes was investigated. The results demonstrated that direct reprogramming of octamer-binding transcription factor 4 (Oct4) and CCAAT-enhancer-binding protein (C/EBP)β activated C/EBPα and peroxisome proliferator-activated receptor-γ expression, inducing the conversion of fibroblasts into adipocytes. Similarly, direct reprogramming of the transcription factors sex determining region-box 2, trans-acting T-cell specific transcription factor (GATA-3) and neurogenic differentiation 1 in fibroblasts may induce neurogenic differentiation through hemagglutinating virus of Japan envelope (HVJ-E) transfection. Moreover, hepatogenic differentiation was induced by combining the direct reprogramming of Oct4, GATA-3, hepatocyte nuclear factor 1 homeobox α and forkhead box protein A2 in fibroblasts. These results demonstrate that specific transcription factors and reprogramming factors are able to directly reprogram fibroblasts into adipogenic, neurogenic and hepatogenic differentiation lineages by HVJ-E transfection.</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2663,37 +3727,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>38891096</t>
+          <t>28853082</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Oncogenic Role of SATB2 In Vitro: Regulator of Pluripotency, Self-Renewal, and Epithelial-Mesenchymal Transition in Prostate Cancer.</t>
+          <t>Reprogramming of Human Retinal Pigment Epithelial Cells under the Effect of bFGF In Vitro.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>human normal prostate epithelial cells (PrECs)</t>
+          <t>human retinal pigment epithelial cells (ARPE-19)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>prostate cancer stem cell-like cells</t>
+          <t>neuronal-like cell</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SATB2</t>
+          <t>bFGF</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>TF</t>
+          <t>cytokine</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2708,11 +3772,37 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>In this study, we examined the oncogenic role of SATB2 in prostate cancer and assessed whether overexpression of SATB2 in human normal prostate epithelial cells (PrECs) induces properties of cancer stem cells (CSCs).</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/28853082</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Immunocytochemical analysis showed that in the presence of bFGF, some cells retained epithelial properties and showed positive staining for connexin-43, while others had long axon-like processes and demonstrated positive staining for βIII-tubulin, which attests to their neuronal transdifferentiation.</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>We studied the effect of bFGF on human retinal pigment epithelial cells in vitro In ARPE-19 cells, enhanced expression of KLF4 mRNA and reduced expression of PAX6, MITF, and OTX2 mRNA specific for retinal pigment epithelium were observed after bFGF application. The expression of KLF4 mRNA peaked in 72 h after bFGF application and then sharply decreased, which was accompanied by a 3-fold increase in TUBB3 mRNA expression (neuronal marker). Immunocytochemical analysis showed that in the presence of bFGF, some cells retained epithelial properties and showed positive staining for connexin-43, while others had long axon-like processes and demonstrated positive staining for βIII-tubulin, which attests to their neuronal transdifferentiation. Despite the prevalence of the epithelial properties, ARPE-19 cells under the influence of bFGF can show proneuronal properties.</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2720,37 +3810,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>33882394</t>
+          <t>39104117</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Generation of an induced pluripotent stem cell line SDQLCHi026-A from a hereditary tyrosinemia type I patient carrying compound heterozygote mutations in FAH gene.</t>
+          <t>Characteristic changes in astrocyte properties during astrocyte-to-neuron conversion induced by NeuroD1/Ascl1/Dlx2.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>patient somatic cell</t>
+          <t>cortical astrocyte (reactive)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>induced pluripotent stem cell (iPSC)</t>
+          <t>neuron</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>OCT4, SOX2, KLF4, BCL-XL, MYC</t>
+          <t>NEUROD1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>TF, TF, TF, TF, TF</t>
+          <t>TF</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2760,16 +3850,42 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>abstract</t>
+          <t>fulltext</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Induced pluripotent stem cells (iPSCs) were developed using non-integrating episomal vectors containing OCT4, SOX2, KLF4, BCL-XL and MYC.</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/39104117</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Similar changes in cell identity occurred from 3 dpi to 60 dpi in cells infected with viruses expressing NeuroD1 (Figure 1I) or Dlx2 (Figure 1J).</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>JOURNAL/nrgr/04.03/01300535-202506000-00030/figure1/v/2024-08-05T133530Z/r/image-tiff Direct in vivo conversion of astrocytes into functional new neurons induced by neural transcription factors has been recognized as a potential new therapeutic intervention for neural injury and degenerative disorders. However, a few recent studies have claimed that neural transcription factors cannot convert astrocytes into neurons, attributing the converted neurons to pre-existing neurons mis-expressing transgenes. In this study, we overexpressed three distinct neural transcription factors--NeuroD1, Ascl1, and Dlx2--in reactive astrocytes in mouse cortices subjected to stab injury, resulting in a series of significant changes in astrocyte properties. Initially, the three neural transcription factors were exclusively expressed in the nuclei of astrocytes. Over time, however, these astrocytes gradually adopted neuronal morphology, and the neural transcription factors was gradually observed in the nuclei of neuron-like cells instead of astrocytes. Furthermore, we noted that transcription factor-infected astrocytes showed a progressive decrease in the expression of astrocytic markers AQP4 (astrocyte endfeet signal), CX43 (gap junction signal), and S100β. Importantly, none of these changes could be attributed to transgene leakage into pre-existing neurons. Therefore, our findings suggest that neural transcription factors such as NeuroD1, Ascl1, and Dlx2 can effectively convert reactive astrocytes into neurons in the adult mammalian brain.</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2777,32 +3893,32 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>35801179</t>
+          <t>29038558</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Foxa2 and Pet1 Direct and Indirect Synergy Drive Serotonergic Neuronal Differentiation.</t>
+          <t>Prokineticin receptor-1-dependent paracrine and autocrine pathways control cardiac tcf21&lt;sup&gt;+&lt;/sup&gt; fibroblast progenitor cell transformation into adipocytes and vascular cells.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>mouse embryonic stem cell (mESC)</t>
+          <t>tcf21+ cardiac fibroblast progenitor cell</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>serotonergic neuron</t>
+          <t>vasculogenic cell</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ASCL1, Lmx1b, FOXA2</t>
+          <t>prokineticin-2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>TF, TF, TF</t>
+          <t>cytokine</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2817,16 +3933,42 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>fulltext</t>
+          <t>abstract</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>The addition of Pet1 or Foxa2 to iAL (iALP and iALF, respectively) was sufficient to induce serotonergic staining and TPH expression.</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/29038558</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>We found that prokineticin-2 is a cardiomyocyte secretome that controls CFP transformation into adipocytes and vasculogenic cells in vivo and in vitro.</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Cardiac fat tissue volume and vascular dysfunction are strongly associated, accounting for overall body mass. Despite its pathophysiological significance, the origin and autocrine/paracrine pathways that regulate cardiac fat tissue and vascular network formation are unclear. We hypothesize that adipocytes and vasculogenic cells in adult mice hearts may share a common cardiac cells that could transform into adipocytes or vascular lineages, depending on the paracrine and autocrine stimuli. In this study utilizing transgenic mice overexpressing prokineticin receptor (PKR1) in cardiomyocytes, and tcf21ERT-cre&lt;sup&gt;TM&lt;/sup&gt;-derived cardiac fibroblast progenitor (CFP)-specific PKR1 knockout mice (PKR1 &lt;sup&gt;tcf-/-&lt;/sup&gt;), as well as FACS-isolated CFPs, we showed that adipogenesis and vasculogenesis share a common CFPs originating from the tcf21&lt;sup&gt;+&lt;/sup&gt; epithelial lineage. We found that prokineticin-2 is a cardiomyocyte secretome that controls CFP transformation into adipocytes and vasculogenic cells in vivo and in vitro. Upon HFD exposure, PKR1 &lt;sup&gt;tcf-/-&lt;/sup&gt; mice displayed excessive fat deposition in the atrioventricular groove, perivascular area, and pericardium, which was accompanied by an impaired vascular network and cardiac dysfunction. This study contributes to the cardio-obesity field by demonstrating that PKR1 via autocrine/paracrine pathways controls CFP-vasculogenic- and CFP-adipocyte-transformation in adult heart. Our study may open up new possibilities for the treatment of metabolic cardiac diseases and atherosclerosis.</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2834,32 +3976,32 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>27874233</t>
+          <t>20675585</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Induction of hepatocyte-like cells from human umbilical cord-derived mesenchymal stem cells by defined microRNAs.</t>
+          <t>Efficient reprogramming of adult neural stem cells to monocytes by ectopic expression of a single gene.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>mesenchymal stem cell (MSC)</t>
+          <t>adult neural stem cells</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>hepatocyte-like cell</t>
+          <t>monocyte</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>miR-122, miR-1246, miR-1290, miR-148a, miR-424, miR-542-5p</t>
+          <t>PU.1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>miRNA</t>
+          <t>TF</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2874,16 +4016,42 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>fulltext</t>
+          <t>abstract</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>These results demonstrated that 6mix‐without‐miR‐30a set successfully induced hepatic differentiation of hMSCs, which demonstrated miR‐30a was dispensable for the induction of HLCs.</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/20675585</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>We report that adult neural stem cells can be reprogrammed at very high efficiency to monocytes, a differentiated fate of an unrelated somatic lineage, by ectopic expression of the Ets transcription factor PU.1.</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Neural stem cells have a broad differentiation repertoire during embryonic development and can be reprogrammed to pluripotency comparatively easily. We report that adult neural stem cells can be reprogrammed at very high efficiency to monocytes, a differentiated fate of an unrelated somatic lineage, by ectopic expression of the Ets transcription factor PU.1. The reprogrammed cells display a marker profile and functional characteristics of monocytes and integrate into tissues after transplantation. The failure to reprogram lineage-committed neural cells to monocytes with PU.1 suggests that neural stem cells are uniquely amenable to reprogramming.</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2891,32 +4059,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>41421413</t>
+          <t>31976351</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Therapeutic potential of microRNA let-7a-enriched exosomes in modulating macrophage plasticity (M1) and inhibiting malignant tendencies in breast cancer.</t>
+          <t>Highly efficient induced pluripotent stem cell reprogramming of cryopreserved lymphoblastoid cell lines.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>M2 macrophage</t>
+          <t>cryopreserved lymphoblastoid cell line (LCL)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>M1 macrophage</t>
+          <t>induced pluripotent stem cell (iPSC)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>let-7a</t>
+          <t>OCT4, SOX2, KLF4, LMYC, LIN28, mp53DD</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>miRNA</t>
+          <t>TF, TF, TF, TF, TF, TF</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2931,16 +4099,42 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>abstract</t>
+          <t>fulltext</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Peritoneal macrophages from Balb/c mice were extracted, polarized into the immunosuppressive M2 phenotype, and subsequently treated with let-7a -enriched exosomes (TEX + let-7a), leading to their repolarization into M1 macrophages.</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/31976351</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>For iPSC reprogramming of cryopreserved LCLs, the LCLs are propagated and while still in logarithmic growth phase, nucleofected with episomal plasmids (pCEhOCT3/4, pCE-hSK, pCE-hUL, and pCE-mp53DD), encoding reprogramming factors (i.e., OCT3/4, SOX2, KLF4, LMYC, and LIN28), and a mouse p53 carboxy-terminal dominant-negative fragment using 4D-Nucleofector X Kit and 4D-Nucleofector system.</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Tissue culture based &lt;i&gt;in-vitro&lt;/i&gt; experimental modeling of human inherited disorders provides insight into the cellular and molecular mechanisms involved and the underlying genetic component influencing the disease phenotype. The breakthrough development of induced pluripotent stem cell (iPSC) technology represents a quantum leap in experimental modeling of human diseases, providing investigators with a self-renewing and thus unlimited source of pluripotent cells for targeted differentiation into functionally relevant disease specific tissue/cell types. The existing rich bio-resource of Epstein-Barr virus (EBV) immortalized lymphoblastoid cell line (LCL) repositories generated from a wide array of patients in genetic and epidemiological studies worldwide, many of them with extensive genotypic, genomic and phenotypic data already existing, provides a great opportunity to reprogram iPSCs from any of these LCL donors in the context of their own genetic identity for disease modeling and disease gene identification. However, due to the low reprogramming efficiency and poor success rate of LCL to iPSC reprogramming, these LCL resources remain severely underused for this purpose. Here, we detailed step-by-step instructions to perform our highly efficient LCL-to-iPSC reprogramming protocol using EBNA1/OriP episomal plasmids encoding pluripotency transcription factors (&lt;i&gt;i.e.&lt;/i&gt;, OCT3/4, SOX2, KLF4, L-MYC, and LIN28), mouse p53DD (p53 carboxy-terminal dominant-negative fragment) and commercially available reprogramming media. We achieved a consistently high reprogramming efficiency and 100% success rate (&gt; 200 reprogrammed iPSC lines) using this protocol.</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2948,32 +4142,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>32346096</t>
+          <t>33718351</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bmi1 inhibitor PTC-209 promotes Chemically-induced Direct Cardiac Reprogramming of cardiac fibroblasts into cardiomyocytes.</t>
+          <t>Sall4 and Myocd Empower Direct Cardiac Reprogramming From Adult Cardiac Fibroblasts After Injury.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>cardiac fibroblast</t>
+          <t>adult cardiac fibroblast (ACF)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>induced-cardiomyocyte</t>
+          <t>cardiomyocyte-like cell (iCM)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>PTC-209</t>
+          <t>GATA4, MEF2C, TBX5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>small_molecule</t>
+          <t>TF, TF, TF</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2988,16 +4182,42 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>abstract</t>
+          <t>fulltext</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>To this aim, here we show that pre-treatment with the Bmi1 inhibitor PTC-209 is sufficient to increase the efficiency of Chemical-induced Direct Cardiac Reprogramming both in mouse embryonic fibroblasts and adult cardiac fibroblasts.</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/33718351</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>For NCFs and ACFs reprogramming, many mCherry+ cells were observed after a 3 week induction and some mCherry-negative cells also expressed cardiac troponin I (cTnI) and cardiac troponin T (cTnT) in the two kinds of fibroblasts (Figures 1B,C and Supplementary Figure 4).</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Direct conversion of fibroblasts into induced cardiomyocytes (iCMs) holds promising potential to generate functional cardiomyocytes for drug development and clinical applications, especially for direct &lt;i&gt;in situ&lt;/i&gt; heart regeneration by delivery of reprogramming genes into adult cardiac fibroblasts in injured hearts. For a decade, many cocktails of transcription factors have been developed to generate iCMs from fibroblasts of different tissues &lt;i&gt;in vitro&lt;/i&gt; and some were applied &lt;i&gt;in vivo&lt;/i&gt;. Here, we aimed to develop genetic cocktails that induce cardiac reprogramming directly in cultured cardiac fibroblasts isolated from adult mice with myocardial infarction (MICFs), which could be more relevant to heart diseases. We found that the widely used genetic cocktail, Gata4, Mef2c, and Tbx5 (GMT) were inefficient in reprogramming cardiomyocytes from MICFs. In a whole well of a 12-well plate, less than 10 mCherry&lt;sup&gt;+&lt;/sup&gt; cells (&lt;0.1%) were observed after 2 weeks of GMT infection with &lt;i&gt;Myh6&lt;/i&gt;-reporter transgenic MICFs. By screening 22 candidate transcription factors predicted through analyzing the gene regulatory network of cardiac development, we found that five factors, GMTMS (GMT plus Myocd and Sall4), induced more iCMs expressing the cardiac structural proteins cTnT and cTnI at a frequency of about 22.5 ± 2.7% of the transduced MICFs at day 21 post infection. What is more, GMTMS induced abundant beating cardiomyocytes at day 28 post infection. Specifically, Myocd contributed mainly to inducing the expression of cardiac proteins, while Sall4 accounted for the induction of functional properties, such as contractility. RNA-seq analysis of the iCMs at day 28 post infection revealed that they were reprogrammed to adopt a cardiomyocyte-like gene expression profile. Overall, we show here that Sall4 and Myocd play important roles in cardiac reprogramming from MICFs, providing a cocktail of genetic factors that have potential for further applications in &lt;i&gt;in vivo&lt;/i&gt; cardiac reprogramming.</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3005,32 +4225,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>27903753</t>
+          <t>37856222</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>A Novel LSD1 Inhibitor T-3775440 Disrupts GFI1B-Containing Complex Leading to Transdifferentiation and Impaired Growth of AML Cells.</t>
+          <t>Localized T3 production modifies the transcriptome and promotes the hepatocyte-like lineage in iPSC-derived hepatic organoids.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>acute erythroid leukemia (AEL) cells</t>
+          <t>induced pluripotent stem cell (iPSC)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>granulomonocytic-like lineage cells</t>
+          <t>hepatic organoid (hepatocyte and cholangiocyte)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>T-3775440</t>
+          <t>BMP4, BMP7, FGF7, CHIR99021</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>small_molecule</t>
+          <t>cytokine, cytokine, cytokine, small_molecule</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3045,16 +4265,42 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>abstract</t>
+          <t>fulltext</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>T-3775440 treatment enforced transdifferentiation of erythroid/megakaryocytic lineages into granulomonocytic-like lineage cells.</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/37856222</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>On day 10, the 2D cultures were disrupted by dissociation, and subsequently, the cells self-reestablished into a 3D structure that grew progressively under stimulation of key reagents in the differentiation cocktails — i.e., BMP4, BMP7, FGF7, and the WNT agonist CHIR99021 — to promote the hepatic specification (Figure 1D) (17).</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Thyroid hormone (TH) levels are low during development, and the deiodinases control TH signaling through tissue-specific activation or inactivation of TH. Here, we studied human induced pluripotent stem cell-derived (iPSC-derived) hepatic organoids and identified a robust induction of DIO2 expression (the deiodinase that activates T4 to T3) that occurs in hepatoblasts. The surge in DIO2-T3 (the deiodinase that activates thyroxine [T4] to triiodothyronine [T3]) persists until the hepatoblasts differentiate into hepatocyte- or cholangiocyte-like cells, neither of which expresses DIO2. Preventing the induction of the DIO2-T3 signaling modified the expression of key transcription factors, decreased the number of hepatocyte-like cells by ~60%, and increased the number of cholangiocyte-like cells by ~55% without affecting the growth or the size of the mature liver organoid. Physiological levels of T3 could not fully restore the transition from hepatoblasts to mature cells. This indicates that the timed surge in DIO2-T3 signaling critically determines the fate of developing human hepatoblasts and the transcriptome of the maturing hepatocytes, with physiological and clinical implications for how the liver handles energy substrates.</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3062,37 +4308,37 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>37679064</t>
+          <t>35538505</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Uncovering the role of FOXA2 in the Development of Human Serotonin Neurons.</t>
+          <t>Mouse mesoderm-specific transcript inhibits adipogenic differentiation and induces trans-differentiation into hepatocyte-like cells in 3T3-L1 preadiocytes.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>human pluripotent stem cell (hPSC)</t>
+          <t>3T3-L1 preadipocyte</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>serotonin neurons (SNs)</t>
+          <t>hepatocyte</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>retinoic acid, modulation of Sonic Hedgehog signaling</t>
+          <t>Mest</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>small_molecule, other</t>
+          <t>TF</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3102,16 +4348,42 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>abstract</t>
+          <t>fulltext</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Furthermore, repressing FOXA2 expression by retinoic acid (RA) and dynamically modulating Sonic Hedgehog (SHH) signaling pathway promotes human SN differentiation.</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/35538505</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Further, Mest induced trans-differentiation of 3T3-L1 cells into hepatocytes, and its overexpression induced the expression of hepatocyte marker genes, including albumin and α-fetoprotein.</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>The mesoderm-specific transcript (Mest) is an imprinted gene that is transcribed from the paternal allele. It is a marker of adipose tissue expansion; however, it is uncertain whether Mest expression promotes or suppresses adipogenic differentiation. To elucidate the effects of Mest expression on adipogenic differentiation, we transfected an expression vector or siRNA for mouse Mest into 3T3-L1 mouse preadipocyte cell line. In differentiated 3T3-L1 adipocytes, Mest overexpression decreased lipid accumulation. Conversely, gene silencing of Mest increased the accumulation of lipid droplets in adipocytes. These results demonstrate that Mest negatively regulates adipocyte differentiation. Further, Mest induced trans-differentiation of 3T3-L1 cells into hepatocytes, and its overexpression induced the expression of hepatocyte marker genes, including albumin and α-fetoprotein. In the presence of dexamethasone, the forced expression of the Mest caused morphological changes in 3T3-L1 cells. Cells were flat and polygonal shapes, with an increased accumulation of intracellular glycogen and other features that are typical of hepatocytes. Therefore, Mest inhibits adipogenic differentiation of 3T3-L1 preadipocytes by inducing hepatocyte trans-differentiation.</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3119,37 +4391,37 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>37126449</t>
+          <t>40913769</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cross-activation of FGF, NODAL, and WNT pathways constrains BMP-signaling-mediated induction of the totipotent state in mouse embryonic stem cells.</t>
+          <t>Chemogenetic tuning reveals optimal MAPK signaling for cell-fate programming.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>mouse embryonic stem cell (mESC)</t>
+          <t>mouse embryonic fibroblast (MEF)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>totipotent cell</t>
+          <t>motor neuron</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>BMP signaling, inhibition of FGF pathway, inhibition of NODAL pathway, inhibition of WNT pathway</t>
+          <t>NGN2, Isl1, Lhx3, p53DD, HRASG12V, RepSox</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>other, other, other, other</t>
+          <t>TF, TF, TF, other, other, small_molecule</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3159,16 +4431,42 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>abstract</t>
+          <t>fulltext</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>We exploit this finding to enhance the proportion of totipotent cells by rationally inhibiting the cross-activated pathways.</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/40913769</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>In this model system, the transduction of mouse embryonic fibroblasts with a single cassette of transcription factors (Ngn2, Isl1, and Lhx3 [NIL]) drives their conversion to motor neurons (Figure 1B).</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Cell states evolve through the combined activity of signaling pathways and gene networks. While transcription factors can direct cell fate, these factors rely on a receptive cell state. How signaling levels contribute to the emergence of receptive cell states remains poorly defined. Using a well-defined model of direct conversion, we examined how levels of the mitogen-activated protein kinase (MAPK)-activating oncogene HRAS&lt;sup&gt;G12V&lt;/sup&gt; influence direct conversion of primary fibroblasts to induced motor neurons. The rates of direct conversion respond biphasically to increasing HRAS&lt;sup&gt;G12V&lt;/sup&gt; levels. An optimal "Goldilocks" level of MAPK signaling efficiently drives cell-fate programming, whereas high levels of HRAS&lt;sup&gt;G12V&lt;/sup&gt; induce senescence. Through chemogenetic tuning, we set the optimal MAPK activity for high rates of conversion in the absence of HRAS mutants. In addition to proliferation, MAPK signaling influences conversion by regulating Ngn2 activity. Our results highlight the need to tune therapeutic interventions within a non-monotonic landscape that is shaped by genetics and levels of gene expression.</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3176,37 +4474,37 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>22029419</t>
+          <t>26732729</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cobalt chloride pretreatment promotes cardiac differentiation of human embryonic stem cells under atmospheric oxygen level.</t>
+          <t>miR-124-9-9* potentiates Ascl1-induced reprogramming of cultured Müller glia.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>human embryonic stem cell (hESC)</t>
+          <t>Müller glia</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>cardiomyocyte</t>
+          <t>retinal neuron</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>cobalt chloride</t>
+          <t>miR-124-9-9*</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>small_molecule</t>
+          <t>miRNA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3221,11 +4519,37 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Treatment of undifferentiated hES2 human ESCs with 50 μM cobalt chloride markedly increased protein levels of the HIF-1α subunit, and was associated with increased expression of early cardiac specific transcription factors and cardiotrophic factors including NK2.5, vascular endothelial growth factor, and cardiotrophin-1.</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/26732729</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>The aim of this study was to test whether (1) lentiviral gene transfer of miR-124-9-9* can reprogram Müller glia into retinal neurons and (2) miR-124-9-9* can improve Ascl1-induced reprogramming.</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>The Müller glia of fish provide a source for neuronal regeneration after injury, but they do not do so in mammals. We previously showed that lentiviral gene transfer of the transcription factor Achaete-scute homolog 1 (Ascl1/Mash1) in murine Müller glia cultures resulted in partial reprogramming of the cells to retinal progenitors. The microRNAs (miRNAs) miR-124-9-9* facilitate neuronal reprogramming of fibroblasts, but their role in glia reprogramming has not been reported. The aim of this study was to test whether (1) lentiviral gene transfer of miR-124-9-9* can reprogram Müller glia into retinal neurons and (2) miR-124-9-9* can improve Ascl1-induced reprogramming. Primary Müller glia cultures were generated from postnatal day (P) 11/12 mice, transduced with lentiviral particles, i.e., miR-124-9-9*-RFP, nonsense-RFP, Ascl1-GFP, or GFP-control. Gene expression and immunofluorescence analyses were performed within 3 weeks after infection. 1. Overexpression of miR-124-9-9* induced the expression of the proneural factor Ascl1 and additional markers of neurons, including TUJ1 and MAP2. 2. When Ascl1 and miR-124-9-9* were combined, 50 to 60% of Müller glia underwent neuronal reprogramming, whereas Ascl1 alone results in a 30 to 35% reprogramming rate. 3. Analysis of the miR-124-9-9* treated glial cells showed a reduction in the level of Ctdsp1 and Ptbp1, indicating a critical role for the REST pathway in the repression of neuronal genes in Müller glia. Our data further suggest that miR-124-9-9* and the REST complex may play a role in regulating the reprogramming of Müller glia to progenitors that underlies retinal regeneration in zebrafish.</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3233,37 +4557,37 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>40715046</t>
+          <t>31489945</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Direct transdifferentiation of tumorigenic melanoma cells induces tumor cell reversion.</t>
+          <t>mRNA-Driven Generation of Transgene-Free Neural Stem Cells from Human Urine-Derived Cells.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>human melanoma cells (BRAF-mutated and NRAS-mutated lines)</t>
+          <t>human urine-derived cells (hUCs)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>induced neuron (iN)</t>
+          <t>neural stem cells (iNSCs)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ASCL1, BRN2, MYT1L, NEUROD1</t>
+          <t>defined small molecules, self-replicable mRNA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>TF, TF, TF, TF</t>
+          <t>small_molecule, other</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3273,16 +4597,42 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>fulltext</t>
+          <t>abstract</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>In order to examine if melanoma cells can be transdifferentiated into neurons, the neuron-specific transcription factors ASCL1, BRN2, MYT1L, and NEUROD1 were ectopically overexpressed in different melanoma cell lines (Figs. 1B, C and S1A, B).</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/31489945</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Here, we describe the advanced transgene-free generation of iNSCs from human urine-derived cells (HUCs) by combining a cocktail of defined small molecules with self-replicable mRNA delivery.</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Human neural stem cells (NSCs) hold enormous promise for neurological disorders, typically requiring their expandable and differentiable properties for regeneration of damaged neural tissues. Despite the therapeutic potential of induced NSCs (iNSCs), a major challenge for clinical feasibility is the presence of integrated transgenes in the host genome, contributing to the risk for undesired genotoxicity and tumorigenesis. Here, we describe the advanced transgene-free generation of iNSCs from human urine-derived cells (HUCs) by combining a cocktail of defined small molecules with self-replicable mRNA delivery. The established iNSCs were completely transgene-free in their cytosol and genome and further resembled human embryonic stem cell-derived NSCs in the morphology, biological characteristics, global gene expression, and potential to differentiate into functional neurons, astrocytes, and oligodendrocytes. Moreover, iNSC colonies were observed within eight days under optimized conditions, and no teratomas formed in vivo, implying the absence of pluripotent cells. This study proposes an approach to generate transplantable iNSCs that can be broadly applied for neurological disorders in a safe, efficient, and patient-specific manner.</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3290,32 +4640,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>28462819</t>
+          <t>27874233</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Human ESC/iPSC-Derived Hepatocyte-like Cells Achieve Zone-Specific Hepatic Properties by Modulation of WNT Signaling.</t>
+          <t>Induction of hepatocyte-like cells from human umbilical cord-derived mesenchymal stem cells by defined microRNAs.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>human ESC/iPSC-derived hepatocyte-like cells</t>
+          <t>mesenchymal stem cell (MSC)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>perivenous zone-specific hepatocyte-like cells</t>
+          <t>hepatocyte-like cell</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>WNT7B, WNT8B</t>
+          <t>miR-122, miR-1246, miR-1290, miR-148a, miR-424, miR-542-5p</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>cytokine, cytokine</t>
+          <t>miRNA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3330,16 +4680,787 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t>fulltext</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/27874233</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>These results demonstrated that 6mix‐without‐miR‐30a set successfully induced hepatic differentiation of hMSCs, which demonstrated miR‐30a was dispensable for the induction of HLCs.</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Generating functional hepatocyte-like cells (HLCs) from mesenchymal stem cells (MSCs) is of great urgency for bio-artificial liver support system (BALSS). Previously, we obtained HLCs from human umbilical cord-derived MSCs by overexpressing seven microRNAs (HLC-7) and characterized their liver functions in vitro and in vivo. Here, we aimed to screen out the optimal miRNA candidates for hepatic differentiation. We sequentially removed individual miRNAs from the pool and examined the effect of transfection with remainder using RT-PCR, periodic acid-Schiff (PAS) staining and low-density lipoprotein (LDL) uptake assays and by assessing their function in liver injury models. Surprisingly, miR-30a and miR-1290 were dispensable for hepatic differentiation. The remaining five miRNAs (miR-122, miR-148a, miR-424, miR-542-5p and miR-1246) are essential for this process, because omitting any one from the five-miRNA combination prevented hepatic trans-differentiation. We found that HLCs trans-differentiated from five microRNAs (HLC-5) expressed high level of hepatic markers and functioned similar to hepatocytes. Intravenous transplantation of HLC-5 into nude mice with CCl&lt;sub&gt;4&lt;/sub&gt; -induced fulminant liver failure and acute liver injury not only improved serum parameters and their liver histology, but also improved survival rate of mice in severe hepatic failure. These data indicated that HLC-5 functioned similar to HLC-7 in vitro and in vivo, which have been shown to resemble hepatocytes. Instead of using seven-miRNA combination, a simplified five-miRNA combination can be used to obtain functional HLCs in only 7 days. Our study demonstrated an optimized and efficient method for generating functional MSC-derived HLCs that may serve as an attractive cell alternative for BALSS.</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>known_issue_note</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>pmid</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>source_cell</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>target_cell</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>factors</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>factor_type</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>single_tf_flag</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>is_duplicate</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>pubmed_url</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>evidence_sentence</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>abstract</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Here, we identified that WNT7B and WNT8B secreted from hepatocytes and cholangiocytes play important roles in achieving perivenous zone-specific characteristics, such as the enhancement of glutamine secretion, citric acid cycle, cytochrome P450 (CYP) 1A2 metabolism, and CYP1A2 induction capacities.</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>single TF likely member of Yamanaka recipe, not standalone SOX2 recipe</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>32016422</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Concurrent binding to DNA and RNA facilitates the pluripotency reprogramming activity of Sox2.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>somatic cell</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>pluripotent state</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SOX2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/32016422</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Deletion of the RBM does not affect selection of target genes but mitigates binding to pluripotency related transcripts, switches exon usage and impairs the reprogramming of somatic cells to a pluripotent state.</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Some transcription factors that specifically bind double-stranded DNA appear to also function as RNA-binding proteins. Here, we demonstrate that the transcription factor Sox2 is able to directly bind RNA in vitro as well as in mouse and human cells. Sox2 targets RNA via a 60-amino-acid RNA binding motif (RBM) positioned C-terminally of the DNA binding high mobility group (HMG) box. Sox2 can associate with RNA and DNA simultaneously to form ternary RNA/Sox2/DNA complexes. Deletion of the RBM does not affect selection of target genes but mitigates binding to pluripotency related transcripts, switches exon usage and impairs the reprogramming of somatic cells to a pluripotent state. Our findings designate Sox2 as a multi-functional factor that associates with RNA whilst binding to cognate DNA sequences, suggesting that it may co-transcriptionally regulate RNA metabolism during somatic cell reprogramming.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>peer-reviewed version of PMID 36993577</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>37421991</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A novel transcription factor combination for direct reprogramming to a spontaneously contracting human cardiomyocyte-like state.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>cardiac fibroblast</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>cardiomyocyte-like state</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>MYOCD, SMAD6, TBX20, FGF2, XAV939</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>TF, TF, TF, cytokine, small_molecule</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/37421991</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Addition of FGF2 and XAV939 to the MST cocktail resulted in reprogrammed cells with spontaneous contraction and cardiomyocyte-like calcium transients.</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>The reprogramming of somatic cells to a spontaneously contracting cardiomyocyte-like state using defined transcription factors has proven successful in mouse fibroblasts. However, this process has been less successful in human cells, thus limiting the potential clinical applicability of this technology in regenerative medicine. We hypothesized that this issue is due to a lack of cross-species concordance between the required transcription factor combinations for mouse and human cells. To address this issue, we identified novel transcription factor candidates to induce cell conversion between human fibroblasts and cardiomyocytes, using the network-based algorithm Mogrify. We developed an automated, high-throughput method for screening transcription factor, small molecule, and growth factor combinations, utilizing acoustic liquid handling and high-content kinetic imaging cytometry. Using this high-throughput platform, we screened the effect of 4960 unique transcription factor combinations on direct conversion of 24 patient-specific primary human cardiac fibroblast samples to cardiomyocytes. Our screen revealed the combination of MYOCD, SMAD6, and TBX20 (MST) as the most successful direct reprogramming combination, which consistently produced up to 40% TNNT2&lt;sup&gt;+&lt;/sup&gt; cells in just 25 days. Addition of FGF2 and XAV939 to the MST cocktail resulted in reprogrammed cells with spontaneous contraction and cardiomyocyte-like calcium transients. Gene expression profiling of the reprogrammed cells also revealed the expression of cardiomyocyte associated genes. Together, these findings indicate that cardiac direct reprogramming in human cells can be achieved at similar levels to those attained in mouse fibroblasts. This progress represents a step forward towards the clinical application of the cardiac direct reprogramming approach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bioRxiv/preprint duplicate; should prefer peer-reviewed PMID 37421991</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>36993577</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A Novel Transcription Factor Combination for Direct Reprogramming to a Spontaneously Contracting Human Cardiomyocyte-like State.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>cardiac fibroblast</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>cardiomyocyte</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>MYOCD, SMAD6, TBX20, FGF2, XAV939</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>TF, TF, TF, cytokine, small_molecule</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/36993577</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Addition of FGF2 and XAV939 to the MST cocktail resulted in reprogrammed cells with spontaneous contraction and cardiomyocyte-like calcium transients.</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>The reprogramming of somatic cells to a spontaneously contracting cardiomyocyte-like state using defined transcription factors has proven successful in mouse fibroblasts. However, this process has been less successful in human cells, thus limiting the potential clinical applicability of this technology in regenerative medicine. We hypothesized that this issue is due to a lack of cross-species concordance between the required transcription factor combinations for mouse and human cells. To address this issue, we identified novel transcription factor candidates to induce cell conversion between human fibroblasts and cardiomyocytes, using the network-based algorithm Mogrify. We developed an automated, high-throughput method for screening transcription factor, small molecule, and growth factor combinations, utilizing acoustic liquid handling and high-content kinetic imaging cytometry. Using this high-throughput platform, we screened the effect of 4,960 unique transcription factor combinations on direct conversion of 24 patient-specific primary human cardiac fibroblast samples to cardiomyocytes. Our screen revealed the combination of &lt;i&gt;MYOCD&lt;/i&gt; , &lt;i&gt;SMAD6&lt;/i&gt; , and &lt;i&gt;TBX20&lt;/i&gt; (MST) as the most successful direct reprogramming combination, which consistently produced up to 40% TNNT2 &lt;sup&gt;+&lt;/sup&gt; cells in just 25 days. Addition of FGF2 and XAV939 to the MST cocktail resulted in reprogrammed cells with spontaneous contraction and cardiomyocyte-like calcium transients. Gene expression profiling of the reprogrammed cells also revealed the expression of cardiomyocyte associated genes. Together, these findings indicate that cardiac direct reprogramming in human cells can be achieved at similar levels to those attained in mouse fibroblasts. This progress represents a step forward towards the clinical application of the cardiac direct reprogramming approach. Using network-based algorithm Mogrify, acoustic liquid handling, and high-content kinetic imaging cytometry we screened the effect of 4,960 unique transcription factor combinations. Using 24 patient-specific human fibroblast samples we identified the combination of &lt;i&gt;MYOCD&lt;/i&gt; , &lt;i&gt;SMAD6&lt;/i&gt; , and &lt;i&gt;TBX20&lt;/i&gt; (MST) as the most successful direct reprogramming combination. MST cocktail results in reprogrammed cells with spontaneous contraction, cardiomyocyte-like calcium transients, and expression of cardiomyocyte associated genes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>abstract entry missing source/small molecules; fulltext entry may be more accurate</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>31089332</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Metastable Reprogramming State of Single Transcription Factor-Derived Induced Hepatocyte-Like Cells.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>induced hepatocyte-like cells (iHeps)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>HNF1A, small molecules</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TF, small_molecule</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/31089332</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>We previously described the generation of induced hepatocyte-like cells (iHeps) using the hepatic transcription factor &lt;i&gt;Hnf1a&lt;/i&gt; together with small molecules.</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>We previously described the generation of induced hepatocyte-like cells (iHeps) using the hepatic transcription factor &lt;i&gt;Hnf1a&lt;/i&gt; together with small molecules. These iHeps represent a hepatic state that is more mature compared with iHeps generated with multiple hepatic factors. However, the underlying mechanism of hepatic conversion involving transgene dependence of the established iHeps is largely unknown. Here, we describe the generation of transgene-independent iHeps by inducing the ectopic expression of &lt;i&gt;Hnf1a&lt;/i&gt; using both an episomal vector and a doxycycline-inducible lentivirus. In contrast to iHeps with sustained expression of &lt;i&gt;Hnf1a&lt;/i&gt;, transgene-independent &lt;i&gt;Hnf1a&lt;/i&gt; iHeps lose their typical morphology and &lt;i&gt;in vitro&lt;/i&gt; functionality with rapid downregulation of hepatic markers upon withdrawal of small molecules. Taken together, our data indicates that the reprogramming state of single factor &lt;i&gt;Hnf1a-&lt;/i&gt;derived iHeps is metastable and that the hepatic identity of these cells could be maintained only by the continuous supply of either small molecules or the master hepatic factor &lt;i&gt;Hnf1a&lt;/i&gt;. Our findings emphasize the importance of a factor screening strategy for inducing specific cellular identities with a stable reprogramming state in order to eventually translate direct conversion technology to the clinic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>abstract entry missing source/small molecules; fulltext entry may be more accurate</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>31089332</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Metastable Reprogramming State of Single Transcription Factor-Derived Induced Hepatocyte-Like Cells.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>mouse embryonic fibroblast (MEF)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>induced hepatocyte-like cell (iHep)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>HNF1A, A83-01, BMP4, CHIR99021</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>TF, small_molecule, small_molecule, small_molecule</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>fulltext</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/31089332</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>To elucidate the role of Hnf1a in the maintenance of the reprogrammed hepatic state, we introduced the master hepatic factor Hnf1a [36–38] in mouse embryonic fibroblasts (MEFs) using an episomal vector system [13] in the presence of three small molecules, A83-01, BMP4, and CHIR99021 (ABR), as we had described previously [13, 31] (Figure 1(a)).</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>We previously described the generation of induced hepatocyte-like cells (iHeps) using the hepatic transcription factor &lt;i&gt;Hnf1a&lt;/i&gt; together with small molecules. These iHeps represent a hepatic state that is more mature compared with iHeps generated with multiple hepatic factors. However, the underlying mechanism of hepatic conversion involving transgene dependence of the established iHeps is largely unknown. Here, we describe the generation of transgene-independent iHeps by inducing the ectopic expression of &lt;i&gt;Hnf1a&lt;/i&gt; using both an episomal vector and a doxycycline-inducible lentivirus. In contrast to iHeps with sustained expression of &lt;i&gt;Hnf1a&lt;/i&gt;, transgene-independent &lt;i&gt;Hnf1a&lt;/i&gt; iHeps lose their typical morphology and &lt;i&gt;in vitro&lt;/i&gt; functionality with rapid downregulation of hepatic markers upon withdrawal of small molecules. Taken together, our data indicates that the reprogramming state of single factor &lt;i&gt;Hnf1a-&lt;/i&gt;derived iHeps is metastable and that the hepatic identity of these cells could be maintained only by the continuous supply of either small molecules or the master hepatic factor &lt;i&gt;Hnf1a&lt;/i&gt;. Our findings emphasize the importance of a factor screening strategy for inducing specific cellular identities with a stable reprogramming state in order to eventually translate direct conversion technology to the clinic.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>allowed_values</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>how_to_use</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Original extraction label: source cell, target cell, and named factor/cocktail are explicitly supported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Original extraction label: conversion is likely, but source/target/factors are vague, partial, or need full-text confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Original extraction label: conversion is inferred or weakly supported; usually not included in default website view.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>recipe_valid</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>yes | partial | no | unclear</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Overall recipe-level correctness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>source_cell_valid</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>yes | partial | no | not_applicable</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Whether source cell is correct and specific enough.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>target_cell_valid</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>yes | partial | no | not_applicable</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Whether target cell is correct and specific enough.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>factors_valid</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>yes | partial | no | not_applicable</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Whether the factor list is correct and complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>standalone_recipe</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>yes | no_member_of_larger_recipe | unclear</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Use no_member_of_larger_recipe for cases like SOX2-only Yamanaka-member papers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>duplicate_status</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>no_duplicate | duplicate_preprint | duplicate_other | unsure</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mark PMID-level duplicates, especially bioRxiv to peer-reviewed pairs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>preferred_pmid</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PMID or blank</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>For duplicates, enter the PMID that should be kept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>error_category</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>single_tf_incomplete; missing_source; factors_unspecified; wrong_factor; wrong_cell; duplicate_preprint; target_synonym; evidence_weak; other</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Use semicolon-separated tags.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>keep | fix | hide_single_tf | mark_duplicate | remove | needs_fulltext</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Suggested database action after annotation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>corrected_source_cell</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>free text</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Fill only if source_cell needs correction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>corrected_target_cell</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>free text</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Fill only if target_cell needs correction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>corrected_factors</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>free text</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Fill only if factors need correction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>annotation_notes</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>free text</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Short explanation or literature note.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/verification_sample_v3.xlsx
+++ b/verification_sample_v3.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA51"/>
+  <dimension ref="A1:AB51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,85 +483,90 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>conversion_scope</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>single_tf_flag</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>pubmed_url</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>evidence_sentence</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>abstract</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>recipe_valid</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>source_cell_valid</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>target_cell_valid</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>factors_valid</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>standalone_recipe</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>duplicate_status</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>preferred_pmid</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>error_category</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>action</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>corrected_source_cell</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>corrected_target_cell</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>corrected_factors</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>annotation_notes</t>
         </is>
@@ -573,17 +578,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>34977272</t>
+          <t>31806618</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>miRNA-mediated control of exogenous &lt;i&gt;OCT4&lt;/i&gt; during mesenchymal-epithelial transition increases measles vector reprogramming efficiency.</t>
+          <t>NANOG and LIN28 dramatically improve human cell reprogramming by modulating LIN41 and canonical WNT activities.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>human neonatal fibroblast (NHF) or adult human fibroblast (AHF)</t>
+          <t>primary mesenchymal stem cells (MSCs)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -593,12 +598,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>OCT4, SOX2, KLF4, c-MYC</t>
+          <t>OCT4, SOX2, KLF4, MYC, GLIS1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>TF, TF, TF, TF</t>
+          <t>TF, TF, TF, TF, TF</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -618,37 +623,69 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>classical_reprogramming</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/34977272</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>We have previously produced a single-cycle MeV expressing the four RFs, MV4FN, to produce iPSCs.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/31806618</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>&lt;i&gt;OCT4&lt;/i&gt; is a key mediator of induced pluripotent stem cell (iPSC) reprogramming, but the mechanistic insights into the role of exogenous &lt;i&gt;OCT4&lt;/i&gt; and timelines that initiate pluripotency remain to be resolved. Here, using measles reprogramming vectors, we present microRNA (miRNA) targeting of exogenous &lt;i&gt;OCT4&lt;/i&gt; to shut down its expression during the mesenchymal to the epithelial transition phase of reprogramming. We showed that exogenous &lt;i&gt;OCT4&lt;/i&gt; is required only for the initiation of reprogramming and is dispensable for the maturation stage. However, the continuous expression of &lt;i&gt;SOX2&lt;/i&gt;, &lt;i&gt;KLF4&lt;/i&gt;, and &lt;i&gt;c-MYC&lt;/i&gt; is necessary for the maturation stage of the iPSC. Additionally, we demonstrate a novel application of miRNA targeting in a viral vector to contextually control the vector/transgene, ultimately leading to an improved reprogramming efficiency. This novel approach could be applied to other systems for improving the efficiency of vector-induced processes.</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+          <t>The applications of GLIS1, NANOG or LIN28 each improved the reprogramming efficiency of human MSCs compared with OSKM</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Human cell reprogramming remains extremely inefficient and the underlying mechanisms by different reprogramming factors are elusive. We found that NANOG and LIN28 (NL) synergize to improve OCT4, SOX2, KLF4 and MYC (OSKM)-mediated reprogramming by ∼76-fold and shorten reprogramming latency by at least 1 week. This synergy is inhibited by GLIS1 but reinforced by an inhibitor of the histone methyltransferase DOT1L (iDOT1L) to a ∼127-fold increase in TRA-1-60-positive (+) iPSC colonies. Mechanistically, NL serve as the main drivers of reprogramming in cell epithelialization, the expression of Let-7 miRNA target &lt;i&gt;LIN41&lt;/i&gt;, and the activation of canonical WNT/β-CATENIN signaling, which can be further enhanced by iDOT1L treatment. &lt;i&gt;LIN41&lt;/i&gt; overexpression in addition to OSKM similarly promoted cell epithelialization and WNT activation in reprogramming, and a dominant-negative LIN41 mutation significantly blocked NL- and iDOT1L-enhanced reprogramming. We also found that NL- and iDOT1L-induced canonical WNT activation facilitates the initial development kinetics of iPSCs. However, a substantial increase in more mature, homogeneous TRA-1-60+ colony formation was achieved by inhibiting WNT activity at the middle-to-late-reprogramming stage. We further found that LIN41 can replace LIN28 to synergize with NANOG, and that the coexpression of LIN41 with NL further enhanced the formation of mature iPSCs under WNT inhibition. Our study established LIN41 and canonical WNT signaling as the key downstream effectors of NL for the dramatic improvement in reprogramming efficiency and kinetics, and optimized a condition for the robust formation of mature human iPSC colonies from primary cells.This article has an associated First Person interview with the first author of the paper.</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>evidence_weak</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Evidence sentence describes GLIS1/NANOG/LIN28 as OSKM efficiency enhancers, not a standalone reprogramming demonstration. Factors list (OSKM+GLIS1) is plausible but sentence does not confirm successful iPSC formation.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -656,32 +693,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>38903080</t>
+          <t>36104343</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Generation of hiPSC-derived brain microvascular endothelial cells using a combination of directed differentiation and transcriptional reprogramming strategies.</t>
+          <t>Cancer co-opts differentiation of B-cell precursors into macrophage-like cells.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>induced pluripotent stem cell (iPSC)</t>
+          <t>bone marrow pre-B and immature B cells</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>brain microvascular endothelial cell (BMEC)</t>
+          <t>macrophage</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FOXF2, ZIC3</t>
+          <t>M-CSF</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>TF, TF</t>
+          <t>cytokine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -701,37 +738,69 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/38903080</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Here, we report generation, transcriptomic and functional characterization of reprogrammed BMECs (rBMECs) by combining hiPSC differentiation into BBB-primed endothelial cells and reprogramming with two BBB transcription factors FOXF2 and ZIC3.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/36104343</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>The blood-brain barrier (BBB), formed by specialized brain microvascular endothelial cells (BMECs), regulates brain function in health and disease. &lt;i&gt;In vitro&lt;/i&gt; modeling of the human BBB is limited by the lack of robust hiPSC protocols to generate BMECs. Here, we report generation, transcriptomic and functional characterization of reprogrammed BMECs (rBMECs) by combining hiPSC differentiation into BBB-primed endothelial cells and reprogramming with two BBB transcription factors FOXF2 and ZIC3. rBMECs express a subset of the BBB gene repertoire including tight junctions and transporters, exhibit stronger paracellular barrier properties, lower caveolar-mediated transcytosis, and similar p-Glycoprotein activity compared to primary HBMECs. They can acquire an inflammatory phenotype when treated with oligomeric Aβ42. rBMECs integrate with hiPSC-derived pericytes and astrocytes to form a 3D neurovascular system using the MIMETAS microfluidics platform. This novel 3D system resembles the &lt;i&gt;in vivo&lt;/i&gt; BBB at structural and functional levels to enable investigation of pathogenic mechanisms of neurological diseases.</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+          <t>We link the transdifferentiation to a small subset of CSF1R&lt;sup&gt;+&lt;/sup&gt; Pax5&lt;sup&gt;Low&lt;/sup&gt; cells within BM pre-B and immature B cells responding to cancer-secreted M-CSF with downregulation of the transcription factor Pax5 via CSF1R signaling.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>We have recently reported that some cancers induce accumulation of bone marrow (BM) B-cell precursors in the spleen to convert them into metastasis-promoting, immunosuppressive B cells. Here, using various murine tumor models and samples from humans with breast and ovarian cancers, we provide evidence that cancers also co-opt differentiation of these B-cell precursors to generate macrophage-like cells (termed B-MF). We link the transdifferentiation to a small subset of CSF1R&lt;sup&gt;+&lt;/sup&gt; Pax5&lt;sup&gt;Low&lt;/sup&gt; cells within BM pre-B and immature B cells responding to cancer-secreted M-CSF with downregulation of the transcription factor Pax5 via CSF1R signaling. Although the primary source of tumor-associated macrophages is monocytes, B-MFs are phenotypically and functionally distinguishable. Compared to monocyte-derived macrophages, B-MFs more efficiently phagocytize apoptotic cells, suppress proliferation of T cells and induce FoxP3&lt;sup&gt;+&lt;/sup&gt; regulatory T cells. In mouse tumor models, B-MFs promote shrinkage of the tumor-infiltrating IFNγ&lt;sup&gt;+&lt;/sup&gt; CD4 T cell pool and increase cancer progression and metastasis, suggesting that this cancer-induced transdifferentiation pathway is functionally relevant and hence could serve as an immunotherapeutic target.</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>evidence_weak;factors_unspecified</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>M-CSF is a cytokine cue, not a TF reprogramming factor. Evidence sentence describes a mechanistic finding in a CSF1R+ Pax5Low subset, not a direct reprogramming experimental result. Context is cancer-induced transdifferentiation.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -739,32 +808,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>28514439</t>
+          <t>28665920</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Haematopoietic stem and progenitor cells from human pluripotent stem cells.</t>
+          <t>Lineage conversion of mouse fibroblasts to pancreatic α-cells.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CD34+FLK1+CD235A−CD43− hemogenic endothelium derived from human pluripotent stem cells</t>
+          <t>mouse tail-tip fibroblast (TTF) from p19Arf-/- mice</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>hematopoietic stem/progenitor cells with multi-lineage engraftment potential</t>
+          <t>glucagon-producing cell (iAlpha cell)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>RUNX1, LCOR, SPI1, ERG, HOXA5, HOXA9, HOXA10</t>
+          <t>GATA4, PDX1, Hhex, Pax4, FOXA3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>TF, TF, TF, TF, TF, TF, TF</t>
+          <t>TF, TF, TF, TF, TF</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -784,37 +853,65 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/28514439</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Conversion of haemogenic endothelium (HE) into haematopoietic stem/progenitor cells by seven transcription factors requires EHT.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/28665920</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>A variety of tissue lineages can be differentiated from pluripotent stem cells by mimicking embryonic development through stepwise exposure to morphogens, or by conversion of one differentiated cell type into another by enforced expression of master transcription factors. Here, to yield functional human haematopoietic stem cells, we perform morphogen-directed differentiation of human pluripotent stem cells into haemogenic endothelium followed by screening of 26 candidate haematopoietic stem-cell-specifying transcription factors for their capacity to promote multi-lineage haematopoietic engraftment in mouse hosts. We recover seven transcription factors (ERG, HOXA5, HOXA9, HOXA10, LCOR, RUNX1 and SPI1) that are sufficient to convert haemogenic endothelium into haematopoietic stem and progenitor cells that engraft myeloid, B and T cells in primary and secondary mouse recipients. Our combined approach of morphogen-driven differentiation and transcription-factor-mediated cell fate conversion produces haematopoietic stem and progenitor cells from pluripotent stem cells and holds promise for modelling haematopoietic disease in humanized mice and for therapeutic strategies in genetic blood disorders.</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+          <t>Taken together, TTFs are converted into glucagon-producing cells with 5TF overexpression and culture in neural-basal medium-based conditional medium for 28 days (Figure 1j; Supplementary Figure S1e).</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>α-cells, which synthesize glucagon, also support β-cell survival and have the capacity to transdifferentiate into β-cells. However, the role of α-cells in pathological conditions and their putative clinical applications remain elusive due in large part to the lack of mature α-cells. Here, we present a new technique to generate functional α-like cells. α-like cells (iAlpha cells) were generated from mouse fibroblasts by transduction of transcription factors, including Hhex, Foxa3, Gata4, Pdx1 and Pax4, which induce α-cell-specific gene expression and glucagon secretion in response to KCl and Arg stimulation. The cell functions in vivo and in vitro were evaluated. Lineage-specific and functional-related gene expression was tested by realtime PCR, insulin tolerance test (ITT), glucose tolerance test (GTT), Ki67 and glucagon immunohistochemistry analysis were done in iAlpha cells transplanted nude mice. iAlpha cells possess α-cell function in vitro and alter blood glucose levels in vivo. Transplantation of iAlpha cells into nude mice resulted in insulin resistance and increased β-cell proliferation. Taken together, we present a novel strategy to generate functional α-like cells for the purposes of disease modeling and regenerative medicine.</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Direct statement: TTFs converted to glucagon-producing cells with 5TF (GATA4, PDX1, Hhex, Pax4, FOXA3) overexpression. Complete, standalone, valid recipe.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -822,17 +919,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26418476</t>
+          <t>31806618</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brief Report: Inhibition of miR-145 Enhances Reprogramming of Human Dermal Fibroblasts to Induced Pluripotent Stem Cells.</t>
+          <t>NANOG and LIN28 dramatically improve human cell reprogramming by modulating LIN41 and canonical WNT activities.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>fibroblast</t>
+          <t>primary mesenchymal stem cells (MSCs)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -842,12 +939,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>OCT4, KLF4, SOX2, c-MYC, miR-145 inhibitor</t>
+          <t>OCT4, SOX2, KLF4, MYC, GLIS1, NANOG, LIN28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>TF, TF, TF, TF, knockdown</t>
+          <t>TF, TF, TF, TF, TF, TF, TF</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -867,37 +964,69 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>classical_reprogramming</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/26418476</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>To assess how inhibition of miR‐145 affects iPSCs generation efficiency, we transiently transfected DFs with miR‐145 inhibitor at day 0. The next day cells were transduced with OKSM and 23 days later the efficiency of iPSCs generation was determined by counting of AP‐positive and TRA‐1‐60‐positive colonies.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/31806618</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>MicroRNA (miRNAs) are short noncoding RNA molecules involved in many cellular processes and shown to play a key role in somatic cell induced reprogramming. We performed an array based screening to identify candidates that are differentially expressed between dermal skin fibroblasts (DFs) and induced pluripotent stem cells (iPSCs). We focused our investigations on miR-145 and showed that this candidate is highly expressed in DFs relative to iPSCs and significantly downregulated during reprogramming process. Inhibition of miR-145 in DFs led to the induction of "cellular plasticity" demonstrated by: (a) alteration of cell morphology associated with downregulation of mesenchymal and upregulation of epithelial markers; (b) upregulation of pluripotency-associated genes including SOX2, KLF4, C-MYC; (c) downregulation of miRNA let-7b known to inhibit reprogramming; and (iv) increased efficiency of reprogramming to iPSCs in the presence of reprogramming factors. Together, our results indicate a direct functional link between miR-145 and molecular pathways underlying reprogramming of somatic cells to iPSCs.</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
+          <t>Primary MSCs were transduced with OSKM or OSKM+GNL expressed in a retroviral pMXs-vector (Fig. 1A).</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Human cell reprogramming remains extremely inefficient and the underlying mechanisms by different reprogramming factors are elusive. We found that NANOG and LIN28 (NL) synergize to improve OCT4, SOX2, KLF4 and MYC (OSKM)-mediated reprogramming by ∼76-fold and shorten reprogramming latency by at least 1 week. This synergy is inhibited by GLIS1 but reinforced by an inhibitor of the histone methyltransferase DOT1L (iDOT1L) to a ∼127-fold increase in TRA-1-60-positive (+) iPSC colonies. Mechanistically, NL serve as the main drivers of reprogramming in cell epithelialization, the expression of Let-7 miRNA target &lt;i&gt;LIN41&lt;/i&gt;, and the activation of canonical WNT/β-CATENIN signaling, which can be further enhanced by iDOT1L treatment. &lt;i&gt;LIN41&lt;/i&gt; overexpression in addition to OSKM similarly promoted cell epithelialization and WNT activation in reprogramming, and a dominant-negative LIN41 mutation significantly blocked NL- and iDOT1L-enhanced reprogramming. We also found that NL- and iDOT1L-induced canonical WNT activation facilitates the initial development kinetics of iPSCs. However, a substantial increase in more mature, homogeneous TRA-1-60+ colony formation was achieved by inhibiting WNT activity at the middle-to-late-reprogramming stage. We further found that LIN41 can replace LIN28 to synergize with NANOG, and that the coexpression of LIN41 with NL further enhanced the formation of mature iPSCs under WNT inhibition. Our study established LIN41 and canonical WNT signaling as the key downstream effectors of NL for the dramatic improvement in reprogramming efficiency and kinetics, and optimized a condition for the robust formation of mature human iPSC colonies from primary cells.This article has an associated First Person interview with the first author of the paper.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>evidence_weak</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Evidence sentence only describes vector transduction (methods), not iPSC colony formation outcome. Same paper as row 1. Needs a result-confirming sentence.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -905,32 +1034,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>28223284</t>
+          <t>39724753</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mafa Enables Pdx1 to Effectively Convert Pancreatic Islet Progenitors and Committed Islet α-Cells Into β-Cells In Vivo.</t>
+          <t>Systemic brain dissemination of glioblastoma requires transdifferentiation into endothelial-like cells via TGF-β-ALK1-Smad1/5 signaling.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>pancreatic islet Ngn3-positive progenitors</t>
+          <t>glioblastoma tumor cell</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>β-cell</t>
+          <t>endothelial cell</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mafa, PDX1</t>
+          <t>TGF-β-ALK1-Smad1/5 signaling, TGF-β-ALK5-Smad2/3 signaling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>TF, TF</t>
+          <t>other, other</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -950,37 +1079,69 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/28223284</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Here we have generated transgenic mice conditionally expressing the islet β-cell-enriched Mafa and/or Pdx1 transcription factors to examine their potential to transdifferentiate embryonic pan-islet cell Ngn3-positive progenitors and the later glucagon-positive α-cell population into β-cells.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/39724753</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Among the therapeutic avenues being explored for replacement of the functional islet β-cell mass lost in type 1 diabetes (T1D), reprogramming of adult cell types into new β-cells has been actively pursued. Notably, mouse islet α-cells will transdifferentiate into β-cells under conditions of near β-cell loss, a condition similar to T1D. Moreover, human islet α-cells also appear to poised for reprogramming into insulin-positive cells. Here we have generated transgenic mice conditionally expressing the islet β-cell-enriched Mafa and/or Pdx1 transcription factors to examine their potential to transdifferentiate embryonic pan-islet cell Ngn3-positive progenitors and the later glucagon-positive α-cell population into β-cells. Mafa was found to both potentiate the ability of Pdx1 to induce β-cell formation from Ngn3-positive endocrine precursors and enable Pdx1 to produce β-cells from α-cells. These results provide valuable insight into the fundamental mechanisms influencing islet cell plasticity in vivo.</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
+          <t>Mechanistically, in addition to TGF-β-ALK5-Smad2/3 signaling, glioblastoma tumour cells also activate TGF-β-ALK1-Smad1/5 signaling - a mechanism previously thought to be limited to endothelial cells.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Glioblastoma is the most aggressive type of brain cancer, but treatment improvements for glioblastoma patients remain stagnated for over 20 years. This is despite the large number of clinical trials that have attempted to replicate the success of therapeutics developed for other cancer types. This discrepancy highlights the urgent need to decipher the unique biology of glioblastomas. Here, we show that glioblastoma tumour cells are highly plastic, integrating into blood vessel walls to disseminate throughout the brain. This relies on the transdifferentiation of glioblastoma tumor cells into endothelial-like cells in a process we termed endothelialisation. Mechanistically, in addition to TGF-β-ALK5-Smad2/3 signaling, glioblastoma tumour cells also activate TGF-β-ALK1-Smad1/5 signaling - a mechanism previously thought to be limited to endothelial cells. Consequently, therapeutic targeting of TGF-β-ALK1-Smad1/5 activity impaired endothelialisation-driven glioblastoma progression. This study identifies a previously unknown component of glioblastoma biology and establishes a therapeutic approach to reduce the progression of this disease.</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>evidence_weak;wrong_factor</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Evidence describes TGF-beta signaling pathway activation in tumor cells, not an intentional reprogramming experiment. TGF-beta-ALK1/ALK5 pathways are not reprogramming factors. This is cancer biology mechanistic finding, not cell fate conversion.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -988,12 +1149,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29286621</t>
+          <t>38412659</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Quasi-Stem Cells Derived from Human Somatic Cells by Chemically Modified Carbon Nanotubes.</t>
+          <t>Generation of induced pluripotent stem cell line NIMHi010-A from dermal fibroblast cells of a healthy individual.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1008,12 +1169,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OCT4, NANOG, SOX2</t>
+          <t>c-MYC, SOX2, KLF4, OCT4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>TF, TF, TF</t>
+          <t>TF, TF, TF, TF</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,37 +1194,65 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>classical_reprogramming</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/29286621</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>We obtained encouraging results showing that PLL-SWCNT treatment transformed fibroblast cells, and the transformed cells expressed the pluripotency-associated factors OCT4, NANOG, and SOX2 in addition to TRA-1-60 and SSEA-4, which are characteristic stem cell markers.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/38412659</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Surface modification of micro- and nanotopography was employed to alter the surface properties of scaffolds for controlling cell attachment, proliferation, and differentiation. This study reports a method for generating multinucleated colonies as evidenced by spherical colony formation through nanotopography-induced expression of reprogramming factors in human dermal fibroblasts. Colony formation was achieved by subjecting the cells to specific environments such as culturing with single-walled carbon nanotubes and poly-l-lysine (PLL-SWCNTs). We obtained encouraging results showing that PLL-SWCNT treatment transformed fibroblast cells, and the transformed cells expressed the pluripotency-associated factors OCT4, NANOG, and SOX2 in addition to TRA-1-60 and SSEA-4, which are characteristic stem cell markers. Downregulation of lamin A/C, HDAC1, HDAC6, Bcl2, cytochrome c, p-FAK, p-ERK, and p-JNK and upregulation of H3K4me3 and p-p38 were confirmed in the generated colonies, indicating reprogramming of cells. This protocol increases the possibility of successfully reprogramming somatic cells into induced pluripotent stem cells (iPSCs), thereby overcoming the difficulties in iPSC generation such as genetic mutations, carcinogenesis, and undetermined risk factors.</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+          <t>The iPSC line was generated from human dermal fibroblasts using Sendai viruses carrying reprogramming factors c-MYC, SOX2, KLF4, and OCT4 under a feeder-free culture system.</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>In this study, we have established human induced pluripotent stem cell (hiPSC) line, NIMHi010-A of a 42-year-old healthy donor. The iPSC line was generated from human dermal fibroblasts using Sendai viruses carrying reprogramming factors c-MYC, SOX2, KLF4, and OCT4 under a feeder-free culture system. The generated hiPSC line expressed typical pluripotency markers, displayed a normal karyotype, and demonstrated the potential to differentiate into the three germ layers. This hiPSC line will serve as a healthy control model for physiological processes and drug screening of Asian origin from Indian population.</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Classic OSKM Sendai virus reprogramming of human dermal fibroblasts to iPSC. Evidence directly confirms iPSC generation. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1071,82 +1260,114 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>34331868</t>
+          <t>37171961</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Enhancer decommissioning imposes an epigenetic barrier to sensory hair cell regeneration.</t>
+          <t>Epistatic genetic interactions between Insm1 and Ikzf2 during cochlear outer hair cell development.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>perinatal supporting cells</t>
+          <t>outer hair cell</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>hair cell</t>
+          <t>inner hair cell</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Notch signaling blockade</t>
+          <t>Insm1 deletion</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>knockdown</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>cell_state_modulation</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/37171961</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>OHCs transdifferentiate into IHCs in Insm1 mutants</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>The cochlea harbors two types of sound receptors, outer hair cells (OHCs) and inner hair cells (IHCs). OHCs transdifferentiate into IHCs in Insm1 mutants, and OHCs in Ikzf2-deficient mice are dysfunctional and maintain partial IHC gene expression. Insm1 potentially acts as a positive but indirect regulator of Ikzf2, considering that Insm1 is expressed earlier than Ikzf2 and primarily functions as a transcriptional repressor. However, direct evidence of this possibility is lacking. Here, we report the following results: first, Insm1 overexpression in IHCs leads to ectopic Ikzf2 expression. Second, Ikzf2 expression is repressed in Insm1-deficient OHCs, and forced expression of Ikzf2 mitigates the OHC abnormality in Insm1 mutants. Last, dual ablation of Insm1 and Ikzf2 generates a similar OHC phenotype as does Insm1 ablation alone. Collectively, our findings reveal the transcriptional cascade from Insm1 to Ikzf2, which should facilitate future investigation of the molecular mechanisms underlying OHC development and regeneration.</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
           <t>other</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>abstract</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/34331868</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Blocking Notch signaling during the perinatal period of plasticity rapidly eliminates epigenetic silencing and allows supporting cells to transdifferentiate into hair cells.</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Adult mammalian tissues such as heart, brain, retina, and the sensory structures of the inner ear do not effectively regenerate, although a latent capacity for regeneration exists at embryonic and perinatal times. We explored the epigenetic basis for this latent regenerative potential in the mouse inner ear and its rapid loss during maturation. In perinatal supporting cells, whose fate is maintained by Notch-mediated lateral inhibition, the hair cell enhancer network is epigenetically primed (H3K4me1) but silenced (active H3K27 de-acetylation and trimethylation). Blocking Notch signaling during the perinatal period of plasticity rapidly eliminates epigenetic silencing and allows supporting cells to transdifferentiate into hair cells. Importantly, H3K4me1 priming of the hair cell enhancers in supporting cells is removed during the first post-natal week, coinciding with the loss of transdifferentiation potential. We hypothesize that enhancer decommissioning during cochlear maturation contributes to the failure of hair cell regeneration in the mature organ of Corti.</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Insm1 deletion drives OHC→IHC transdifferentiation; valid loss-of-function reprogramming recipe. Factor notation 'Insm1 deletion' should be standardized (e.g., INSM1 loss-of-function). Evidence is direct.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1199,37 +1420,69 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>directed_differentiation</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/34209429</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>The differentiation of euploid and isogenic trisomic iPSCs into neural precursor cells, Eu-NPCs and T21-NPCs respectively, was obtained by the dual-SMAD inhibition protocol [9] in monolayer cultures (see Matherial and Methods).</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>The presence of mitochondrial alterations in Down syndrome suggests that it might affect neuronal differentiation. We established a model of trisomic iPSCs, differentiating into neural precursor cells (NPCs) to monitor the occurrence of differentiation defects and mitochondrial dysfunction. Isogenic trisomic and euploid iPSCs were differentiated into NPCs in monolayer cultures using the dual-SMAD inhibition protocol. Expression of pluripotency and neural differentiation genes was assessed by qRT-PCR and immunofluorescence. Meta-analysis of expression data was performed on iPSCs. Mitochondrial Ca&lt;sup&gt;2+&lt;/sup&gt;, reactive oxygen species (ROS) and ATP production were investigated using fluorescent probes. Oxygen consumption rate (OCR) was determined by Seahorse Analyzer. NPCs at day 7 of induction uniformly expressed the differentiation markers PAX6, SOX2 and NESTIN but not the stemness marker OCT4. At day 21, trisomic NPCs expressed higher levels of typical glial differentiation genes. Expression profiles indicated that mitochondrial genes were dysregulated in trisomic iPSCs. Trisomic NPCs showed altered mitochondrial Ca&lt;sup&gt;2+&lt;/sup&gt;, reduced OCR and ATP synthesis, and elevated ROS production. Human trisomic iPSCs can be rapidly and efficiently differentiated into NPC monolayers. The trisomic NPCs obtained exhibit greater glial-like differentiation potential than their euploid counterparts and manifest mitochondrial dysfunction as early as day 7 of neuronal differentiation.</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>factors_unspecified</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Dual-SMAD inhibition is a well-validated iPSC→NPC differentiation protocol. However 'dual-SMAD inhibition' is vague — specific inhibitors (SB431542 + LDN193189/dorsomorphin) should be named.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1237,27 +1490,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>38133504</t>
+          <t>34324176</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Retinal Ganglion Cell Fate Induction by Ngn-Family Transcription Factors.</t>
+          <t>Isolation and Neuronal Reprogramming of Mouse Embryonic Fibroblasts.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>late-stage retinal progenitor cell (RPC)</t>
+          <t>mouse embryonic fibroblast (MEF)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>retinal ganglion cell</t>
+          <t>neuron</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ngn1, NGN2, NGN3</t>
+          <t>ASCL1, BRN2, Myt1l</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1282,37 +1535,65 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/38133504</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>In vivo, Ngn-TFs reprogrammed the differentiation-competent state of late-stage RPCs to generate RGCs.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/34324176</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Retinal ganglion cells (RGCs) are the projection neurons of the retina. Loss of RGCs is the cellular basis for vision loss in patients with glaucoma. Finding ways to regenerate RGCs will aid in the development of regenerative therapies for patients with glaucoma. The aim of this study was to examine the ability of Ngn-family transcription factors (TFs) to induce RGC regeneration through reprogramming in vitro and in vivo. In vitro, lentiviruses were used to deliver Ngn-TFs into mouse embryonic fibroblasts (MEFs). In vivo, mouse pup retina electroporation was used to deliver Ngn-TFs into late-stage retinal progenitor cells (RPCs). Immunofluorescence staining and RNA sequencing were used to examine cell fate reprogramming; patch-clamp recording was used to examine neuronal electrophysiologic functions. In vitro, all three Ngn-TFs, Ngn1, Ngn2, and Ngn3, were able to work alone to reprogram MEFs into RGC-like neurons that resembled RGCs at the transcriptome level, exhibited typical neuronal membrane electrophysiologic properties, and formed functional synaptic communications with retinal neurons. In vivo, Ngn-TFs reprogrammed the differentiation-competent state of late-stage RPCs to generate RGCs. Ngn-TFs are effective in inducing an RGC-like fate both in vitro and in vivo and might be explored further in the future for glaucoma translational applications.</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+          <t>Here we provide a detailed protocol for the isolation of MEFs devoid of neural tissue and their direct reprogramming into functional neurons by overexpression of neuronal reprogramming factors (Ascl1, Brn2, and Myt1l) using lentiviral vectors.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Forced expression of specific neuronal transcription factors in mouse embryonic fibroblasts (MEFs) can lead to their direct conversion into functional neurons. Direct neuronal reprogramming has become a powerful tool to characterize individual factors and molecular mechanisms involved in forced and normal neurogenesis and to generate neuronal cell types for in vitro studies. Here we provide a detailed protocol for the isolation of MEFs devoid of neural tissue and their direct reprogramming into functional neurons by overexpression of neuronal reprogramming factors (Ascl1, Brn2, and Myt1l) using lentiviral vectors. This method enables quick and efficient generation of mouse neurons in vitro for versatile functional and mechanistic characterization.</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>BAM (ASCL1, BRN2, MYT1L) MEF→neuron direct reprogramming is a classic validated recipe. Evidence describes protocol directly. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1320,17 +1601,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21445094</t>
+          <t>22415842</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rational optimization of reprogramming culture conditions for the generation of induced pluripotent stem cells with ultra-high efficiency and fast kinetics.</t>
+          <t>Using microRNAs to enhance the generation of induced pluripotent stem cells.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>somatic cell</t>
+          <t>mouse embryonic fibroblast (MEF)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1340,12 +1621,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>OCT4, SOX2, KLF4</t>
+          <t>defined factors, microRNA mimics</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>TF, TF, TF</t>
+          <t>TF, miRNA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1365,37 +1646,69 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>classical_reprogramming</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/21445094</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>First, we developed an optimized defined medium, iCD1, which allows Oct4/Sox2/Klf4 (OSK)-mediated reprogramming to achieve ultra-high efficiency (~10% at day 8).</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/22415842</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>The ectopic expression of several transcription factors can restore embryonic cell fate to cultured somatic cells and generate induced pluripotent stem cells (iPSCs), revealing a previously unknown pathway to pluripotency. However, this technology is currently limited by low efficiency, slow kinetics and multi-factorial requirement. Here we show that reprogramming can be improved and dramatically accelerated by optimizing culture conditions. First, we developed an optimized defined medium, iCD1, which allows Oct4/Sox2/Klf4 (OSK)-mediated reprogramming to achieve ultra-high efficiency (~10% at day 8). We also found that this optimized condition renders both Sox2 and Klf4 dispensable, although the elimination of these two factors leads to lower efficiency and slower kinetics. Our studies define a shortened route, both in timing and factor requirement, toward pluripotency. This new paradigm not only provides a rationale to further improve iPSC generation but also simplifies the conceptual understanding of reprogramming by defined factors.</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
+          <t>Mouse embryonic fibroblasts (MEFs) are isolated from E13.5 mouse embryos and seeded for reprogramming by defined factors.</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Somatic cells reprogrammed to acquire an ES-like state are termed iPS cells. In this unit, a protocol to use microRNAs as enhancers to increase the reprogramming efficiency is described. Mouse embryonic fibroblasts (MEFs) are isolated from E13.5 mouse embryos and seeded for reprogramming by defined factors. microRNA mimics are transfected into MEFs at two time points during this process to enhance the overall reprogramming efficiency. Two standard protocols for characterization of these miR-iPSCs, embryoid body formation and teratoma formation, are also provided. By using this method, the investigators can obtain a significantly higher number of bona-fide iPSC colonies and miR-iPSCs can be derived at a faster rate than with non-treated cells.</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>factors_unspecified</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Factors 'defined factors, microRNA mimics' are too vague — base OSKM TFs are not listed, only that miRNAs enhance reprogramming. Evidence sentence describes MEF isolation only, not reprogramming outcome. Specific factors must be named.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1403,12 +1716,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>37315521</t>
+          <t>27835665</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MEF2C/p300-mediated epigenetic remodeling promotes the maturation of induced cardiomyocytes.</t>
+          <t>Cytokine-Like 1 Regulates Cardiac Fibrosis via Modulation of TGF-β Signaling.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1418,17 +1731,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>cardiomyocyte</t>
+          <t>myofibroblast</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MEF2C, GATA4, TBX5</t>
+          <t>Cytl1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>TF, TF, TF</t>
+          <t>cytokine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1448,37 +1761,69 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/37315521</t>
-        </is>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Cardiac transcription factors (TFs) directly reprogram fibroblasts into induced cardiomyocytes (iCMs), where MEF2C acts as a pioneer factor with GATA4 and TBX5 (GT).</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/27835665</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Cardiac transcription factors (TFs) directly reprogram fibroblasts into induced cardiomyocytes (iCMs), where MEF2C acts as a pioneer factor with GATA4 and TBX5 (GT). However, the generation of functional and mature iCMs is inefficient, and the molecular mechanisms underlying this process remain largely unknown. Here, we found that the overexpression of transcriptionally activated MEF2C via fusion of the powerful MYOD transactivation domain combined with GT increased the generation of beating iCMs by 30-fold. Activated MEF2C with GT generated iCMs that were transcriptionally, structurally, and functionally more mature than those generated by native MEF2C with GT. Mechanistically, activated MEF2C recruited p300 and multiple cardiogenic TFs to cardiac loci to induce chromatin remodeling. In contrast, p300 inhibition suppressed cardiac gene expression, inhibited iCM maturation, and decreased the beating iCM numbers. Splicing isoforms of MEF2C with similar transcriptional activities did not promote functional iCM generation. Thus, MEF2C/p300-mediated epigenetic remodeling promotes iCM maturation.</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
+          <t>Adenovirus-mediated overexpression of cytl1 was sufficient to induce these two critical CF-related processes in vitro, which were completely abrogated by co-treatment with SB-431542, an antagonist of TGF-β receptor 1.</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Cytokine-like 1 (Cytl1) is a secreted protein that is involved in diverse biological processes. A comparative modeling study indicated that Cytl1 is structurally and functionally similar to monocyte chemoattractant protein 1 (MCP-1). As MCP-1 plays an important role in cardiac fibrosis (CF) and heart failure (HF), we investigated the role of Cytl1 in a mouse model of CF and HF. Cytl1 was upregulated in the failing mouse heart. Pressure overload-induced CF was significantly attenuated in cytl1 knock-out (KO) mice compared to that from wild-type (WT) mice. By contrast, adeno-associated virus (AAV)-mediated overexpression of cytl1 alone led to the development of CF in vivo. The endothelial-mesenchymal transition (EndMT) and the transdifferentiation of fibroblasts (FBs) to myofibroblasts (MFBs) have been suggested to contribute considerably to CF. Adenovirus-mediated overexpression of cytl1 was sufficient to induce these two critical CF-related processes in vitro, which were completely abrogated by co-treatment with SB-431542, an antagonist of TGF-β receptor 1. Cytl1 induced the expression of TGF-β2 both in vivo and in vitro. Antagonizing the receptor for MCP-1, C-C chemokine receptor type 2 (CCR2), with CAS 445479-97-0 did not block the pro-fibrotic activity of Cytl1 in vitro. Collectively, our data suggest that Cytl1 plays an essential role in CF likely through activating the TGF-β-SMAD signaling pathway. Although the receptor for Cyt1l remains to be identified, Cytl1 provides a novel platform for the development of anti-CF therapies.</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>evidence_weak</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Cytl1 overexpression inducing myofibroblast-related processes is biologically plausible (TGF-beta pathway-dependent). Evidence sentence is indirect — it describes abrogation by SB-431542, not a direct conversion outcome statement.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1486,32 +1831,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21390254</t>
+          <t>21615676</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Efficient feeder-free episomal reprogramming with small molecules.</t>
+          <t>Rapamycin and other longevity-promoting compounds enhance the generation of mouse induced pluripotent stem cells.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>fibroblast</t>
+          <t>somatic cell</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>footprint-free human iPSC</t>
+          <t>induced pluripotent stem cell (iPSC)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PD0325901, CHIR99021, A83-01, HA-100, human leukemia inhibitory factor</t>
+          <t>rapamycin, PP242, resveratrol, fisetin, spermidine, LY294002, curcumin</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>small_molecule, small_molecule, small_molecule, small_molecule, cytokine</t>
+          <t>small_molecule, small_molecule, small_molecule, small_molecule, small_molecule, small_molecule, small_molecule</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1531,37 +1876,69 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>classical_reprogramming</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/21390254</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>These improvements enabled the routine derivation of footprint-free human iPSCs from skin fibroblasts, adipose tissue-derived cells and cord blood cells.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/21615676</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Genetic reprogramming of human somatic cells to induced pluripotent stem cells (iPSCs) could offer replenishable cell sources for transplantation therapies. To fulfill their promises, human iPSCs will ideally be free of exogenous DNA (footprint-free), and be derived and cultured in chemically defined media free of feeder cells. Currently, methods are available to enable efficient derivation of footprint-free human iPSCs. However, each of these methods has its limitations. We have previously derived footprint-free human iPSCs by employing episomal vectors for transgene delivery, but the process was inefficient and required feeder cells. Here, we have greatly improved the episomal reprogramming efficiency using a cocktail containing MEK inhibitor PD0325901, GSK3β inhibitor CHIR99021, TGF-β/Activin/Nodal receptor inhibitor A-83-01, ROCK inhibitor HA-100 and human leukemia inhibitory factor. Moreover, we have successfully established a feeder-free reprogramming condition using chemically defined medium with bFGF and N2B27 supplements and chemically defined human ESC medium mTeSR1 for the derivation of footprint-free human iPSCs. These improvements enabled the routine derivation of footprint-free human iPSCs from skin fibroblasts, adipose tissue-derived cells and cord blood cells. This technology will likely be valuable for the production of clinical-grade human iPSCs.</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
+          <t>Here we report that inhibition of the mammalian target of rapamycin (mTOR) pathway by rapamycin or PP242 enhances the efficiency of reprogramming to induced pluripotent stem cells (iPSCs).</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Reprogramming of somatic cells to a pluripotent state was first accomplished using retroviral vectors for transient expression of pluripotency-associated transcription factors. This seminal work was followed by numerous studies reporting alternative (noninsertional) reprogramming methods and various conditions to improve the efficiency of reprogramming. These studies have contributed little to an understanding of global mechanisms underlying reprogramming efficiency. Here we report that inhibition of the mammalian target of rapamycin (mTOR) pathway by rapamycin or PP242 enhances the efficiency of reprogramming to induced pluripotent stem cells (iPSCs). Inhibition of the insulin/IGF-1 signaling pathway, which like mTOR is involved in control of longevity, also enhances reprogramming efficiency. In addition, the small molecules used to inhibit these pathways also significantly improved longevity in Drosophila melanogaster. We further tested the potential effects of six other longevity-promoting compounds on iPSC induction, including two sirtuin activators (resveratrol and fisetin), an autophagy inducer (spermidine), a PI3K (phosphoinositide 3-kinase) inhibitor (LY294002), an antioxidant (curcumin), and an activating adenosine monophosphate-activated protein kinase activator (metformin). With the exception of metformin, all of these chemicals promoted somatic cell reprogramming, though to different extents. Our results show that the controllers of somatic cell reprogramming and organismal lifespan share some common regulatory pathways, which suggests a new approach for studying aging and longevity based on the regulation of cellular reprogramming.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>factors_unspecified;wrong_factor</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Rapamycin, PP242, resveratrol etc. are reprogramming efficiency enhancers, not primary reprogramming factors. Base OSKM factors are missing. Evidence sentence confirms mTOR inhibition boosts iPSC efficiency but primary TFs are absent from factors field.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1569,17 +1946,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>34206684</t>
+          <t>24319660</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Inhibition of CREB-CBP Signaling Improves Fibroblast Plasticity for Direct Cardiac Reprogramming.</t>
+          <t>Direct reprogramming of human fibroblasts toward a cardiomyocyte-like state.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>mouse neonatal tail-tip fibroblast</t>
+          <t>human fibroblast</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1589,12 +1966,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>GATA4, MEF2C, TBX5</t>
+          <t>GATA4, MEF2C, TBX5, ESRRG, MESP1, MYOCD, ZFPM2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>TF, TF, TF</t>
+          <t>TF, TF, TF, TF, TF, TF, TF</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1614,37 +1991,65 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/34206684</t>
-        </is>
-      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Although proper expression of reprogramming factors (e.g., GMT: Gata4, Mef2c, and Tbx5) in fibroblasts is essential to epigenetic reprogramming, the quality or status of fibroblasts prior to the induction of reprogramming is an important factor for successful and efficient reprogramming.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/24319660</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Direct cardiac reprogramming of fibroblasts into induced cardiomyocytes (iCMs) is a promising approach but remains a challenge in heart regeneration. Efforts have focused on improving the efficiency by understanding fundamental mechanisms. One major challenge is that the plasticity of cultured fibroblast varies batch to batch with unknown mechanisms. Here, we noticed a portion of in vitro cultured fibroblasts have been activated to differentiate into myofibroblasts, marked by the expression of αSMA, even in primary cell cultures. Both forskolin, which increases cAMP levels, and TGFβ inhibitor SB431542 can efficiently suppress myofibroblast differentiation of cultured fibroblasts. However, SB431542 improved but forskolin blocked iCM reprogramming of fibroblasts that were infected with retroviruses of Gata4, Mef2c, and Tbx5 (GMT). Moreover, inhibitors of cAMP downstream signaling pathways, PKA or CREB-CBP, significantly improved the efficiency of reprogramming. Consistently, inhibition of p38/MAPK, another upstream regulator of CREB-CBP, also improved reprogramming efficiency. We then investigated if inhibition of these signaling pathways in primary cultured fibroblasts could improve their plasticity for reprogramming and found that preconditioning of cultured fibroblasts with CREB-CBP inhibitor significantly improved the cellular plasticity of fibroblasts to be reprogrammed, yielding ~2-fold more iCMs than untreated control cells. In conclusion, suppression of CREB-CBP signaling improves fibroblast plasticity for direct cardiac reprogramming.</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+          <t>Importantly, primary HDFs and HCFs that were infected with a lentivirus encoding αMHC-mCherry and 7F retrovirus could also be reprogrammed to express α-actinin and cTNT and assemble sarcomeres, although with lower frequency (1%–4%; Figures 2B, 2C, S3A, and S3B).</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Direct reprogramming of adult somatic cells into alternative cell types has been shown for several lineages. We previously showed that GATA4, MEF2C, and TBX5 (GMT) directly reprogrammed nonmyocyte mouse heart cells into induced cardiomyocyte-like cells (iCMs) in vitro and in vivo. However, GMT alone appears insufficient in human fibroblasts, at least in vitro. Here, we show that GMT plus ESRRG and MESP1 induced global cardiac gene-expression and phenotypic shifts in human fibroblasts derived from embryonic stem cells, fetal heart, and neonatal skin. Adding Myocardin and ZFPM2 enhanced reprogramming, including sarcomere formation, calcium transients, and action potentials, although the efficiency remained low. Human iCM reprogramming was epigenetically stable. Furthermore, we found that transforming growth factor β signaling was important for, and improved the efficiency of, human iCM reprogramming. These findings demonstrate that human fibroblasts can be directly reprogrammed toward the cardiac lineage, and lay the foundation for future refinements in vitro and in vivo.</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>7F human cardiac reprogramming (GMT+ESRRG+MESP1+MYOCD+ZFPM2) of HDF/HCF — validated Wada et al. protocol. Evidence confirms sarcomere assembly in primary human fibroblasts. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1652,32 +2057,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>41163067</t>
+          <t>39068473</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chemical direct conversion of human fibroblasts to mesenchymal stem cells that can alleviate inflammation in vivo.</t>
+          <t>Decoding single-cell molecular mechanisms in astrocyte-to-iN reprogramming via Ngn2- and Pax6-mediated direct lineage switching.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>human fibroblast</t>
+          <t>primary postnatal cortical astrocyte</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>mesenchymal stem cell</t>
+          <t>induced neuron (iN)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ALK5iII, KU-60019, Fasudil</t>
+          <t>NGN2, PAX6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>small_molecule, small_molecule, small_molecule</t>
+          <t>TF, TF</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1697,37 +2102,65 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/41163067</t>
-        </is>
-      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Based on these findings, the HDFs/AKF were brought to further detailed analyses as representative chemical compounds-driven directly converted MSCs (cdMSCs).</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/39068473</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Mesenchymal stem cell (MSC) transplantation may significantly benefit patients with some inflammatory diseases. However, invasive procedures are required to collect autologous MSCs from patients, while in vitro expansion of MSCs may spoil their stemness. In this study, we aimed to induce MSC-like phenotypes in human dermal fibroblasts (HDFs). HDFs were cultured with some chemical compounds. The resultant cells were examined for their gene expression and multi-differentiation abilities in vitro. Anti-inflammatory functions in vivo were tested using two types of disease models in mice. Exosomes derived from the cells were also characterized. A combination of a TGF-β receptor inhibitor, a ROCK inhibitor, and an ATM inhibitor provoked HDFs to strongly express MSC markers. The chemical compound-driven directly converted MSCs (cdMSCs) had multilineage differentiation potentials to osteogenic, chondrogenic, and adipogenic lineages in vitro. The genes related to TGF-β, MAPK, Hedgehog and WNT signaling pathways were remarkably changed in expression levels, while CpG DNA methylation statuses were also altered, during the cell type transition. The cdMSCs ameliorated both acute and chronic inflammatory diseases after transplantation into murine models of LPS-induced lung injury and autoimmune arthritis. The cdMSCs secreted exosomes that promoted polarization of M0 macrophages to M2 phenotype while suppressing M1 macrophage induction in vitro. The three compounds successfully converted HDFs into MSC-like cells with high anti-inflammatory activities, which would be useful in regenerative medicine for inflammatory disease.</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+          <t>We utilized primary postnatal cortical astrocytes for reprogramming induced neurons (iNs) through the viral-mediated overexpression of the transcription factors Ngn2 and Pax6 (NP).</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>The limited regenerative capacity of damaged neurons in adult mammals severely restricts neural repair. Although stem cell transplantation is promising, its clinical application remains challenging. Direct reprogramming, which utilizes cell plasticity to regenerate neurons, is an emerging alternative approach. We utilized primary postnatal cortical astrocytes for reprogramming induced neurons (iNs) through the viral-mediated overexpression of the transcription factors Ngn2 and Pax6 (NP). Fluorescence-activated cell sorting (FACS) was used to enrich successfully transfected cells, followed by single-cell RNA sequencing (scRNA-seq) using the 10 × Genomics platform for comprehensive transcriptomic analysis. The scRNA-seq revealed that NP overexpression led to the differentiation of astrocytes into iNs, with percentages of 36% and 39.3% on days 4 and 7 posttransduction, respectively. CytoTRACE predicted the developmental sequence, identifying astrocytes as the reprogramming starting point. Trajectory analysis depicted the dynamic changes in gene expression during the astrocyte-to-iN transition. This study elucidates the molecular dynamics underlying astrocyte reprogramming into iNs, revealing key genes and pathways involved in this process. Our research contributes novel insights into the molecular mechanisms of NP-mediated reprogramming, suggesting avenues for optimizing the efficiency of the reprogramming process.</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>NGN2+PAX6 reprogramming of cortical astrocytes to induced neurons is a documented protocol. Evidence directly describes the viral overexpression reprogramming. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1735,32 +2168,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>28771465</t>
+          <t>27243814</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EBV epigenetically suppresses the B cell-to-plasma cell differentiation pathway while establishing long-term latency.</t>
+          <t>Generation of Functional Beta-Like Cells from Human Exocrine Pancreas.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>mature human B cell</t>
+          <t>human exocrine pancreas</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>lymphoblastoid cell line (LCL)</t>
+          <t>insulin-producing cell (β-cell)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>EBNA3A, EBNA3C</t>
+          <t>PDX1, NGN3, MafA, Pax4, growth factors, ARX suppression</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>TF, TF</t>
+          <t>TF, TF, TF, TF, cytokine, knockdown</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1780,37 +2213,65 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/28771465</t>
-        </is>
-      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Consistent with the binding of EBNA3A and/or EBNA3C leading to irreversible epigenetic changes, cells become committed to a B-blast fate &lt;12 days post-infection and are unable to de-repress p18INK4c or BLIMP-1-in either newly infected cells or conditional LCLs-by inactivating EBNA3A and EBNA3C.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/27243814</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Mature human B cells infected by Epstein-Barr virus (EBV) become activated, grow, and proliferate. If the cells are infected ex vivo, they are transformed into continuously proliferating lymphoblastoid cell lines (LCLs) that carry EBV DNA as extra-chromosomal episomes, express 9 latency-associated EBV proteins, and phenotypically resemble antigen-activated B-blasts. In vivo similar B-blasts can differentiate to become memory B cells (MBC), in which EBV persistence is established. Three related latency-associated viral proteins EBNA3A, EBNA3B, and EBNA3C are transcription factors that regulate a multitude of cellular genes. EBNA3B is not necessary to establish LCLs, but EBNA3A and EBNA3C are required to sustain proliferation, in part, by repressing the expression of tumour suppressor genes. Here we show, using EBV-recombinants in which both EBNA3A and EBNA3C can be conditionally inactivated or using virus completely lacking the EBNA3 gene locus, that-after a phase of rapid proliferation-infected primary B cells express elevated levels of factors associated with plasma cell (PC) differentiation. These include the cyclin-dependent kinase inhibitor (CDKI) p18INK4c, the master transcriptional regulator of PC differentiation B lymphocyte-induced maturation protein-1 (BLIMP-1), and the cell surface antigens CD38 and CD138/Syndecan-1. Chromatin immunoprecipitation sequencing (ChIP-seq) and chromatin immunoprecipitation quantitative PCR (ChIP-qPCR) indicate that in LCLs inhibition of CDKN2C (p18INK4c) and PRDM1 (BLIMP-1) transcription results from direct binding of EBNA3A and EBNA3C to regulatory elements at these loci, producing stable reprogramming. Consistent with the binding of EBNA3A and/or EBNA3C leading to irreversible epigenetic changes, cells become committed to a B-blast fate &lt;12 days post-infection and are unable to de-repress p18INK4c or BLIMP-1-in either newly infected cells or conditional LCLs-by inactivating EBNA3A and EBNA3C. In vitro, about 20 days after infection with EBV lacking functional EBNA3A and EBNA3C, cells develop a PC-like phenotype. Together, these data suggest that EBNA3A and EBNA3C have evolved to prevent differentiation to PCs after infection by EBV, thus favouring long-term latency in MBC and asymptomatic persistence.</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+          <t>We show here that overexpression of exogenous Pax4 in combination with suppression of the endogenous transcription factor ARX considerably enhances the production of functional insulin-secreting β-like cells with concomitant suppression of α-cells.</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Transcription factor mediated lineage reprogramming of human pancreatic exocrine tissue could conceivably provide an unlimited supply of islets for transplantation in the treatment of diabetes. Exocrine tissue can be efficiently reprogrammed to islet-like cells using a cocktail of transcription factors: Pdx1, Ngn3, MafA and Pax4 in combination with growth factors. We show here that overexpression of exogenous Pax4 in combination with suppression of the endogenous transcription factor ARX considerably enhances the production of functional insulin-secreting β-like cells with concomitant suppression of α-cells. The efficiency was further increased by culture on laminin-coated plates in media containing low glucose concentrations. Immunocytochemistry revealed that reprogrammed cultures were composed of ~45% islet-like clusters comprising &gt;80% monohormonal insulin+ cells. The resultant β-like cells expressed insulin protein levels at ~15-30% of that in adult human islets, efficiently processed proinsulin and packaged insulin into secretory granules, exhibited glucose responsive insulin secretion, and had an immediate and prolonged effect in normalising blood glucose levels upon transplantation into diabetic mice. We estimate that approximately 3 billion of these cells would have an immediate therapeutic effect following engraftment in type 1 diabetes patients and that one pancreas would provide sufficient tissue for numerous transplants.</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>PDX1/NGN3/MafA/Pax4 + ARX suppression for human exocrine pancreas→β-cell conversion is valid. Evidence directly demonstrates insulin-secreting β-like cell production. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1818,17 +2279,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24753644</t>
+          <t>29743891</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cardiomyocyte marker expression in mouse embryonic fibroblasts by cell-free cardiomyocyte extract and epigenetic manipulation.</t>
+          <t>A Loss of Function Screen of Epigenetic Modifiers and Splicing Factors during Early Stage of Cardiac Reprogramming.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>mouse embryonic fibroblast (MEF)</t>
+          <t>cardiac fibroblast</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1838,12 +2299,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>cardiomyocyte extract, 5-aza-dC, TSA</t>
+          <t>MEF2C, GATA4, TBX5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>other, small_molecule, small_molecule</t>
+          <t>TF, TF, TF</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1863,37 +2324,65 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/24753644</t>
-        </is>
-      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Immunofluorescence detected the existence of cardiomyocyte markers in the fibroblasts that were exposed to chromatin-modifying agents and permeabilized in the presence of the cardiac extract.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/29743891</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>The regenerative capacity of the mammalian heart is quite limited. Recent reports have focused on reprogramming mesenchymal stem cells into cardiomyocytes. We investigated whether fibroblasts could transdifferentiate into myocardium. Mouse embryonic fibroblasts were treated with Trichostatin A (TSA) and 5-Aza-2-Deoxycytidine (5-aza-dC). The treated cells were permeabilized with streptolysin O and exposed to the mouse cardiomyocyte extract and cultured for 1, 10, and 21 days. Cardiomyocyte markers were detected by immunohistochemistry. Alkaline phosphatase activity and OCT4 were also detected in cells treated by chromatin-modifying agents. The cells exposed to a combination of 5-aza-dC and TSA and permeabilized in the presence of the cardiomyocyte extract showed morphological changes. The cells were unable to express cardiomyocyte markers after 24 h. Immunocytochemical assays showed a notable degree of myosin heavy chain and α-actinin expressions after 10 days. The expression of the natriuretic factor and troponin T occurred after 21 days in these cells. The cells exposed to chromatin-modifying agents also expressed cardiomyocyte markers; however, the proportion of reprogrammed cells was clearly smaller than that in the cultures exposed to 5-aza-dC , TSA, and extract. It seems that the fibroblasts were able to eliminate the previous epigenetic markers and form new ones according to the factors existing in the extract. Since no beating was observed, at least up to 21 days, the cells may need an appropriate extracellular matrix for their function.</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+          <t>We infected cardiac fibroblasts isolated using explant method (ExCFs, [3]) from αMHC-GFP transgenic pups at P1.5 with shRNA pools, subsequently transduced them with the polycistronic reprogramming vector expressing Mef2c, Gata4, and Tbx5 (MGT in short).</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Direct reprogramming of cardiac fibroblasts (CFs) to induced cardiomyocytes (iCMs) is a newly emerged promising approach for cardiac regeneration, disease modeling, and drug discovery. However, its potential has been drastically limited due to the low reprogramming efficiency and largely unknown underlying molecular mechanisms. We have previously screened and identified epigenetic factors related to histone modification during iCM reprogramming. Here, we used shRNAs targeting an additional battery of epigenetic factors involved in chromatin remodeling and RNA splicing factors to further identify inhibitors and facilitators of direct cardiac reprogramming. Knockdown of RNA splicing factors Sf3a1 or Sf3b1 significantly reduced the percentage and total number of cardiac marker positive iCMs accompanied with generally repressed gene expression. Removal of another RNA splicing factor Zrsr2 promoted the acquisition of CM molecular features in CFs and mouse embryonic fibroblasts (MEFs) at both protein and mRNA levels. Moreover, a consistent increase of reprogramming efficiency was observed in CFs and MEFs treated with shRNAs targeting Bcor (component of BCOR complex superfamily) or Stag2 (component of cohesin complex). Our work thus reveals several additional epigenetic and splicing factors that are either inhibitory to or required for iCM reprogramming and highlights the importance of epigenetic regulation and RNA splicing process during cell fate conversion.</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>GMT (MEF2C, GATA4, TBX5) cardiac fibroblast→iCM reprogramming — canonical Srivastava lab recipe. Evidence describes shRNA screen with polycistronic GMT vector in cardiac fibroblasts. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1901,32 +2390,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>26503743</t>
+          <t>28844127</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Generation of integration-free induced hepatocyte-like cells from mouse fibroblasts.</t>
+          <t>Direct Conversion of Human Umbilical Cord Blood into Induced Neural Stem Cells with SOX2 and HMGA2.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>mouse embryonic fibroblast (MEF)</t>
+          <t>human umbilical cord blood CD34+ cell</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>induced hepatocyte (iHep)</t>
+          <t>induced neural stem cell (iNSC)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GATA4, HNF1A, FOXA3</t>
+          <t>SOX2, HMGA2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>TF, TF, TF</t>
+          <t>TF, TF</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1946,37 +2435,65 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/26503743</t>
-        </is>
-      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>We next transfected the MEFs with three distinct combinations of TFs, Hnf4a/Foxa1 (4a1), Hnf4a/Foxa3 (4a3), and Gata4/Hnf1a/Foxa3 (GHF), which were previously shown to elicit the direct conversion of somatic fibroblasts into iHeps (Fig. 1A)9,10.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/28844127</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>The ability to generate integration-free induced hepatocyte-like cells (iHeps) from somatic fibroblasts has the potential to advance their clinical application. Here, we have generated integration-free, functional, and expandable iHeps from mouse somatic fibroblasts. To elicit this direct conversion, we took advantage of an oriP/EBNA1-based episomal system to deliver a set of transcription factors, Gata4, Hnf1a, and Foxa3, to the fibroblasts. The established iHeps exhibit similar morphology, marker expression, and functional properties to primary hepatocytes. Furthermore, integration-free iHeps prolong the survival of fumarylacetoacetate-hydrolase-deficient (Fah(-/-)) mice after cell transplantation. Our study provides a novel concept for generating functional and expandable iHeps using a non-viral, non-integrating, plasmid-based system that could facilitate their pharmaceutical and biomedical application.</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+          <t>The conversion process was induced by two rounds of transduction of retroviral SOX2 and HMGA2 into hUCB CD34+ cells.</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Recent advances have shown the direct reprogramming of mouse and human fibroblasts into induced neural stem cells (iNSCs) without passing through an intermediate pluripotent state. Thus, direct reprogramming strategy possibly provides a safe and homogeneous cellular platform. However, the applications of iNSCs for regenerative medicine are limited by the restricted availability of cell sources. Human umbilical cord blood (hUCB) cells hold great potential in that immunotyped hUCB units can be immediately obtained from public banks. Moreover, hUCB samples do not require invasive procedures during collection or an extensive culture period prior to reprogramming. We recently reported that somatic cells can be directly converted into iNSCs with high efficiency and a short turnaround time. Here, we describe the detailed method for the generation of iNSCs derived from hUCB (hUCB iNSCs) using the lineage-specific transcription factors SOX2 and HMGA2. The protocol for deriving iNSC-like colonies takes 1∼2 weeks and establishment of homogenous hUCB iNSCs takes additional 2 weeks. Established hUCB iNSCs are clonally expandable and multipotent producing neurons and glia. Our study provides an accessible method for generating hUCB iNSCs, contributing development of &lt;i&gt;in vitro&lt;/i&gt; neuropathological model systems.</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>SOX2+HMGA2 reprogramming of hUCB CD34+ cells to iNSCs is documented. Evidence directly describes two-round retroviral transduction. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1984,32 +2501,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>39689498</t>
+          <t>31265161</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sox17 and Erg synergistically activate endothelial cell fate in reprogramming fibroblasts.</t>
+          <t>Transcription factor Tbx5 promotes cardiomyogenic differentiation of cardiac fibroblasts treated with 5-azacytidine.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>lung fibroblast</t>
+          <t>cardiac fibroblast</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>arterial-like induced-endothelial cell</t>
+          <t>cardiomyocyte</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sox17, Erg</t>
+          <t>TBX5, 5-azacytidine</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>TF, TF</t>
+          <t>TF, small_molecule</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2029,37 +2546,65 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/39689498</t>
-        </is>
-      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Sox17-Erg direct reprogramming is a potent tool for the in vitro and in vivo generation of arterial-like induced-endothelial cells from fibroblasts.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/31265161</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Sox17-Erg direct reprogramming is a potent tool for the in vitro and in vivo generation of arterial-like induced-endothelial cells from fibroblasts. In this study, we illustrate the pioneering roles of both Sox17 and Erg in the endothelial cell reprogramming process and demonstrate that emergent gene expression only occurs when both factors are co-expressed. Bioinformatic analyses and molecular validation reveal both Bach2 and Etv4 as integral mediators of Sox17-Erg reprogramming with different roles in lung and heart fibroblast reprogramming. The generated organ-specific induced endothelial cells express molecular signatures similar to vasculature found in the starting cell's organ of origin and the starting chromatin architecture plays a role in the acquisition of this organ-specific identity. Overall, the Sox17-Erg reprogramming mechanism provides foundational knowledge for the future recapitulation of vascular heterogeneity through direct reprogramming.</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
+          <t>Here, we report that a defined transcription factor Tbx5, promoted cardiac reprogramming in the presence of a chemical inducer 5-azacytidine (5-aza).</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Conversion of cardiac fibroblasts (CFs) into induced cardiomyocytes has recently been demonstrated, represents a potential therapeutic strategy for cardiac repair after myocardial injury. However, current approaches are inefficient. Here, we report that a defined transcription factor Tbx5, promoted cardiac reprogramming in the presence of a chemical inducer 5-azacytidine (5-aza). Morphological changes and cardiac specific genes and proteins expression were determined by immunofluorescence, quantitative real-time polymerase chain reaction, and Western blot analysis. Remarkably, Tbx5 enabled cardiac reprogramming with 5-aza by activating the expression of myocardial transcription-related genes, including cTnT, α-actin, Mef2c and inhibiting the expression of pluripotent genes such as Nanog, Oct4, and Sox2. Moreover, overexpression of Tbx5 upregulated the expression of sarcomere protein cTnT in CFs more efficiently at week 3 compared with 5aza-treated alone (P &lt; 0.05). Conversely, inhibition of Tbx5 attenuated cardiac reprogramming. Furthermore, downregulated Tbx5 decreased wnt3a expression. At the same time, the inhibition effect of Tbx5i on cardiac reprogramming was reversed in vitro when these cells were exposed to Chir99021, a GSK-3 inhibitor. This finding provides new insight into the mechanism of cardiac reprogramming underlying the cardiac reprogramming process and lays the foundation for future clinical applications.</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>TBX5 + 5-azacytidine (DNA demethylation agent) cardiac reprogramming of cardiac fibroblasts. Evidence directly states 'promoted cardiac reprogramming'. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2067,32 +2612,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>35245086</t>
+          <t>21497092</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Single-cell transcriptional profiling informs efficient reprogramming of human somatic cells to cross-presenting dendritic cells.</t>
+          <t>Suppression of Ptf1a activity induces acinar-to-endocrine conversion.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>human embryonic fibroblast</t>
+          <t>pancreatic acinar cell</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>induced type 1 conventional dendritic cell (hiDC1)</t>
+          <t>insulin+ endocrine cell</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PU.1, IRF8, BATF3, IFN-γ, IFN-β, TNF-α</t>
+          <t>Ptf1a suppression</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>TF, TF, TF, cytokine, cytokine, cytokine</t>
+          <t>other</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2112,37 +2657,65 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/35245086</t>
-        </is>
-      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Combining IFN-γ, IFN-β, and TNF-α with constitutive expression of cDC1-inducing transcription factors led to improvement of reprogramming efficiency by 190-fold.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/21497092</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Type 1 conventional dendritic cells (cDC1s) are rare immune cells critical for the induction of antigen-specific cytotoxic CD8&lt;sup&gt;+&lt;/sup&gt; T cells, although the genetic program driving human cDC1 specification remains largely unexplored. We previously identified PU.1, IRF8, and BATF3 transcription factors as sufficient to induce cDC1 fate in mouse fibroblasts, but reprogramming of human somatic cells was limited by low efficiency. Here, we investigated single-cell transcriptional dynamics during human cDC1 reprogramming. Human induced cDC1s (hiDC1s) generated from embryonic fibroblasts gradually acquired a global cDC1 transcriptional profile and expressed antigen presentation signatures, whereas other DC subsets were not induced at the single-cell level during the reprogramming process. We extracted gene modules associated with successful reprogramming and identified inflammatory signaling and the cDC1-inducing transcription factor network as key drivers of the process. Combining IFN-γ, IFN-β, and TNF-α with constitutive expression of cDC1-inducing transcription factors led to improvement of reprogramming efficiency by 190-fold. hiDC1s engulfed dead cells, secreted inflammatory cytokines, and performed antigen cross-presentation, key cDC1 functions. This approach allowed efficient hiDC1 generation from adult fibroblasts and mesenchymal stromal cells. Mechanistically, PU.1 showed dominant and independent chromatin targeting at early phases of reprogramming, recruiting IRF8 and BATF3 to shared binding sites. The cooperative binding at open enhancers and promoters led to silencing of fibroblast genes and activation of a cDC1 program. These findings provide mechanistic insights into human cDC1 specification and reprogramming and represent a platform for generating patient-tailored cDC1s, a long-sought DC subset for vaccination strategies in cancer immunotherapy.</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+          <t>We found that postembryonic antagonism of Ptf1a, a master regulator of pancreatic development and acinar cell fate specification, induced the expression of endocrine genes including insulin in the exocrine compartment.</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Pluripotent embryonic cells become progressively lineage restricted during development in a process that culminates in the differentiation of stable organ-specific cell types that perform specialized functions. Terminally differentiated pancreatic acinar cells do not have the innate capacity to contribute to the endocrine β cell lineage, which is destroyed in individuals with autoimmune diabetes. Some cell types can be reprogrammed using a single factor, whereas other cell types require continuous activity of transcriptional regulators to repress alternate cell fates. Thus, we hypothesized that a transcriptional network continuously maintains the pancreatic acinar cell fate. We found that postembryonic antagonism of Ptf1a, a master regulator of pancreatic development and acinar cell fate specification, induced the expression of endocrine genes including insulin in the exocrine compartment. Using a genetic lineage tracing approach, we show that the induced insulin+ cells are derived from acinar cells. Cellular reprogramming occurred under homeostatic conditions, suggesting that the pancreatic microenvironment is sufficient to promote endocrine differentiation. Thus, severe experimental manipulations may not be required to potentiate pancreatic transdifferentiation. These data indicate that targeted postembryonic disruption of the acinar cell fate can restore the developmental plasticity that is lost during development.</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Ptf1a suppression (loss-of-function) in pancreatic acinar cells inducing endocrine/insulin gene expression. Valid lineage conversion by TF suppression. Evidence is direct. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2150,32 +2723,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>24672757</t>
+          <t>29967604</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Counteracting activities of OCT4 and KLF4 during reprogramming to pluripotency.</t>
+          <t>Hsa-miR-99b/let-7e/miR-125a Cluster Regulates Pathogen Recognition Receptor-Stimulated Suppressive Antigen-Presenting Cells.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>murine somatic cells</t>
+          <t>human blood monocytes (differentiating)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>induced pluripotent stem cell (iPSC)</t>
+          <t>suppressive/tolerogenic antigen-presenting cell</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OCT4, KLF4</t>
+          <t>R848, hsa-miR-99b/let-7e/miR-125a cluster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>TF, TF</t>
+          <t>small_molecule, miRNA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2195,37 +2768,69 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/24672757</t>
-        </is>
-      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Differentiated cells can be reprogrammed into induced pluripotent stem cells (iPSCs) after overexpressing four transcription factors, of which Oct4 is essential.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/29967604</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Differentiated cells can be reprogrammed into induced pluripotent stem cells (iPSCs) after overexpressing four transcription factors, of which Oct4 is essential. To elucidate the role of Oct4 during reprogramming, we investigated the immediate transcriptional response to inducible Oct4 overexpression in various somatic murine cell types using microarray analysis. By downregulating somatic-specific genes, Oct4 induction influenced each transcriptional program in a unique manner. A significant upregulation of pluripotent markers could not be detected. Therefore, OCT4 facilitates reprogramming by interfering with the somatic transcriptional network rather than by directly initiating a pluripotent gene-expression program. Finally, Oct4 overexpression upregulated the gene Mgarp in all the analyzed cell types. Strikingly, Mgarp expression decreases during the first steps of reprogramming due to a KLF4-dependent inhibition. At later stages, OCT4 counteracts the repressive activity of KLF4, thereby enhancing Mgarp expression. We show that this temporal expression pattern is crucial for the efficient generation of iPSCs.</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
+          <t>Recently, we showed that pathogen recognition receptor-mediated pro-inflammatory cytokines reprogram differentiating human blood monocytes &lt;i&gt;in vitro&lt;/i&gt; toward an immunosuppressive phenotype through prolonged activation of signal transducer and activator of transcription (STAT) 3.</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Antigen-presenting cells (APCs) regulate the balance of our immune response toward microbes. Whereas immunogenic APCs boost inflammation and activate lymphocytes, the highly plastic cells can switch into a tolerogenic/suppressive phenotype that dampens and resolves the response. Thereby the initially mediated inflammation seems to prime the switch of APCs while the strength of activation determines the grade of the suppressive phenotype. Recently, we showed that pathogen recognition receptor-mediated pro-inflammatory cytokines reprogram differentiating human blood monocytes &lt;i&gt;in vitro&lt;/i&gt; toward an immunosuppressive phenotype through prolonged activation of signal transducer and activator of transcription (STAT) 3. The TLR7/8 ligand R848 (Resiquimod) triggers the high release of cytokines from GM-CSF/IL-4-treated monocytes. These cytokines subsequently upregulate T cell suppressive factors, such as programmed death-ligand 1 (PD-L1) and indolamin-2,3-dioxygenase (IDO) through cytokine receptor-mediated STAT3 activation. Here, we reveal an essential role for the microRNA (miR, miRNA) hsa-miR-99b/let-7e/miR-125a cluster in stabilizing the suppressive phenotype of R848-stimulated APCs on different levels. On the one hand, the miR cluster boosts R848-stimulated cytokine production through regulation of MAPkinase inhibitor Tribbles pseudokinase 2, thereby enhancing cytokine-stimulated activation of STAT3. One the other hand, the STAT3 inhibitor suppressor of cytokine signaling-1 is targeted by the miR cluster, stabilizing the STAT3-induced expression of immunosuppressive factors PD-L1 and IDO. Finally, hsa-miR-99b/let-7e/miR-125a cluster regulates generation of the suppressive tryptophan (Trp) metabolite kynurenine by targeting the tryptophanyl-tRNA synthetase WARS, the direct competitor of IDO in terms of availability of Trp. In summary, our results reveal the hsa-miR-99b/let-7e/miR-125a cluster as an important player in the concerted combination of mechanisms that stabilizes STAT3 activity and thus regulate R848-stimulated suppressive APCs.</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>evidence_weak</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Evidence sentence says 'recently, we showed' — citing a prior publication as background, not this paper's own direct result. R848 + miR-99b/let-7e/miR-125a for immune cell reprogramming is plausible but needs evidence from this paper's experiments.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2233,32 +2838,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>24672749</t>
+          <t>41173009</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Coordination of engineered factors with TET1/2 promotes early-stage epigenetic modification during somatic cell reprogramming.</t>
+          <t>Activation of canonical Wnt signaling is required for efficient direct reprogramming into human hepatic progenitor cells.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>mouse embryonic fibroblast (MEF)</t>
+          <t>HUVEC (human umbilical vein endothelial cell)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>induced pluripotent stem cell (iPSC)</t>
+          <t>hepatocyte-like cell</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>OCT4, SOX2, NANOG, KLF4</t>
+          <t>FOXA3, HNF1A, HNF6, CHIR99021, BIO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>TF, TF, TF, TF</t>
+          <t>TF, TF, TF, small_molecule, small_molecule</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2278,37 +2883,65 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/24672749</t>
-        </is>
-      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>When wild-type OSNK were introduced into MEFs carrying the Oct4-GFP transgene, we obtained 69 ± 7 GFP-positive colonies from 2.5 × 10^4 transduced MEFs at day 16 (Figure 1D).</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41173009</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Somatic cell reprogramming toward induced pluripotent stem cells (iPSCs) holds great promise in future regenerative medicine. However, the reprogramming process mediated by the traditional defined factors (OSMK) is slow and extremely inefficient. Here, we develop a combination of modified reprogramming factors (OySyNyK) in which the transactivation domain of the Yes-associated protein is fused to defined factors and establish a highly efficient and rapid reprogramming system. We show that the efficiency of OySyNyK-induced iPSCs is up to 100-fold higher than the OSNK and the reprogramming by OySyNyK is very rapid and is initiated in 24 hr. We find that OySyNyK factors significantly increase Tet1 expression at the early stage and interact with Tet1/2 to promote reprogramming. Our studies not only establish a rapid and highly efficient iPSC reprogramming system but also uncover a mechanism by which engineered factors coordinate with TETs to regulate 5hmC-mediated epigenetic control.</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
+          <t>HUVECs infected with retroviruses expressing hiHepPC-inducing factors, such as FOXA3, HNF1A, and HNF6, were cultured with or without each small-molecule compound, and the number of hiHepPC colonies formed by albumin+ (ALB+) cells was counted at 9 and 16 days after retrovirus infection (Figure 1A).</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Direct reprogramming is a technique for elucidating the mechanisms that control cell-fate decisions and holds promise as a therapeutic strategy. We previously showed that a specific combination of three transcription factors (FOXA3, HNF1A, and HNF6) can induce direct reprogramming of human umbilical vein endothelial cells (HUVECs) into human induced hepatic progenitor cells (hiHepPCs). However, low reprogramming efficiency limits their application in research and therapy. Here, we show that activation of the canonical Wnt signaling pathway increases the reprogramming efficiency of HUVECs to hiHepPCs by rapidly inducing chromatin remodeling and gene expression changes in the transduced HUVECs. Moreover, endogenous Wnt activation, mainly mediated by WNT2B, is required for the initiation of direct reprogramming from HUVECs to hiHepPCs. Wnt activation that allows rapid induction of hiHepPCs enables efficient production of a large amount of hiHepPCs, which is an advantage in research and clinical applications using hiHepPCs and their descendants.</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>HUVEC→hepatocyte-like cell reprogramming with FOXA3, HNF1A, HNF6 + CHIR99021/BIO (Wnt activators) is a documented protocol. Evidence describes experimental design directly. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2316,32 +2949,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>31849638</t>
+          <t>31797926</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Very Low Efficiency of Direct Reprogramming of Astrocytes Into Neurons in the Brains of Young and Aged Mice After Cerebral Ischemia.</t>
+          <t>Renewed proliferation in adult mouse cochlea and regeneration of hair cells.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>proliferating astrocyte (neocortex)</t>
+          <t>adult cochlear supporting cell</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>neuron (neuroblast and mature neuron)</t>
+          <t>hair cell-like cell</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>NGN2, Bcl-2</t>
+          <t>Myc, Notch1, ATOH1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>TF, other</t>
+          <t>TF, TF, TF</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2361,37 +2994,65 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/31849638</t>
-        </is>
-      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>To this end, we used a retroviral delivery system encoding the transcription factor &lt;i&gt;Ngn2&lt;/i&gt; alone or in combination with the antiapoptotic factor &lt;i&gt;Bcl-2&lt;/i&gt; to target proliferating astrocytes in the neocortex of young and aged mice after cerebral ischemia.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/31797926</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>After cerebral ischemia, the ratio between astroglial cells and neurons in the neurovascular unit is disrupted in the perilesional area. We hypothesized that restoring the balance within the neurovascular unit may lead to an improved neurorestoration after focal ischemia. Recently, an innovative technology has been invented to efficiently convert proliferating astroglial cells into neurons in the injured young brain. However, the conversion efficacy of this technology has not been explored in the post-stroke brains of the aged rodents. To this end, we used a retroviral delivery system encoding the transcription factor &lt;i&gt;Ngn2&lt;/i&gt; alone or in combination with the antiapoptotic factor &lt;i&gt;Bcl-2&lt;/i&gt; to target proliferating astrocytes in the neocortex of young and aged mice after cerebral ischemia. Successful direct &lt;i&gt;in vivo&lt;/i&gt; reprogramming of reactive glia into neuroblasts and mature neurons was assessed by cellular phenotyping. We found that the conversion efficacy of proliferating astrocytes into neurons after cerebral ischemia in young and aged mice is disappointingly low, most likely because the therapeutic vectors carrying the conversion gene are engulfed by phagocytes shortly after intracortical administration. We conclude that other viral vectors and combinations of transcription factors should be employed to improve the efficacy of glia-to-neuron conversion after stroke in young and aged rodents.</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
+          <t>Transient MYC and NOTCH activities enable adult supporting cells to respond to transcription factor Atoh1 and efficiently transdifferentiate into hair cell-like cells.</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>The adult mammalian inner ear lacks the capacity to divide or regenerate. Damage to inner ear generally leads to permanent hearing loss in humans. Here, we present that reprogramming of the adult inner ear induces renewed proliferation and regeneration of inner ear cell types. Co-activation of cell cycle activator Myc and inner ear progenitor gene Notch1 induces robust proliferation of diverse adult cochlear sensory epithelial cell types. Transient MYC and NOTCH activities enable adult supporting cells to respond to transcription factor Atoh1 and efficiently transdifferentiate into hair cell-like cells. Furthermore, we uncover that mTOR pathway participates in MYC/NOTCH-mediated proliferation and regeneration. These regenerated hair cell-like cells take up the styryl dye FM1-43 and are likely to form connections with adult spiral ganglion neurons, supporting that Myc and Notch1 co-activation is sufficient to reprogram fully mature supporting cells to proliferate and regenerate hair cell-like cells in adult mammalian auditory organs.</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>MYC+NOTCH1+ATOH1 adult cochlear SC→hair cell transdifferentiation. Evidence directly states efficient transdifferentiation into hair cell-like cells. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2399,32 +3060,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>34514853</t>
+          <t>34731408</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MUC1-C Contributes to the Maintenance of Human Embryonic Stem Cells and Promotes Somatic Cell Reprogramming.</t>
+          <t>Bend family proteins mark chromatin boundaries and synergistically promote early germ cell differentiation.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>fibroblast</t>
+          <t>mouse embryonic stem cell (mESC)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>induced pluripotent stem cell (iPSC)</t>
+          <t>epiblast-like cell (EpiLC)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MUC1-CD</t>
+          <t>Bend5, Bend4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>TF, TF</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2444,37 +3105,69 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t>directed_differentiation</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/34514853</t>
-        </is>
-      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>In addition, forced overexpression of MUC1-CD increased the efficiency of reprogramming from fibroblast cells to induced pluripotent stem cells, suggesting that MUC1-C expression can contribute to the reprogramming process.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/34731408</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Mucin 1 (MUC1) is a transmembrane glycoprotein overexpressed in several cancer cells in which it regulates cell surface properties, tumor invasion, and cell death. Recently, we reported that MUC1-C, the C-terminal subunit of MUC1, is involved in the growth of mouse embryonic stem (ES) cells. However, the functional significance of MUC1-C in human ES cells remains unclear. In this study, we investigated the expression and function of MUC1-C in human ES cells. Based on reverse transcription-polymerase chain reaction, western blotting, and confocal microscopy following immunostaining, undifferentiated human ES cells expressed MUC1-C and the expression level decreased during differentiation. Inhibition of MUC1-C, by the peptide inhibitor GO201 that targets the cytoplasmic domain of MUC1-C (MUC1-CD), reduced cell proliferation and OCT4 protein expression, and promoted cell death. Moreover, the inhibition of MUC1-C increased the intracellular reactive oxygen species (ROS) levels and downregulated expression of glycolysis-related enzymes. These findings indicate that expression and function of MUC1-C are required for stem cell properties involved in cell proliferation, maintenance of pluripotency and optimal ROS levels, and a high glycolytic flux in human ES cells. In addition, forced overexpression of MUC1-CD increased the efficiency of reprogramming from fibroblast cells to induced pluripotent stem cells, suggesting that MUC1-C expression can contribute to the reprogramming process.</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
+          <t>Through RNA-seq, ChIP-seq, and ATAC-seq analyses, we showed that Bend5 worked together with Bend4 and helped mark chromatin boundaries to promote EpiLC induction in vitro.</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Understanding the regulatory networks for germ cell fate specification is necessary to developing strategies for improving the efficiency of germ cell production in vitro. In this study, we developed a coupled screening strategy that took advantage of an arrayed bi-molecular fluorescence complementation (BiFC) platform for protein-protein interaction screens and epiblast-like cell (EpiLC)-induction assays using reporter mouse embryonic stem cells (mESCs). Investigation of candidate interaction partners of core human pluripotent factors OCT4, NANOG, KLF4 and SOX2 in EpiLC differentiation assays identified novel primordial germ cell (PGC)-inducing factors including BEN-domain (BEND/Bend) family members. Through RNA-seq, ChIP-seq, and ATAC-seq analyses, we showed that Bend5 worked together with Bend4 and helped mark chromatin boundaries to promote EpiLC induction in vitro. Our findings suggest that BEND/Bend proteins represent a new family of transcriptional modulators and chromatin boundary factors that participate in gene expression regulation during early germline development.</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>evidence_weak</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Evidence sentence describes omics analysis of how Bend5/Bend4 promote EpiLC induction — mechanistic finding, not a direct conversion outcome statement. Bend5 and Bend4 are chromatin boundary factors; their role in mESC→EpiLC transition is plausible but evidence is indirect.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2482,32 +3175,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>35801179</t>
+          <t>26719791</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Foxa2 and Pet1 Direct and Indirect Synergy Drive Serotonergic Neuronal Differentiation.</t>
+          <t>Reprogramming somatic cells to cells with neuronal characteristics by defined medium both in vitro and in vivo.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>mouse embryonic stem cell (mESC)</t>
+          <t>mouse embryonic fibroblast (MEF)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>serotonergic neuron</t>
+          <t>induced neuron (iN)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ASCL1, Lmx1b, FOXA2</t>
+          <t>bFGF, N2 supplement, LIF, vitamin C, βMe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>TF, TF, TF</t>
+          <t>cytokine, other, cytokine, small_molecule, small_molecule</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2527,37 +3220,65 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/35801179</t>
-        </is>
-      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>The addition of Pet1 or Foxa2 to iAL (iALP and iALF, respectively) was sufficient to induce serotonergic staining and TPH expression.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/26719791</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Neuronal programming by forced expression of transcription factors (TFs) holds promise for clinical applications of regenerative medicine. However, the mechanisms by which TFs coordinate their activities on the genome and control distinct neuronal fates remain obscure. Using direct neuronal programming of embryonic stem cells, we dissected the contribution of a series of TFs to specific neuronal regulatory programs. We deconstructed the Ascl1-Lmx1b-Foxa2-Pet1 TF combination that has been shown to generate serotonergic neurons and found that stepwise addition of TFs to Ascl1 canalizes the neuronal fate into a diffuse monoaminergic fate. The addition of pioneer factor Foxa2 represses Phox2b to induce serotonergic fate, similar to &lt;i&gt;in vivo&lt;/i&gt; regulatory networks. Foxa2 and Pet1 appear to act synergistically to upregulate serotonergic fate. Foxa2 and Pet1 co-bind to a small fraction of genomic regions but mostly bind to different regulatory sites. In contrast to the combinatorial binding activities of other programming TFs, Pet1 does not strictly follow the Foxa2 pioneer. These findings highlight the challenges in formulating generalizable rules for describing the behavior of TF combinations that program distinct neuronal subtypes.</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
+          <t>Application of 5C medium converted mouse embryonic fibroblasts (MEFs) into TuJ+ neuronal-like cells, which were capable of survival after being transplanted into the mouse brain.</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Currently, direct conversion from somatic cells to neurons requires virus-mediated delivery of at least one transcriptional factor or a combination of several small-molecule compounds. Delivery of transcriptional factors may affect genome stability, while small-molecule compounds may require more evaluations when applied in vivo. Thus, a defined medium with only conventional growth factors or additives for cell culture is desirable for inducing neuronal trans-differentiation. Here, we report that a defined medium (5C) consisting of basic fibroblast growth factor (bFGF), N2 supplement, leukemia inhibitory factor, vitamin C (Vc), and β-mercaptoethanol (βMe) induces the direct conversion of somatic cells to cells with neuronal characteristics. Application of 5C medium converted mouse embryonic fibroblasts (MEFs) into TuJ+ neuronal-like cells, which were capable of survival after being transplanted into the mouse brain. The same 5C medium could convert primary rat astrocytes into neuronal-like cells with mature electrophysiology characteristics in vitro and facilitated the recovery of brain injury, possibly by inducing similar conversions, when infused into the mouse brain in vivo. Crucially, 5C medium could also induce neuronal characteristics in several human cell types. In summary, this 5C medium not only provides a means to derive cells with neuronal characteristics without viral transfection in vitro but might also be useful to produce neurons in vivo for neurodegenerative disease treatment.</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>5C chemical medium (bFGF, N2, LIF, VitC, betaME) alone converts MEFs to TuJ+ neuronal cells capable of brain transplantation. Chemical-only conversion confirmed by evidence. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2610,37 +3331,65 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t>directed_differentiation</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/34488017</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>We found that knockout of the transcription factor E2A substantially increased the proportion of nodal-like cells in hESC-derived CMs.</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Human sinoatrial cardiomyocytes are essential building blocks for cell therapies of conduction system disorders. However, current differentiation protocols for deriving nodal cardiomyocytes from human pluripotent stem cells (hPSCs) are very inefficient. By employing the hPSCs to cardiomyocyte (CM) in vitro differentiation system and generating E2A-knockout hESCs using CRISPR/Cas9 gene editing technology, we analyze the functions of E2A in CM differentiation. We found that knockout of the transcription factor E2A substantially increased the proportion of nodal-like cells in hESC-derived CMs. The E2A ablated CMs displayed smaller cell size, increased beating rates, weaker contractile force, and other functional characteristics similar to sinoatrial node (SAN) cells. Transcriptomic analyses indicated that ion channel-encoding genes were up-regulated in E2A ablated CMs. E2A directly bounded to the promoters of genes key to SAN development via conserved E-box motif, and promoted their expression. Unexpect enhanced activity of NOTCH pathway after E2A ablation could also facilate to induct ventricle workingtype CMs reprogramming into SAN-like cells. Our study revealed a new role for E2A during directed cardiac differentiation of hESCs and may provide new clues for enhancing induction efficiency of SAN-like cardiomyocytes from hPSCs in the future. This work was supported by the NSFC (No.82070391, N.S.; No.81870175 and 81922006, P.L.), the National Key R&amp;D Program of China (2018YFC2000202, N.S.; 2017YFA0103700, P.L.), the Haiju program of National Children's Medical Center EK1125180102, and Innovative research team of high-level local universities in Shanghai and a key laboratory program of the Education Commission of Shanghai Municipality (ZDSYS14005).</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>E2A KO in hESC-derived CMs increases nodal-like cardiomyocyte proportion. Loss-of-function as reprogramming factor is acceptable. Evidence directly states the finding. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2693,37 +3442,69 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/30611717</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Eupatilin induced myofibroblasts to dedifferentiate into intermediate HCS-like cells.</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Myofibroblasts are known to play a key role in the development of idiopathic pulmonary fibrosis (IPF). Two drugs, pirfenidone and nintedanib, are the only approved therapeutic options for IPF, but their applications are limited due to their side effects. Thus, curative IPF drugs represent a huge unmet medical need. A mouse hepatic stellate cell (HSC) line was established that could robustly differentiate into myofibroblasts upon treatment with TGF-β. Eupatilin was assessed in diseased human lung fibroblasts from IPF patients (DHLFs) as well as in human lung epithelial cells (HLECs). The drug's performance was extensively tested in a bleomycin-induced lung fibrosis model (BLM). Global gene expression studies and proteome analysis were performed. Eupatilin attenuated disease severity of BLM in both preventative and therapeutic studies. The drug inhibited the in vitro transdifferantiation of DHLFs to myofibroblasts upon stimulation with TGF-β. No such induction of the in vitro transdifferantiation was observed in TGF-β treated HLECs. Specific carbons of eupatilin were essential for its anti-fibrotic activity. Eupatilin was capable of dismantling latent TGF-β complex, specifically by eliminating expression of the latent TGF-β binding protein 1 (LTBP1), in ECM upon actin depolymerization. Unlike eupatilin, pirfenidone was unable to block fibrosis of DHLFs or HSCs stimulated with TGF-β. Eupatilin attenuated phosphorylation of Smad3 by TGF-β. Eupatilin induced myofibroblasts to dedifferentiate into intermediate HCS-like cells. Eupatilin may act directly on pathogenic myofibroblasts, disarming them, whereas the anti-fibrotic effect of pirfenidone may be indirect. Eupatilin could increase the efficacy of IPF treatment to curative levels.</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>target_synonym</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>Target 'intermediate HSC-like cell' is ambiguous — in context of IPF/myofibroblasts, HSC = hepatic stellate cell (not hematopoietic stem cell). Should be clarified as 'hepatic stellate cell-like cell'. Eupatilin-induced dedifferentiation of myofibroblasts is plausible.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2731,32 +3512,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>37992523</t>
+          <t>35220676</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cardiac reprogramming reduces inflammatory macrophages and improves cardiac function in chronic myocardial infarction.</t>
+          <t>Direct Conversion of Human Endothelial Cells Into Liver Cancer-Forming Cells Using Nonintegrative Episomal Vectors.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>cardiac fibroblast</t>
+          <t>HUVEC</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>cardiomyocyte</t>
+          <t>liver cancer-forming cells (LCCs) resembling combined hepatocellular-cholangiocarcinoma</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MEF2C, GATA4, TBX5, HAND2</t>
+          <t>FOXA3, HNF1A, HNF1B, LIN28B, L-MYC, KLF5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>TF, TF, TF, TF</t>
+          <t>TF, TF, TF, other, TF, TF</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2776,37 +3557,65 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/37992523</t>
-        </is>
-      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Cardiac reprogramming converts CFs into induced CMs, reduces fibrosis, and improves cardiac function in chronic MI through the overexpression of Mef2c/Gata4/Tbx5/Hand2 (MGTH).</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/35220676</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Cardiomyocytes (CMs) have little regenerative capacity. After myocardial infarction (MI), scar formation and myocardial remodeling proceed in the infarct and non-infarct areas, respectively, leading to heart failure (HF). Prolonged activation of cardiac fibroblasts (CFs) and inflammatory cells may contribute to this process; however, therapies targeting these cell types remain lacking. Cardiac reprogramming converts CFs into induced CMs, reduces fibrosis, and improves cardiac function in chronic MI through the overexpression of Mef2c/Gata4/Tbx5/Hand2 (MGTH). However, whether cardiac reprogramming reduces inflammation in infarcted hearts remains unclear. Moreover, the mechanism through which MGTH overexpression in CFs affects inflammatory cells remains unknown. Here, we showed that inflammation persists in the myocardium until three months after MI, which can be reversed with cardiac reprogramming. Single-cell RNA sequencing demonstrated that CFs expressed pro-inflammatory genes and exhibited strong intercellular communication with inflammatory cells, including macrophages, in chronic MI. Cardiac reprogramming suppressed the inflammatory profiles of CFs and reduced the relative ratios and pro-inflammatory signatures of cardiac macrophages. Moreover, fluorescence-activated cell sorting analysis (FACS) revealed that cardiac reprogramming reduced the number of chemokine receptor type 2 (CCR2)-positive inflammatory macrophages in the non-infarct areas in chronic MI, thereby restoring myocardial remodeling. Thus, cardiac reprogramming reduced the number of inflammatory macrophages to exacerbate cardiac function after MI.</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+          <t>We found that a set of six factors, forkhead box A3 (FOXA3), hepatocyte nuclear factor homeobox 1A (HNF1A), HNF1B, lin-28 homolog B (LIN28B), MYCL proto-oncogene, bHLH transcription factor (L-MYC), and Kruppel-like factor 5 (KLF5), induced direct conversion of HUVECs into LCCs.</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Liver cancer is an aggressive cancer associated with a poor prognosis. Development of therapeutic strategies for liver cancer requires fundamental research using suitable experimental models. Recent progress in direct reprogramming technology has enabled the generation of many types of cells that are difficult to obtain and provide a cellular resource in experimental models of human diseases. In this study, we aimed to establish a simple one-step method for inducing cells that can form malignant human liver tumors directly from healthy endothelial cells using nonintegrating episomal vectors. To screen for factors capable of inducing liver cancer-forming cells (LCCs), we selected nine genes and one short hairpin RNA that suppresses tumor protein p53 (TP53) expression and introduced them into human umbilical vein endothelial cells (HUVECs), using episomal vectors. To identify the essential factors, we examined the effect of changing the amounts and withdrawing individual factors. We then analyzed the proliferation, gene and protein expression, morphologic and chromosomal abnormality, transcriptome, and tumor formation ability of the induced cells. We found that a set of six factors, forkhead box A3 (FOXA3), hepatocyte nuclear factor homeobox 1A (HNF1A), HNF1B, lin-28 homolog B (LIN28B), MYCL proto-oncogene, bHLH transcription factor (L-MYC), and Kruppel-like factor 5 (KLF5), induced direct conversion of HUVECs into LCCs. The gene expression profile of these induced LCCs (iLCCs) was similar to that of human liver cancer cells, and these cells effectively formed tumors that resembled human combined hepatocellular-cholangiocarcinoma following transplantation into immunodeficient mice. Conclusion: We succeeded in the direct induction of iLCCs from HUVECs by using nonintegrating episomal vectors. iLCCs generated from patients with cancer and healthy volunteers will be useful for further advancements in cancer research and for developing methods for the diagnosis, treatment, and prognosis of liver cancer.</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>HUVEC→liver cancer-forming cells with 6 factors (FOXA3, HNF1A, HNF1B, LIN28B, L-MYC, KLF5). Evidence directly identifies the factor combination. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2814,32 +3623,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>33239022</t>
+          <t>33099273</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Macrophage to myofibroblast transition contributes to subretinal fibrosis secondary to neovascular age-related macular degeneration.</t>
+          <t>Knockdown of &lt;i&gt;Foxg1&lt;/i&gt; in Sox9+ supporting cells increases the trans-differentiation of supporting cells into hair cells in the neonatal mouse utricle.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>bone marrow-derived macrophage (BMDM) from C57BL/6J mice</t>
+          <t>utricular supporting cell (Sox9+)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>myofibroblast (α-SMA+ cell)</t>
+          <t>utricular hair cell (Myo7a+)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TGF-β1, C3a</t>
+          <t>Foxg1 knockdown</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>cytokine, cytokine</t>
+          <t>knockdown</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2859,37 +3668,69 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/33239022</t>
-        </is>
-      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Together, these data suggest that TGF-β and complement C3a can induce MMT.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/33099273</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Macular fibrosis causes irreparable vision loss in neovascular age-related macular degeneration (nAMD) even with anti-vascular endothelial growth factor (VEGF) therapy. Inflammation is known to play an important role in macular fibrosis although the underlying mechanism remains poorly defined. The aim of this study was to understand how infiltrating macrophages and complement proteins may contribute to macular fibrosis. Subretinal fibrosis was induced in C57BL/6J mice using the two-stage laser protocol developed by our group. The eyes were collected at 10, 20, 30 and 40 days after the second laser and processed for immunohistochemistry for infiltrating macrophages (F4/80 and Iba-1), complement components (C3a and C3aR) and fibrovascular lesions (collagen-1, Isolectin B4 and α-SMA). Human retinal sections with macular fibrosis were also used in the study. Bone marrow-derived macrophages (BMDMs) from C57BL/6J mice were treated with recombinant C3a, C5a or TGF-β for 48 and 96 h. qPCR, Western blot and immunohistochemistry were used to examine the expression of myofibroblast markers. The involvement of C3a-C3aR pathway in macrophage to myofibroblast transition (MMT) and subretinal fibrosis was further investigated using a C3aR antagonist (C3aRA) and a C3a blocking antibody in vitro and in vivo. Approximately 20~30% of F4/80&lt;sup&gt;+&lt;/sup&gt; (or Iba-1&lt;sup&gt;+&lt;/sup&gt;) infiltrating macrophages co-expressed α-SMA in subretinal fibrotic lesions both in human nAMD eyes and in the mouse model. TGF-β and C3a, but not C5a treatment, significantly upregulated expression of α-SMA, fibronectin and collagen-1 in BMDMs. C3a-induced upregulation of α-SMA, fibronectin and collagen-1 in BMDMs was prevented by C3aRA treatment. In the two-stage laser model of induced subretinal fibrosis, treatment with C3a blocking antibody but not C3aRA significantly reduced vascular leakage and Isolectin B4&lt;sup&gt;+&lt;/sup&gt; lesions. The treatment did not significantly alter collagen-1&lt;sup&gt;+&lt;/sup&gt; fibrotic lesions. MMT plays a role in macular fibrosis secondary to nAMD. MMT can be induced by TGF-β and C3a but not C5a. Further research is required to fully understand the role of MMT in macular fibrosis. Macrophage to myofibroblast transition (MMT) contributes to subretinal fibrosis. Subretinal fibrosis lesions contain various cell types, including macrophages and myofibroblasts, and are fibrovascular. Myofibroblasts are key cells driving pathogenic fibrosis, and they do so by producing excessive amount of extracellular matrix proteins. We have found that infiltrating macrophages can transdifferentiate into myofibroblasts, a phenomenon termed macrophage to myofibroblast transition (MMT) in macular fibrosis. In addition to TGF-β1, C3a generated during complement activation in CNV can also induce MMT contributing to macular fibrosis. RPE = retinal pigment epithelium. BM = Bruch's membrane. MMT = macrophage to myofibroblast transition. TGFB = transforming growth factor β. a-SMA = alpha smooth muscle actin. C3a = complement C3a.</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
+          <t>Because we previously reported that cKD of Foxg1 in cochlear SCs using Sox2-CreER mice induces increased HC numbers in neonatal mice [38], we hypothesized that Foxg1 has a similar function in the utricle as it does in the cochlea.</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Foxg1 plays important roles in regeneration of hair cell (HC) in the cochlea of neonatal mouse. Here, we used Sox9-CreER to knock down &lt;i&gt;Foxg1&lt;/i&gt; in supporting cells (SCs) in the utricle in order to investigate the role of Foxg1 in HC regeneration in the utricle. We found Sox9 an ideal marker of utricle SCs and bred Sox9&lt;sup&gt;CreER/+&lt;/sup&gt;Foxg1&lt;sup&gt;loxp/loxp&lt;/sup&gt; mice to conditionally knock down &lt;i&gt;Foxg1&lt;/i&gt; in utricular SCs. Conditional knockdown (cKD) of &lt;i&gt;Foxg1&lt;/i&gt; in SCs at postnatal day one (P01) led to increased number of HCs at P08. These regenerated HCs had normal characteristics, and could survive to at least P30. Lineage tracing showed that a significant portion of newly regenerated HCs originated from SCs in &lt;i&gt;Foxg1&lt;/i&gt; cKD mice compared to the mice subjected to the same treatment, which suggested SCs trans-differentiate into HCs in the &lt;i&gt;Foxg1&lt;/i&gt; cKD mouse utricle. After neomycin treatment &lt;i&gt;in vitro&lt;/i&gt;, more HCs were observed in &lt;i&gt;Foxg1&lt;/i&gt; cKD mice utricle compared to the control group. Together, these results suggest that &lt;i&gt;Foxg1&lt;/i&gt; cKD in utricular SCs may promote HC regeneration by inducing trans-differentiation of SCs. This research therefore provides theoretical basis for the effects of Foxg1 in trans-differentiation of SCs and regeneration of HCs in the mouse utricle.</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>evidence_weak</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>Evidence sentence cites a prior paper ('we previously reported') rather than this paper's own result. Current paper's finding (utricular SC→HC by Foxg1 knockdown) needs to be confirmed by an evidence sentence from this paper's experiments.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2897,32 +3738,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>41237238</t>
+          <t>22912667</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Blocking nuclear receptor Nr4a3 unlocks the senescence barrier to promote direct cardiac reprogramming.</t>
+          <t>MiR-25 regulates Wwp2 and Fbxw7 and promotes reprogramming of mouse fibroblast cells to iPSCs.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>tail tip fibroblast</t>
+          <t>mouse embryonic fibroblast (MEF)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>cardiomyocyte</t>
+          <t>induced pluripotent stem cell (iPSC)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MEF2C, GATA4, TBX5</t>
+          <t>OCT4, c-MYC, KLF4, SOX2, miR-25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>TF, TF, TF</t>
+          <t>TF, TF, TF, TF, miRNA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2942,37 +3783,65 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t>classical_reprogramming</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/41237238</t>
-        </is>
-      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Again, we found that both MGT and MGTH successfully induced iCMs in neonatal TTFs but rarely induced cTnT+ iCMs in adult and aged TTFs by flow cytometry and ICC.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/22912667</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Direct reprogramming of fibroblasts into induced cardiomyocytes (iCMs) offers a regenerative strategy for heart repair, but efficiency declines in adult and aged cells. Transcriptomic and epigenetic profiling identified cellular senescence as a major barrier limiting cardiac fibroblast (CF) plasticity and cardiogenic conversion. Postneonatal fibroblasts exhibited impaired activation of cardiac gene programs and persistent expression of fibrotic and inflammatory signatures. A loss-of-function screen identified Nr4a3 as a central repressor. Nr4a3 overexpression promoted senescence and suppressed iCM induction, whereas knockdown enhanced reprogramming in murine and human senescent CFs. Mechanistically, Nr4a3 depletion remodeled the chromatin landscape from a fibrotic and inflammatory state to a regenerative cardiac program. Blocking downstream Cxcl14 restored reprogramming in refractory fibroblasts. In vivo, Nr4a3 knockdown improved heart function following myocardial infarction. These findings established cellular senescence as a major barrier to cardiac reprogramming and identified Nr4a3 and its effectors as potential targets to enhance heart regeneration.</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
+          <t>We screened 52 miRNAs cloned in a piggybac (PB) vector for their roles in reprogramming of mouse embryonic fibroblast cells to iPSCs.</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>miRNAs are a class of small non-coding RNAs that regulate gene expression and have critical functions in various biological processes. Hundreds of miRNAs have been identified in mammalian genomes but only a small number of them have been functionally characterized. Recent studies also demonstrate that some miRNAs have important roles in reprogramming somatic cells to induced pluripotent stem cells (iPSCs). We screened 52 miRNAs cloned in a piggybac (PB) vector for their roles in reprogramming of mouse embryonic fibroblast cells to iPSCs. To identify targets of miRNAs, we made Dgcr8-deficient embryonic stem (ES) cells and introduced miRNA mimics to these cells, which lack miRNA biogenesis. The direct target genes of miRNA were identified through global gene expression analysis and target validation. We found that over-expressing miR-25 or introducing miR-25 mimics enhanced production of iPSCs. We identified a number of miR-25 candidate gene targets. Of particular interest were two ubiquitin ligases, Wwp2 and Fbxw7, which have been proposed to regulate Oct4, c-Myc and Klf5, respectively. Our findings thus highlight the complex interplay between miRNAs and transcription factors involved in reprogramming, stem cell self-renewal and maintenance of pluripotency.</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>OSKM + miR-25 reprogramming of MEFs to iPSCs. miR-25 as an enhancer is documented. Evidence describes the miRNA screening in reprogramming context. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2980,27 +3849,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>41645083</t>
+          <t>37357214</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Conjoining cell reprogramming and mass spectrometry to identify the proteomic variations in the reprogrammed bladder cancer cells: finding cues of normalisation.</t>
+          <t>[Establishment of induced pluripotent stem cell model of Aicardi-Goutières Syndrome mutated in TREX1].</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>bladder cancer cell line HTB-5</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>iPSC-like reprogrammed bladder cancer cells</t>
+          <t>induced pluripotent stem cell (iPSC)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OCT4, SOX2, KLF4, c-MYC</t>
+          <t>OCT4, SOX2, c-MYC, KLF4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3025,37 +3894,65 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t>classical_reprogramming</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/41645083</t>
-        </is>
-      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Sendai virus-based reprogramming was utilised to reprogram the bladder cancer cell line HTB-5.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/37357214</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Cancer cell reprogramming is a critical area of research that holds the power to transform malignancies into benign states while revealing key mechanisms of carcinogenesis. This study aimed to develop a more effective in vitro bladder cancer model using induced pluripotent stem cell technology and identify potential diagnostic and therapeutic biomarkers for bladder cancer. Sendai virus-based reprogramming was utilised to reprogram the bladder cancer cell line HTB-5. The reprogrammed cells were characterised by expressing pluripotency-associated markers, colony formation abilities, cell migration, and drug responses. LC-MS/MS reveals changes in protein composition among parental cancer cells, reprogrammed cancer cells, and normal uroepithelial cells. Reprogrammed bladder cancer cells display the expression of pluripotency-associated markers and demonstrate altered behaviours, including cell migration and responses to anticancer therapies. The genome-wide regulation by Sendai-virus delivery of Yamanaka factors resulted in distinctive protein expression patterns in reprogrammed bladder cancer cells, indicative of the pluripotency as well as spontaneous differentiation. A total of 297 dysregulated proteins in bladder cancer cells were normalised upon reprogramming. We proposed 25 potential biomarker candidates for diagnostic and therapeutic purposes, of which 12 candidates were demonstrated for the first time at the protein level. Differentially regulated proteins in parental bladder cancer cells and reprogrammed bladder cancer cells highlighted the critical protein-protein interactions that indicate the normalisation process of the parental bladder cancer cells. These cues could be used to pinpoint the candidate proteins to optimise the controlled partial/full reprogramming, to discover the therapeutic potential of reprogramming and to propose clinically relevant biomarker candidates. [Figure: see text] The online version contains supplementary material available at 10.1186/s12885-026-15634-x.</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+          <t>Then,the peripheral blood mononuclear cells(PBMCs) were transduced with OCT3/4, SOX2, c-Myc and Klf4 by using Sendai virus, and PBMCs were reprogrammed into iPSCs.</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>To establish and identify induced pluripotent stem cells (iPSCs) derived from patients with Aicardi-Goutières syndrome (AGS) with TREX1 gene 667G&gt;A mutation, and obtain a specific induced pluripotent stem cell model for Aicardi-Goutières syndrome (AGS-iPSCs). A 3-year-old male child with Aicardi-Goutieres syndrome was admitted to Zhongshan People's Hospital in December 2020. After obtaining the informed consent of the patient's family members, 5 ml peripheral blood samples from the patient were collected, and mononuclear cells were isolated. Then,the peripheral blood mononuclear cells(PBMCs) were transduced with OCT3/4, SOX2, c-Myc and Klf4 by using Sendai virus, and PBMCs were reprogrammed into iPSCs. The pluripotency and differentiation ability of the cells were identified by cellular morphological analysis, real-time PCR, alkaline phosphatase staining (AP), immunofluorescence, teratoma formation experiments in mice. The results showed that the induced pluripotent stem cell line of Aicardi-Goutieres syndrome was successfully constructed and showed typical embryonic stem-like morphology after stable passage, RT-PCR showed mRNA expression of stem cell markers, AP staining was positive, OCT4, SOX2, NANOG, SSEA4, TRA-1-81 and TRA-1-60 pluripotency marker proteins were strongly expressed. In vivo teratoma formation experiments showed that iPSCs differentiate into the ectoderm (neural tube like tissue), mesoderm (vascular wall tissue) and endoderm (glandular tissue). Karyotype analysis also confirmed that iPSCs still maintained the original karyotype (46, XY). In conclusion, induced pluripotent stem cell line for Aicardi-Goutières syndrome was successfully established using Sendai virus, which provided an important model platform for studying the pathogenesis of the disease and for drug screening.</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Standard OSKM Sendai virus reprogramming of PBMCs to iPSCs. Evidence directly confirms transduction and reprogramming. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3063,32 +3960,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20663865</t>
+          <t>12881423</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>The Necdin-Wnt pathway causes epigenetic peroxisome proliferator-activated receptor gamma repression in hepatic stellate cells.</t>
+          <t>Myeloid lineage switch of Pax5 mutant but not wild-type B cell progenitors by C/EBPalpha and GATA factors.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>activated hepatic stellate cell</t>
+          <t>Pax5(-/-) pro-B cell</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>quiescent hepatic stellate cell</t>
+          <t>macrophage</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>necdin silencing (shRNA)</t>
+          <t>C/EBPalpha, GATA1, GATA2, GATA3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>knockdown</t>
+          <t>TF, TF, TF, TF</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3108,37 +4005,65 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/20663865</t>
-        </is>
-      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Silencing of necdin with adenovirally expressed shRNA, reverses activated HSCs to quiescent cells in a manner dependent on PPARγ and suppressed canonical Wnt signaling.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/12881423</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Hepatic stellate cells (HSCs), vitamin A-storing liver pericytes, undergo myofibroblastic trans-differentiation or "activation" to participate in liver wound healing. This cellular process involves loss of regulation by adipogenic transcription factors such as peroxisome proliferator-activated receptor γ (PPARγ). Necdin, a melanoma antigen family protein, promotes neuronal and myogenic differentiation while inhibiting adipogenesis. The present study demonstrates that necdin is selectively expressed in HSCs among different liver cell types and induced during their activation in vitro and in vivo. Silencing of necdin with adenovirally expressed shRNA, reverses activated HSCs to quiescent cells in a manner dependent on PPARγ and suppressed canonical Wnt signaling. Promoter analysis, site-directed mutagenesis, and chromatin immunoprecipitation demonstrate that Wnt10b, a canonical Wnt induced in activated HSCs, is a direct target of necdin. Necdin silencing abrogates three epigenetic signatures implicated in repression of PPARγ: increased MeCP2 (methyl CpG binding protein 2) and HP-1α co-repressor recruitments to Pparγ promoter and enhanced H3K27 dimethylation at the exon 5 locus, again in a manner dependent on suppressed canonical Wnt. These epigenetic effects are reproduced by antagonism of canonical Wnt signaling with Dikkopf-1. Our results demonstrate a novel necdin-Wnt pathway, which serves to mediate antiadipogenic HSC trans-differentiation via epigenetic repression of PPARγ.</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+          <t>Here we demonstrate that ectopic expression of the transcription factors C/EBPalpha, GATA1, GATA2 and GATA3 strongly promoted in vitro macrophage differentiation and myeloid colony formation of Pax5(-/-) pro-B cells.</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>The developmental potential of hematopoietic progenitors is restricted early on to either the erythromyeloid or lymphoid lineages. The broad developmental potential of Pax5(-/-) pro-B cells is in apparent conflict with such a strict separation, although these progenitors realize the myeloid and erythroid potential with lower efficiency compared to the lymphoid cell fates. Here we demonstrate that ectopic expression of the transcription factors C/EBPalpha, GATA1, GATA2 and GATA3 strongly promoted in vitro macrophage differentiation and myeloid colony formation of Pax5(-/-) pro-B cells. GATA2 and GATA3 expression also resulted in efficient engraftment and myeloid development of Pax5(-/-) pro-B cells in vivo. The myeloid transdifferentiation of Pax5(-/-) pro-B cells was accompanied by the rapid activation of myeloid genes and concomitant repression of B-lymphoid genes by C/EBPalpha and GATA factors. These data identify the Pax5(-/-) pro-B cells as lymphoid progenitors with a latent myeloid potential that can be efficiently activated by myeloid transcription factors. The same regulators were unable to induce a myeloid lineage switch in Pax5(+/+) pro-B cells, indicating that Pax5 dominates over myeloid transcription factors in B-lymphocytes.</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>C/EBPalpha, GATA1, GATA2, GATA3 converting Pax5(-/-) pro-B cells to macrophages. Evidence directly describes the reprogramming result with myeloid colony formation. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3146,32 +4071,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>34171285</t>
+          <t>20691899</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Reprogramming astrocytes to motor neurons by activation of endogenous Ngn2 and Isl1.</t>
+          <t>Direct reprogramming of fibroblasts into functional cardiomyocytes by defined factors.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>mouse spinal astrocyte</t>
+          <t>fibroblast</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>motor neuron</t>
+          <t>cardiomyocyte</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NGN2, Isl1</t>
+          <t>GATA4, MEF2C, TBX5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>TF, TF</t>
+          <t>TF, TF, TF</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3191,37 +4116,65 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/34171285</t>
-        </is>
-      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Here, we showed that the activation of endogenous genes Ngn2 and Isl1 by CRISPRa enabled reprogramming of mouse spinal astrocytes and embryonic fibroblasts to motor neurons.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/20691899</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Central nervous system injury and neurodegenerative diseases cause irreversible loss of neurons. Overexpression of exogenous specific transcription factors can reprogram somatic cells into functional neurons for regeneration and functional reconstruction. However, these practices are potentially problematic due to the integration of vectors into the host genome. Here, we showed that the activation of endogenous genes Ngn2 and Isl1 by CRISPRa enabled reprogramming of mouse spinal astrocytes and embryonic fibroblasts to motor neurons. These induced neurons showed motor neuronal morphology and exhibited electrophysiological activities. Furthermore, astrocytes in the spinal cord of the adult mouse can be converted into motor neurons by this approach with high efficiency. These results demonstrate that the activation of endogenous genes is sufficient to induce astrocytes into functional motor neurons in vitro and in vivo. This direct neuronal reprogramming approach may provide a novel potential therapeutic strategy for treating neurodegenerative diseases and spinal cord injury.</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
+          <t>Here, we report that a combination of three developmental transcription factors (i.e., Gata4, Mef2c, and Tbx5) rapidly and efficiently reprogrammed postnatal cardiac or dermal fibroblasts directly into differentiated cardiomyocyte-like cells.</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>The reprogramming of fibroblasts to induced pluripotent stem cells (iPSCs) raises the possibility that a somatic cell could be reprogrammed to an alternative differentiated fate without first becoming a stem/progenitor cell. A large pool of fibroblasts exists in the postnatal heart, yet no single "master regulator" of direct cardiac reprogramming has been identified. Here, we report that a combination of three developmental transcription factors (i.e., Gata4, Mef2c, and Tbx5) rapidly and efficiently reprogrammed postnatal cardiac or dermal fibroblasts directly into differentiated cardiomyocyte-like cells. Induced cardiomyocytes expressed cardiac-specific markers, had a global gene expression profile similar to cardiomyocytes, and contracted spontaneously. Fibroblasts transplanted into mouse hearts one day after transduction of the three factors also differentiated into cardiomyocyte-like cells. We believe these findings demonstrate that functional cardiomyocytes can be directly reprogrammed from differentiated somatic cells by defined factors. Reprogramming of endogenous or explanted fibroblasts might provide a source of cardiomyocytes for regenerative approaches.</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>GMT (GATA4, MEF2C, TBX5) fibroblast→cardiomyocyte — seminal Ieda et al. 2010 paper. Evidence sentence directly describes rapid, efficient reprogramming. Source 'fibroblast' is less specific but acceptable. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3229,32 +4182,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>26354680</t>
+          <t>29719629</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>High-efficiency reprogramming of fibroblasts into cardiomyocytes requires suppression of pro-fibrotic signalling.</t>
+          <t>Improvement of non-alcoholic steatohepatitis by hepatocyte-like cells generated from iPSCs with Oct4/Sox2/Klf4/Parp1.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>mouse embryonic fibroblast (MEF)</t>
+          <t>mouse fibroblast</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>cardiomyocyte</t>
+          <t>induced pluripotent stem cell (iPSC)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>GATA4, HAND2, MEF2C, TBX5, A83-01</t>
+          <t>OCT4, SOX2, KLF4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>TF, TF, TF, TF, small_molecule</t>
+          <t>TF, TF, TF</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3274,37 +4227,69 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t>classical_reprogramming</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/26354680</t>
-        </is>
-      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Spontaneously beating cells in GHMT-MEFs treated with A83-01 by 3 weeks.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/29719629</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Direct reprogramming of fibroblasts into cardiomyocytes by forced expression of cardiomyogenic factors, GMT (GATA4, Mef2C, Tbx5) or GHMT (GATA4, Hand2, Mef2C, Tbx5), has recently been demonstrated, suggesting a novel therapeutic strategy for cardiac repair. However, current approaches are inefficient. Here we demonstrate that pro-fibrotic signalling potently antagonizes cardiac reprogramming. Remarkably, inhibition of pro-fibrotic signalling using small molecules that target the transforming growth factor-β or Rho-associated kinase pathways converts embryonic fibroblasts into functional cardiomyocyte-like cells, with the efficiency up to 60%. Conversely, overactivation of these pro-fibrotic signalling networks attenuates cardiac reprogramming. Furthermore, inhibition of pro-fibrotic signalling dramatically enhances the kinetics of cardiac reprogramming, with spontaneously contracting cardiomyocytes emerging in less than 2 weeks, as opposed to 4 weeks with GHMT alone. These findings provide new insights into the molecular mechanisms underlying cardiac conversion of fibroblasts and would enhance efforts to generate cardiomyocytes for clinical applications.</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
+          <t>The iPSCs were reprogrammed by the transduction of retroviral vectors encoding four transcription factors (Oct-4/Sox2/Klf4/c-Myc; OSKM), three transcription factors (Oct-4/Sox2/Klf4; OSK), or three factors plus parp1 (Oct-4/Sox2/Klf4/Parp1, abbreviated as OSK-P), as described previously [15].</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>The prevalence of nonalcoholic fatty liver disease (NAFLD) is usually increased with age. Non-alcoholic steatohepatitis (NASH), a serious form of NAFLD, may lead to cirrhosis and end-stage liver diseases. Induced pluripotent stem cells (iPSCs) hold promising potential in personalized medicine. Although obviation of c-Myc reduces tumorigenic risk, it also largely reduced the generation of iPSCs. Recently, Poly(ADP-ribose) polymerase 1 (Parp1) has been reported to enhance cell reprogramming. In this study, we demonstrated that forced expression of Oct4/Sox2/Klf4/Parp1 (OSKP) effectively promoted iPSC generation from senescent somatic cells from 18-month-old mouse. The iPSCs presented regular pluripotent properties, ability to form smaller teratoma with smaller size, and the potential for tridermal differentiation including hepatocyte-like cells (OSKP-iPSC-Heps). Resembled to fetal hepatocytes but not senescent hepatocytes, these OSKP-iPSC-Heps possessed antioxidant ability and were resistant to oxidative insult induced by H&lt;sub&gt;2&lt;/sub&gt;O&lt;sub&gt;2&lt;/sub&gt; or exogenous fatty acid. Intrasplenic transplantation of OSKP-iPSC-Heps ameliorated the triglyceride over-accumulation and hepatitis, prevented the production of inflammatory cytokines and oxidative substances, and reduced apoptotic cells in methionine/choline-deficient diet (MCDD)-fed mice. In conclusion, we demonstrated that Parp-1 promoted iPSC generation from senescent cells, which can be used for the treatment of NASH after hepatic-specific differentiation. These findings indicated that patient-derived iPSC-Heps may offer an alternative option for treatment of NASH and NASH-associated end-stage liver diseases.</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>evidence_weak</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Evidence sentence describes multiple reprogramming conditions (OSKM, OSK, OSK+other) without specifying which applies to this row's factors (OSK). The entry is ambiguous about which 3TF condition is being captured.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3312,32 +4297,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>35791490</t>
+          <t>29198829</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MiR-106b-5p Regulates the Reprogramming of Spermatogonial Stem Cells into iPSC (Induced Pluripotent Stem Cell)-Like Cells.</t>
+          <t>Generation of Induced Progenitor-like Cells from Mature Epithelial Cells Using Interrupted Reprogramming.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>spermatogonial stem cell</t>
+          <t>EPCAMhigh-Club cell (mature Club cell from mouse lung)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>induced pluripotent stem cell (iPSC)</t>
+          <t>Club-iPL cell (interrupted reprogramming cell)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>miR-106b-5p</t>
+          <t>OCT4, SOX2, KLF4, c-MYC</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>miRNA</t>
+          <t>TF, TF, TF, TF</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3357,37 +4342,65 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/35791490</t>
-        </is>
-      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Interestingly, the induced SSC experimental groups showed similar properties to the iPS groups regarding the expression of OSKMN genes (Fig. 3).</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/29198829</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Recent years have brought notable progress in raising the efficiency of the reprogramming technique so that approaches have evolved from known transgenic factors to only a few miRNAs. Nevertheless, there is a poor understanding of both the key factors and biological networks underlying this reprogramming. The present study aimed to investigate the potential of miR-106b-5p in regulating spermatogonial stem cells (SSCs) to induced pluripotent stem cell (iPSC)-like cells. We used SSCs because pluripotency is inducible in SSCs under defined culture conditions, and they have a few issues compared to other adult stem cells. As both signaling and post-transcriptional gene controls are critical for pluripotency regulation, we traced the expression of Oct-4, Sox-2, Klf-4, c-Myc, and Nanog (OSKMN). Besides, we considered miR-106b-5p targets using bioinformatic methods. Our results showed that transfected SSCs with miR-106b-5p increased the expression of the OSKMN factors, which was significantly more than negative control groups. Moreover, using the functional miRNA enrichment analysis, online tools, and databases, we predicted that miR-106b-5p targeted a signaling pathway gene named MAPK1/ERK2, related to regulating stem cell pluripotency. Together, our data suggest that miR-106b-5p regulates the reprogramming of SSCs into iPSC-like cells. Furthermore, noteworthy progress in the in vitro development of SSCs indicates promise reservoirs and opportunities for future clinical trials.</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
+          <t>Thus, we selected a 3-week induction period during which we achieved the greatest level of expansion without activation of Nanog expression, and hereafter term the 3w+Dox cells Club-iPL cells.</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>A suitable source of progenitor cells is required to attenuate disease or affect cure. We present an "interrupted reprogramming" strategy to generate "induced progenitor-like (iPL) cells" using carefully timed expression of induced pluripotent stem cell reprogramming factors (Oct4, Sox2, Klf4, and c-Myc; OSKM) from non-proliferative Club cells. Interrupted reprogramming allowed controlled expansion yet preservation of lineage commitment. Under clonogenic conditions, iPL cells expanded and functioned as a bronchiolar progenitor-like population to generate mature Club cells, mucin-producing goblet cells, and cystic fibrosis transmembrane conductance regulator (CFTR)-expressing ciliated epithelium. In vivo, iPL cells can repopulate CFTR-deficient epithelium. This interrupted reprogramming process could be metronomically applied to achieve controlled progenitor-like proliferation. By carefully controlling the duration of expression of OSKM, iPL cells do not become pluripotent, and they maintain their memory of origin and retain their ability to efficiently return to their original phenotype. A generic technique to produce highly specified populations may have significant implications for regenerative medicine.</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>OSKM interrupted reprogramming of Club cells to iPL cells (3-week induction). Novel strategy with specific evidence for 3-week timepoint selection. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3395,32 +4408,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>41379378</t>
+          <t>34795766</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Vav1 Sustains the Expression of Insulin, PDX1 and miR-375 During Differentiation of hiPSCs to β Cells: A Potential Target to Improve the In Vitro Generation of Insulin-Producing Cells.</t>
+          <t>Chemically Defined Conditions Mediate an Efficient Induction of Dental Pulp Pluripotent-Like Stem Cells into Hepatocyte-Like Cells.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CD34-enriched blood cells</t>
+          <t>dental pulp pluripotent stem cells (DPPSCs)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>induced pluripotent stem cell (iPSC)</t>
+          <t>definitive endoderm (DE) cells</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sendai virus</t>
+          <t>Act A, Wnt3A</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>cytokine, cytokine</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3440,37 +4453,65 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t>directed_differentiation</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/41379378</t>
-        </is>
-      </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Human iPSC clones were generated by reprogramming CD34-enriched blood cells from healthy subjects using the Sendai virus technology (CytoTune-iPS Sendai Reprogramming Kit, Thermo Fisher Scientific, Waltham, MA, USA) [38, 39].</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/34795766</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Human-induced pluripotent stem cells (hiPSCs) have emerged as a promising source of transplantable insulinproducing cells (IPCs) to restore insulin levels in Type 1 Diabetes (T1D) patients. Despite progress, obtaining fully functional β cells from hiPSCs remains challenging, underscoring the need to better understand the intracellular mechanisms involved. We investigated here the potential role of Vav1, a multidomain protein that we identified as crucial for the maturation of human biliary stem cells (hBTSCs) into β-like cells and in the trans-differentiation of pancreatic adenocarcinoma (PDAC) cells into IPCs; METHODS: Levels and subcellular localization of Vav1 were investigated throughout a seven-step differentiation process of hiPSCs to β cells. Vav1expression was forcedly modulated in pancreatic progenitors, and the potential effects were evaluated on insulin production and on PDX1, miR-375, and Akt, key regulators of β cells generation; RESULTS. Vav1 showed dynamic modulation, with pancreatic precursor cells requiring adequate levels of the protein to generate IPCs. Vav1 sustains the expression of PDX1, a primary regulator of insulin expression, and of its target miR-375, essential for determining β cell mass. Furthermore, Vav1 reduction correlated with increased activation of Akt, which regulates cell survival and insulin secretion in β cells and is down-regulated by miR- 375. Our findings suggest the existence of a Vav1/PDX1/miR-375/Akt axis as part of the complex network orchestrating the generation of functional β cells. These insights indicate that strategies aimed at specifically modulating Vav1 levels may positively impact the generation of IPCs in vitro and, ultimately, β cell replacement therapy for T1D.</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
+          <t>Taken together, the increase in expression levels of bona-fide DE markers in conditional media supplemented with Act A alone or with Wnt3A suggests that our approaches using chemically defined differentiation conditions have successfully enriched the DE lineage of DPPSCs.</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Liver diseases are major causes of morbidity and mortality. Dental pulp pluripotent-like stem cells (DPPSCs) are of a considerable promise in tissue engineering and regenerative medicine as a new source of tissue-specific cells; therefore, this study is aimed at demonstrating their ability to generate functional hepatocyte-like cells &lt;i&gt;in vitro&lt;/i&gt;. Cells were differentiated on a collagen scaffold in serum-free media supplemented with growth factors and cytokines to recapitulate liver development. At day 5, the differentiated DPPSC cells expressed the endodermal markers FOXA1 and FOXA2. Then, the cells were derived into the hepatic lineage generating hepatocyte-like cells. In addition to the associated morphological changes, the cells expressed the hepatic genes HNF6 and AFP. The terminally differentiated hepatocyte-like cells expressed the liver functional proteins albumin and CYP3A4. In this study, we report an efficient serum-free protocol to differentiate DPPSCs into functional hepatocyte-like cells. Our approach promotes the use of DPPSCs as a new source of adult stem cells for prospective use in liver regenerative medicine.</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>Activin A ± Wnt3A directing DPPSCs to definitive endoderm. Evidence describes DE marker expression in chemically defined conditions. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3478,32 +4519,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>40715046</t>
+          <t>41233896</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Direct transdifferentiation of tumorigenic melanoma cells induces tumor cell reversion.</t>
+          <t>Directly reprogrammed NK cells driven by BCL11B depletion enhance targeted immunotherapy against pancreatic ductal adenocarcinoma.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>human melanoma cells (BRAF-mutated and NRAS-mutated lines)</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>induced neuron (iN)</t>
+          <t>cytotoxic NK cells (1F-NKs; CD56brightCD16bright)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ASCL1, BRN2, MYT1L, NEUROD1</t>
+          <t>BCL11B knockdown (shRNA or CRISPR)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>TF, TF, TF, TF</t>
+          <t>knockdown</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3523,37 +4564,65 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/40715046</t>
-        </is>
-      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>In order to examine if melanoma cells can be transdifferentiated into neurons, the neuron-specific transcription factors ASCL1, BRN2, MYT1L, and NEUROD1 were ectopically overexpressed in different melanoma cell lines (Figs. 1B, C and S1A, B).</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41233896</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Melanoma is an aggressive skin cancer and highly lethal at advanced stages due to its high tumorigenicity and metastatic capacity. Changing the phenotype of cancer cells from one lineage to another, a process called transdifferentiation, leads to tumor cell reversion, which goes along with a drastic reduction of their tumorigenicity. Via ectopic overexpression of four neuronal transcription factors, we transdifferentiated melanoma cells into neuron-like cells expressing neuronal markers and showing a neuron-like morphology. Moreover, the tumorigenic and metastatic potential of transdifferentiated cells in vitro and in vivo was significantly reduced. Transdifferentiated cells were also more sensitive to radiotherapy compared with their parental counterparts. We conclude that transdifferentiation of cancer cells into terminally differentiated neuron-like cells might represent a prospective new therapeutic approach for the treatment of melanoma.</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
+          <t>We established a direct reprogramming strategy to generate cytotoxic NK cells (1 F-NKs) by targeting BCL11B, a transcription factor essential for T cell lineage commitment, using shRNA or CRISPR/Cas9 in peripheral blood mononuclear cells (PBMCs).</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Pancreatic ductal adenocarcinoma (PDAC) is a lethal malignancy characterized by desmoplastic stroma, immunosuppressive tumor microenvironment (TME), and resistance to standard therapies. Natural killer (NK) cell-based immunotherapies have shown limited efficacy due to impaired persistence, infiltration, and function in PDAC. We established a direct reprogramming strategy to generate cytotoxic NK cells (1 F-NKs) by targeting BCL11B, a transcription factor essential for T cell lineage commitment, using shRNA or CRISPR/Cas9 in peripheral blood mononuclear cells (PBMCs). A genome-wide CRISPR/Cas9 screen identified tumor-intrinsic modulators of NK resistance. Functional and in vivo studies assesses the efficacy of 1 F-NKs alone and in combination with mesothelin (MSLN)-CAR engineering and PKMYT1 inhibition. BCL11B depletion enabled the generation of CD56&lt;sup&gt;bright&lt;/sup&gt;CD16&lt;sup&gt;bright&lt;/sup&gt; 1 F-NKs with potent cytotoxicity and elevated NKG2D and CX3CR1 expression. Site-specific integration of a mesothelin (MSLN)-CAR into BCL11B locus generated MSLN-1 F-NKs with stable antigen specific activity. A genome-wide screen identified PKMYT1 as a modulator of tumor resistance to NK cell-mediated killing; its inhibition by RP6306 upregulated NKG2D ligands (MICA/B) and CX3CL1, sensitizing PDACs to 1 F-NK cytotoxicity. In PDAC xenograft models, 1 F-NKs alone or combined with CAR engineering and RP6306 significantly reduced tumor growth and prolonged survival. Notably, this triple combination elicited a synergistic antitumor effect, outperforming each monotherapy or dual combination. This study presents a synergistic immunotherapy platform that integrates NK reprogramming, CAR engineering, and tumor sensitization. The combinatorial approach significantly enhances antitumor efficacy in PDAC and offers a promising strategy for overcoming immune resistance in solid tumors.</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>BCL11B knockdown (shRNA/CRISPR) in PBMCs generating cytotoxic NK cells — valid direct reprogramming via loss-of-function. Evidence directly describes the strategy and outcome. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3561,32 +4630,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>30635054</t>
+          <t>31489945</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>The therapeutic potential of induced hepatocyte-like cells generated by direct reprogramming on hepatic fibrosis.</t>
+          <t>mRNA-Driven Generation of Transgene-Free Neural Stem Cells from Human Urine-Derived Cells.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>mouse embryonic fibroblast (MEF)</t>
+          <t>human urine-derived cells (hUCs)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>induced hepatocyte-like cells (iHeps)</t>
+          <t>neural stem cells (iNSCs)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>HNF1A, small molecules</t>
+          <t>defined small molecules, self-replicable mRNA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>TF, small_molecule</t>
+          <t>small_molecule, other</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3606,37 +4675,69 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/30635054</t>
-        </is>
-      </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>In this study, we generated iHEPs by direct reprogramming from mouse embryonic fibroblast (MEF) either using specific transcription factors such as c-Myc and Klf-4 (type A), or adding small molecules to HNF1α (type B).</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/31489945</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Until now, there is no effective anti-fibrotic therapy available for liver cirrhosis. Stem cell therapies have been studied for the treatment of hepatic fibrosis. However, the use of embryonic stem cells or induced pluripotent stem cells (iPSC) has limitations such as ethical concern or malignancy potential. Induced hepatocyte-like cells (iHEPs) generated by direct reprogramming technology may overcome these limitations. In this study, we generated iHEPs by direct reprogramming from mouse embryonic fibroblast (MEF) either using specific transcription factors such as c-Myc and Klf-4 (type A), or adding small molecules to HNF1α (type B). We investigated the effect of iHEPs on acute liver injury and chronic hepatic fibrosis animal models induced by CCl&lt;sub&gt;4&lt;/sub&gt; intra-peritoneal injection in BALB/C nude mice. In acute liver injury model, serum AST/ALT levels peaked at 24 h after CCl&lt;sub&gt;4&lt;/sub&gt; injection. Intra-splenic transplantation of iHEPs significantly attenuated CCl&lt;sub&gt;4&lt;/sub&gt;-induced acute liver injury. GFP-labeled iHEPs (type A) migrated to the liver after intra-splenic transplantation that was confirmed by Western blotting and immunofluorescence staining. We found that GFP and albumin were co-localized in migrated iHEPs in the liver suggesting migrated iHEPs were functional. In chronic hepatic fibrosis mice experiment, transplantation of either type A or type B iHEPs significantly attenuated liver fibrosis induced by CCl&lt;sub&gt;4&lt;/sub&gt; injection for 10 weeks. Our study suggests that iHEPs may be used as a novel therapeutic strategy for the treatment of hepatic fibrosis.</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
+          <t>Here, we describe the advanced transgene-free generation of iNSCs from human urine-derived cells (HUCs) by combining a cocktail of defined small molecules with self-replicable mRNA delivery.</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Human neural stem cells (NSCs) hold enormous promise for neurological disorders, typically requiring their expandable and differentiable properties for regeneration of damaged neural tissues. Despite the therapeutic potential of induced NSCs (iNSCs), a major challenge for clinical feasibility is the presence of integrated transgenes in the host genome, contributing to the risk for undesired genotoxicity and tumorigenesis. Here, we describe the advanced transgene-free generation of iNSCs from human urine-derived cells (HUCs) by combining a cocktail of defined small molecules with self-replicable mRNA delivery. The established iNSCs were completely transgene-free in their cytosol and genome and further resembled human embryonic stem cell-derived NSCs in the morphology, biological characteristics, global gene expression, and potential to differentiate into functional neurons, astrocytes, and oligodendrocytes. Moreover, iNSC colonies were observed within eight days under optimized conditions, and no teratomas formed in vivo, implying the absence of pluripotent cells. This study proposes an approach to generate transplantable iNSCs that can be broadly applied for neurological disorders in a safe, efficient, and patient-specific manner.</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>factors_unspecified</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>'Defined small molecules' and 'self-replicable mRNA' are too vague. Specific small molecule cocktail names and mRNA-encoded TFs (likely SOX2, HMGA2 or similar) must be listed. Evidence confirms the approach but factors are underspecified.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3644,32 +4745,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>28587331</t>
+          <t>36581370</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Directly reprogramming fibroblasts into adipogenic, neurogenic and hepatogenic differentiation lineages by defined factors.</t>
+          <t>Generation of Induced Pluripotent Stem Cells from Lymphoblastoid Cell Lines by Electroporation of Episomal Vectors.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>human fibroblast</t>
+          <t>lymphoblastoid cell line</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>neurocyte</t>
+          <t>induced pluripotent stem cell (iPSC)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SOX2, GATA-3, NEUROD1</t>
+          <t>OCT4, SOX2, KLF4, c-MYC</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>TF, TF, TF</t>
+          <t>TF, TF, TF, TF</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3689,37 +4790,69 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t>classical_reprogramming</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/28587331</t>
-        </is>
-      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Similarly, direct reprogramming of the transcription factors sex determining region-box 2, trans-acting T-cell specific transcription factor (GATA-3) and neurogenic differentiation 1 in fibroblasts may induce neurogenic differentiation through hemagglutinating virus of Japan envelope (HVJ-E) transfection.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/36581370</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>The reprogramming of adult cells into pluripotent cells or directly into alternative adult cell types represents a great potential technology for regenerative medicine. In the present study, the potential of key developmental adipogenic, neurogenic and hepatogenic regulators to reprogram human fibroblasts into adipocytes, neurocytes and hepatocytes was investigated. The results demonstrated that direct reprogramming of octamer-binding transcription factor 4 (Oct4) and CCAAT-enhancer-binding protein (C/EBP)β activated C/EBPα and peroxisome proliferator-activated receptor-γ expression, inducing the conversion of fibroblasts into adipocytes. Similarly, direct reprogramming of the transcription factors sex determining region-box 2, trans-acting T-cell specific transcription factor (GATA-3) and neurogenic differentiation 1 in fibroblasts may induce neurogenic differentiation through hemagglutinating virus of Japan envelope (HVJ-E) transfection. Moreover, hepatogenic differentiation was induced by combining the direct reprogramming of Oct4, GATA-3, hepatocyte nuclear factor 1 homeobox α and forkhead box protein A2 in fibroblasts. These results demonstrate that specific transcription factors and reprogramming factors are able to directly reprogram fibroblasts into adipogenic, neurogenic and hepatogenic differentiation lineages by HVJ-E transfection.</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
+          <t>Consequently, lentiviral and retroviral transduction of OCT4, SOX2, KFL4 and c-MYC into LCLs does not elicit iPSC colony formation.</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Lymphoblastoid cell lines (LCLs) deposited from disease-affected individuals could be a valuable donor cell source for generating disease-specific induced pluripotent stem cells (iPSCs). However, generation of iPSCs from the LCLs is still challenging, as yet no effective gene delivery strategy has been developed. Here, we reveal an effective gene delivery method specifically for LCLs. We found that LCLs appear to be refractory toward retroviral and lentiviral transduction. Consequently, lentiviral and retroviral transduction of OCT4, SOX2, KFL4 and c-MYC into LCLs does not elicit iPSC colony formation. Interestingly, however we found that transfection of oriP/EBNA-1-based episomal vectors by electroporation is an efficient gene delivery system into LCLs, enabling iPSC generation from LCLs. These iPSCs expressed pluripotency makers (OCT4, NANOG, SSEA4, SALL4) and could form embryoid bodies. Our data show that electroporation is an effective gene delivery method with which LCLs can be efficiently reprogrammed into iPSCs.</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>evidence_weak</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Evidence sentence explicitly states OSKM does NOT elicit iPSC colony formation from LCLs. This is a negative result — the recipe is recorded as if valid but the evidence proves failure. Entry should be removed or flagged as failed/non-permissive source cell.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3727,32 +4860,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>28853082</t>
+          <t>30018471</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Reprogramming of Human Retinal Pigment Epithelial Cells under the Effect of bFGF In Vitro.</t>
+          <t>Generation of dopamine neuronal-like cells from induced neural precursors derived from adult human cells by non-viral expression of lineage factors.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>human retinal pigment epithelial cells (ARPE-19)</t>
+          <t>human fibroblast</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>neuronal-like cell</t>
+          <t>induced neuron (iN)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>bFGF</t>
+          <t>SHH-C24II, purmorphamine, CHIR99021, FGF8b, LMX1A, FOXA2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>cytokine</t>
+          <t>small_molecule, small_molecule, small_molecule, small_molecule, TF, TF</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3772,37 +4905,69 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/28853082</t>
-        </is>
-      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Immunocytochemical analysis showed that in the presence of bFGF, some cells retained epithelial properties and showed positive staining for connexin-43, while others had long axon-like processes and demonstrated positive staining for βIII-tubulin, which attests to their neuronal transdifferentiation.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/30018471</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>We studied the effect of bFGF on human retinal pigment epithelial cells in vitro In ARPE-19 cells, enhanced expression of KLF4 mRNA and reduced expression of PAX6, MITF, and OTX2 mRNA specific for retinal pigment epithelium were observed after bFGF application. The expression of KLF4 mRNA peaked in 72 h after bFGF application and then sharply decreased, which was accompanied by a 3-fold increase in TUBB3 mRNA expression (neuronal marker). Immunocytochemical analysis showed that in the presence of bFGF, some cells retained epithelial properties and showed positive staining for connexin-43, while others had long axon-like processes and demonstrated positive staining for βIII-tubulin, which attests to their neuronal transdifferentiation. Despite the prevalence of the epithelial properties, ARPE-19 cells under the influence of bFGF can show proneuronal properties.</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
+          <t>Upon differentiation, iNPs gave rise to dopamine neuronal-like cells expressing TUJ1, TH, AADC, DAT, VMAT2 and GIRK2.</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Reprogramming technology holds great promise for the study and treatment of Parkinson's disease (PD) as patient-specific ventral midbrain dopamine (vmDA) neurons can be generated. This should facilitate the investigation of early changes occurring during PD pathogenesis, permitting the identification of new drug targets and providing a platform for drug screening. To date, most studies using reprogramming technology to study PD have employed induced pluripotent stem cells. Research into PD using direct reprogramming has been limited due to an inability to generate high yields of authentic human vmDA neurons. Nevertheless, direct reprogramming offers a number of advantages, and development of this technology is warranted. Previous reports have indicated that induced neural precursors (iNPs) derived from adult human fibroblasts by lineage factor-mediated direct reprogramming can give rise to dopamine neurons expressing tyrosine hydroxylase (TH+). Using normal adult human fibroblasts, the present study aimed to extend these findings and determine the capacity of iNPs for generating vmDA neurons, with the aim of utilising this technology for the future study of PD. While iNPs expressed late vmDA fate markers such as NURR1 and PITX3, critical early regional markers LMX1A, FOXA2 and EN1 were not expressed. Upon differentiation, iNPs gave rise to dopamine neuronal-like cells expressing TUJ1, TH, AADC, DAT, VMAT2 and GIRK2. To induce an authentic A9 phenotype, a series of experiments investigated temporal exposure to patterning factors. Exposure to SHH-C24II, purmorphamine, CHIR99021 and/or FGF8b during or after reprogramming was insufficient to induce expression of early vmDA regional markers. Addition of LMX1A/FOXA2 to the transfection cocktail did not induce a sustained vmDA iNP phenotype. This study reports for the first time that iNPs derived from healthy adult human cells by non-viral expression of lineage factors can give rise to dopamine neuronal-like cells. Direct-to-iNP reprogramming could be a suitable strategy for modelling PD in vitro using aged donor-derived cells.</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>target_synonym</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Target 'induced neuron (iN)' is imprecise — abstract/evidence confirm these are ventral midbrain dopaminergic (vmDA) neurons. Should be 'induced dopaminergic neuron (iDAN)' or 'induced dopaminergic neuron'. SHH+purmorphamine+CHIR+FGF8b+LMX1A+FOXA2 are correct vmDA specification factors.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3810,27 +4975,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>39104117</t>
+          <t>26288179</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Characteristic changes in astrocyte properties during astrocyte-to-neuron conversion induced by NeuroD1/Ascl1/Dlx2.</t>
+          <t>Neurogenin 3 Expressing Cells in the Human Exocrine Pancreas Have the Capacity for Endocrine Cell Fate.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>cortical astrocyte (reactive)</t>
+          <t>acinar and duct cells of human exocrine pancreas</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>neuron</t>
+          <t>insulin-producing cell (β-cell)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NEUROD1</t>
+          <t>Neurogenin 3 (NGN3)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3850,42 +5015,70 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fulltext</t>
+          <t>abstract</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/39104117</t>
-        </is>
-      </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Similar changes in cell identity occurred from 3 dpi to 60 dpi in cells infected with viruses expressing NeuroD1 (Figure 1I) or Dlx2 (Figure 1J).</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/26288179</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>JOURNAL/nrgr/04.03/01300535-202506000-00030/figure1/v/2024-08-05T133530Z/r/image-tiff Direct in vivo conversion of astrocytes into functional new neurons induced by neural transcription factors has been recognized as a potential new therapeutic intervention for neural injury and degenerative disorders. However, a few recent studies have claimed that neural transcription factors cannot convert astrocytes into neurons, attributing the converted neurons to pre-existing neurons mis-expressing transgenes. In this study, we overexpressed three distinct neural transcription factors--NeuroD1, Ascl1, and Dlx2--in reactive astrocytes in mouse cortices subjected to stab injury, resulting in a series of significant changes in astrocyte properties. Initially, the three neural transcription factors were exclusively expressed in the nuclei of astrocytes. Over time, however, these astrocytes gradually adopted neuronal morphology, and the neural transcription factors was gradually observed in the nuclei of neuron-like cells instead of astrocytes. Furthermore, we noted that transcription factor-infected astrocytes showed a progressive decrease in the expression of astrocytic markers AQP4 (astrocyte endfeet signal), CX43 (gap junction signal), and S100β. Importantly, none of these changes could be attributed to transgene leakage into pre-existing neurons. Therefore, our findings suggest that neural transcription factors such as NeuroD1, Ascl1, and Dlx2 can effectively convert reactive astrocytes into neurons in the adult mammalian brain.</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
+          <t>During in vitro differentiation, NGN3+ cells express genes in a pattern characteristic of endocrine development and result in cells that resemble beta cells on the basis of coexpression of insulin C-peptide, chromogranin A and pancreatic and duodenal homeobox 1.</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Neurogenin 3 (NGN3) is necessary and sufficient for endocrine differentiation during pancreatic development and is expressed by a population of progenitor cells that give rise exclusively to hormone-secreting cells within islets. NGN3 protein can be detected in the adult rodent pancreas only following certain types of injury, when it is transiently expressed by exocrine cells undergoing reprogramming to an endocrine cell fate. Here, NGN3 protein can be detected in 2% of acinar and duct cells in living biopsies of histologically normal adult human pancreata and 10% in cadaveric biopsies of organ donor pancreata. The percentage and total number of NGN3+ cells increase during culture without evidence of proliferation or selective cell death. Isolation of highly purified and viable NGN3+ cell populations can be achieved based on coexpression of the cell surface glycoprotein CD133. Transcriptome and targeted expression analyses of isolated CD133+ / NGN3+ cells indicate that they are distinct from surrounding exocrine tissue with respect to expression phenotype and Notch signaling activity, but retain high level mRNA expression of genes indicative of acinar and duct cell function. NGN3+ cells have an mRNA expression profile that resembles that of mouse early endocrine progenitor cells. During in vitro differentiation, NGN3+ cells express genes in a pattern characteristic of endocrine development and result in cells that resemble beta cells on the basis of coexpression of insulin C-peptide, chromogranin A and pancreatic and duodenal homeobox 1. NGN3 expression in the adult human exocrine pancreas marks a dedifferentiating cell population with the capacity to take on an endocrine cell fate. These cells represent a potential source for the treatment of diabetes either through ex vivo manipulation, or in vivo by targeting mechanisms controlling their population size and endocrine cell fate commitment.</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>NGN3 alone is sufficient for endocrine differentiation in pancreatic context — well-established single-TF recipe. Evidence confirms beta cell-like gene expression. Valid standalone single-TF entry.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3893,32 +5086,32 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>29038558</t>
+          <t>37393720</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Prokineticin receptor-1-dependent paracrine and autocrine pathways control cardiac tcf21&lt;sup&gt;+&lt;/sup&gt; fibroblast progenitor cell transformation into adipocytes and vascular cells.</t>
+          <t>Three induced pluripotent stem cell lines (TRNDi033-A, TRNDi034-A, TRNDi035-A) generated from lymphoblasts of three apparently healthy individuals.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tcf21+ cardiac fibroblast progenitor cell</t>
+          <t>human lymphoblast</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>vasculogenic cell</t>
+          <t>induced pluripotent stem cell (iPSC)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>prokineticin-2</t>
+          <t>OCT4, SOX2, KLF4, L-MYC, LIN28</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>cytokine</t>
+          <t>TF, TF, TF, TF, other</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3938,37 +5131,65 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
+          <t>classical_reprogramming</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/29038558</t>
-        </is>
-      </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>We found that prokineticin-2 is a cardiomyocyte secretome that controls CFP transformation into adipocytes and vasculogenic cells in vivo and in vitro.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/37393720</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Cardiac fat tissue volume and vascular dysfunction are strongly associated, accounting for overall body mass. Despite its pathophysiological significance, the origin and autocrine/paracrine pathways that regulate cardiac fat tissue and vascular network formation are unclear. We hypothesize that adipocytes and vasculogenic cells in adult mice hearts may share a common cardiac cells that could transform into adipocytes or vascular lineages, depending on the paracrine and autocrine stimuli. In this study utilizing transgenic mice overexpressing prokineticin receptor (PKR1) in cardiomyocytes, and tcf21ERT-cre&lt;sup&gt;TM&lt;/sup&gt;-derived cardiac fibroblast progenitor (CFP)-specific PKR1 knockout mice (PKR1 &lt;sup&gt;tcf-/-&lt;/sup&gt;), as well as FACS-isolated CFPs, we showed that adipogenesis and vasculogenesis share a common CFPs originating from the tcf21&lt;sup&gt;+&lt;/sup&gt; epithelial lineage. We found that prokineticin-2 is a cardiomyocyte secretome that controls CFP transformation into adipocytes and vasculogenic cells in vivo and in vitro. Upon HFD exposure, PKR1 &lt;sup&gt;tcf-/-&lt;/sup&gt; mice displayed excessive fat deposition in the atrioventricular groove, perivascular area, and pericardium, which was accompanied by an impaired vascular network and cardiac dysfunction. This study contributes to the cardio-obesity field by demonstrating that PKR1 via autocrine/paracrine pathways controls CFP-vasculogenic- and CFP-adipocyte-transformation in adult heart. Our study may open up new possibilities for the treatment of metabolic cardiac diseases and atherosclerosis.</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
+          <t>Expanded human lymphoblast cells from three different aged healthy individuals, 8-year-old male, 0-year-old newborn (NB) male, and 26-year-old female, were used to generate induced pluripotent stem cell (iPSC) lines TRNDi033-A, TRNDi034-A and TRNDi035-A, respectively, by exogenous expression of five reprogramming factors, human OCT4, SOX2, KLF4, L-MYC and LIN28.</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Expanded human lymphoblast cells from three different aged healthy individuals, 8-year-old male, 0-year-old newborn (NB) male, and 26-year-old female, were used to generate induced pluripotent stem cell (iPSC) lines TRNDi033-A, TRNDi034-A and TRNDi035-A, respectively, by exogenous expression of five reprogramming factors, human OCT4, SOX2, KLF4, L-MYC and LIN28. The authenticity of established iPSC lines was confirmed by the expressions of stem cell markers, karyotype analysis, embryoid body formation, and scorecard analysis. These iPSC lines could serve as healthy donor controls that are age and sex matched for the studies involving patient-specific iPSCs.</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>OCT4/SOX2/KLF4/L-MYC/LIN28 reprogramming of human lymphoblasts to iPSCs. Evidence directly describes iPSC generation from age-matched donors. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3976,27 +5197,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20675585</t>
+          <t>34699746</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Efficient reprogramming of adult neural stem cells to monocytes by ectopic expression of a single gene.</t>
+          <t>Temporal proteomics during neurogenesis reveals large-scale proteome and organelle remodeling via selective autophagy.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>adult neural stem cells</t>
+          <t>human embryonic stem cell (hESC)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>monocyte</t>
+          <t>induced neuron (iN)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PU.1</t>
+          <t>NGN2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4021,37 +5242,65 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
+          <t>directed_differentiation</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/20675585</t>
-        </is>
-      </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>We report that adult neural stem cells can be reprogrammed at very high efficiency to monocytes, a differentiated fate of an unrelated somatic lineage, by ectopic expression of the Ets transcription factor PU.1.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/34699746</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Neural stem cells have a broad differentiation repertoire during embryonic development and can be reprogrammed to pluripotency comparatively easily. We report that adult neural stem cells can be reprogrammed at very high efficiency to monocytes, a differentiated fate of an unrelated somatic lineage, by ectopic expression of the Ets transcription factor PU.1. The reprogrammed cells display a marker profile and functional characteristics of monocytes and integrate into tissues after transplantation. The failure to reprogram lineage-committed neural cells to monocytes with PU.1 suggests that neural stem cells are uniquely amenable to reprogramming.</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
+          <t>Here, we show that NGN2-driven conversion of human embryonic stem cells to induced neurons (iNeurons) is associated with increased PINK1-independent mitophagic flux that is temporally correlated with metabolic reprogramming to support oxidative phosphorylation.</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Cell state changes are associated with proteome remodeling to serve newly emergent cell functions. Here, we show that NGN2-driven conversion of human embryonic stem cells to induced neurons (iNeurons) is associated with increased PINK1-independent mitophagic flux that is temporally correlated with metabolic reprogramming to support oxidative phosphorylation. Global multiplex proteomics during neurogenesis revealed large-scale remodeling of functional modules linked with pluripotency, mitochondrial metabolism, and proteostasis. Differentiation-dependent mitophagic flux required BNIP3L and its LC3-interacting region (LIR) motif, and BNIP3L also promoted mitophagy in dopaminergic neurons. Proteomic analysis of ATG12&lt;sup&gt;-/-&lt;/sup&gt; iNeurons revealed accumulation of endoplasmic reticulum, Golgi, and mitochondria during differentiation, indicative of widespread organelle remodeling during neurogenesis. This work reveals broad organelle remodeling of membrane-bound organelles during NGN2-driven neurogenesis via autophagy, identifies BNIP3L's central role in programmed mitophagic flux, and provides a proteomic resource for elucidating how organelle remodeling and autophagy alter the proteome during changes in cell state.</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>NGN2 alone converts hESCs to induced neurons — well-established single-TF recipe (Zhang et al. 2013). Evidence directly describes NGN2-driven conversion to iNeurons. Valid standalone single-TF entry.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4059,32 +5308,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>31976351</t>
+          <t>31488328</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Highly efficient induced pluripotent stem cell reprogramming of cryopreserved lymphoblastoid cell lines.</t>
+          <t>Inducing Different Neuronal Subtypes from Astrocytes in the Injured Mouse Cerebral Cortex.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>cryopreserved lymphoblastoid cell line (LCL)</t>
+          <t>astrocyte</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>induced pluripotent stem cell (iPSC)</t>
+          <t>neuron</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>OCT4, SOX2, KLF4, LMYC, LIN28, mp53DD</t>
+          <t>ASCL1, NURR1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>TF, TF, TF, TF, TF, TF</t>
+          <t>TF, TF</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4104,37 +5353,65 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/31976351</t>
-        </is>
-      </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>For iPSC reprogramming of cryopreserved LCLs, the LCLs are propagated and while still in logarithmic growth phase, nucleofected with episomal plasmids (pCEhOCT3/4, pCE-hSK, pCE-hUL, and pCE-mp53DD), encoding reprogramming factors (i.e., OCT3/4, SOX2, KLF4, LMYC, and LIN28), and a mouse p53 carboxy-terminal dominant-negative fragment using 4D-Nucleofector X Kit and 4D-Nucleofector system.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/31488328</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Tissue culture based &lt;i&gt;in-vitro&lt;/i&gt; experimental modeling of human inherited disorders provides insight into the cellular and molecular mechanisms involved and the underlying genetic component influencing the disease phenotype. The breakthrough development of induced pluripotent stem cell (iPSC) technology represents a quantum leap in experimental modeling of human diseases, providing investigators with a self-renewing and thus unlimited source of pluripotent cells for targeted differentiation into functionally relevant disease specific tissue/cell types. The existing rich bio-resource of Epstein-Barr virus (EBV) immortalized lymphoblastoid cell line (LCL) repositories generated from a wide array of patients in genetic and epidemiological studies worldwide, many of them with extensive genotypic, genomic and phenotypic data already existing, provides a great opportunity to reprogram iPSCs from any of these LCL donors in the context of their own genetic identity for disease modeling and disease gene identification. However, due to the low reprogramming efficiency and poor success rate of LCL to iPSC reprogramming, these LCL resources remain severely underused for this purpose. Here, we detailed step-by-step instructions to perform our highly efficient LCL-to-iPSC reprogramming protocol using EBNA1/OriP episomal plasmids encoding pluripotency transcription factors (&lt;i&gt;i.e.&lt;/i&gt;, OCT3/4, SOX2, KLF4, L-MYC, and LIN28), mouse p53DD (p53 carboxy-terminal dominant-negative fragment) and commercially available reprogramming media. We achieved a consistently high reprogramming efficiency and 100% success rate (&gt; 200 reprogrammed iPSC lines) using this protocol.</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
+          <t>Interestingly, injection of AAV-FLEx-Nurr1 alone showed low efficiency in neuronal induction (about 20% iNs; Figure S2A), indicating that the combination of a proneural factor, either Ngn2 or Ascl1, with Nurr1 is particularly efficient in astrocytes to neuron conversion.</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Astrocytes are particularly promising candidates for reprogramming into neurons, as they maintain some of the original patterning information from their radial glial ancestors. However, to which extent the position of astrocytes influences the fate of reprogrammed neurons remains unknown. To elucidate this, we performed stab wound injury covering an entire neocortical column, including the gray matter (GM) and white matter (WM), and targeted local reactive astrocytes via injecting FLEx switch (Cre-On) adeno-associated viral (AAV) vectors into mGFAP-Cre mice. Single proneural factors were not sufficient for adequate reprogramming, although their combination with the nuclear receptor-related 1 protein (Nurr1) improved reprogramming efficiency. Nurr1 and Neurogenin 2 (Ngn2) resulted in high-efficiency reprogramming of targeted astrocytes into neurons that develop lamina-specific hallmarks, including the appropriate long-distance axonal projections. Surprisingly, in the WM, we did not observe any reprogrammed neurons, thereby unveiling a crucial role of region- and layer-specific differences in astrocyte reprogramming.</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>ASCL1+NURR1 reprogramming of astrocytes to neurons. Evidence notes NURR1 alone had low efficiency (~20%), confirming the combination is the effective recipe. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4142,32 +5419,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>33718351</t>
+          <t>36581367</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sall4 and Myocd Empower Direct Cardiac Reprogramming From Adult Cardiac Fibroblasts After Injury.</t>
+          <t>Inhibition of Class I Histone Deacetylase Enhances Self-Reprogramming of Spermatogonial Stem Cells into Pluripotent Stem Cells.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>adult cardiac fibroblast (ACF)</t>
+          <t>spermatogonial stem cell (SSC)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>cardiomyocyte-like cell (iCM)</t>
+          <t>germline-derived pluripotent stem cell (gPSC)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>GATA4, MEF2C, TBX5</t>
+          <t>CI-994</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>TF, TF, TF</t>
+          <t>small_molecule</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4187,37 +5464,65 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/33718351</t>
-        </is>
-      </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>For NCFs and ACFs reprogramming, many mCherry+ cells were observed after a 3 week induction and some mCherry-negative cells also expressed cardiac troponin I (cTnI) and cardiac troponin T (cTnT) in the two kinds of fibroblasts (Figures 1B,C and Supplementary Figure 4).</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/36581367</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Direct conversion of fibroblasts into induced cardiomyocytes (iCMs) holds promising potential to generate functional cardiomyocytes for drug development and clinical applications, especially for direct &lt;i&gt;in situ&lt;/i&gt; heart regeneration by delivery of reprogramming genes into adult cardiac fibroblasts in injured hearts. For a decade, many cocktails of transcription factors have been developed to generate iCMs from fibroblasts of different tissues &lt;i&gt;in vitro&lt;/i&gt; and some were applied &lt;i&gt;in vivo&lt;/i&gt;. Here, we aimed to develop genetic cocktails that induce cardiac reprogramming directly in cultured cardiac fibroblasts isolated from adult mice with myocardial infarction (MICFs), which could be more relevant to heart diseases. We found that the widely used genetic cocktail, Gata4, Mef2c, and Tbx5 (GMT) were inefficient in reprogramming cardiomyocytes from MICFs. In a whole well of a 12-well plate, less than 10 mCherry&lt;sup&gt;+&lt;/sup&gt; cells (&lt;0.1%) were observed after 2 weeks of GMT infection with &lt;i&gt;Myh6&lt;/i&gt;-reporter transgenic MICFs. By screening 22 candidate transcription factors predicted through analyzing the gene regulatory network of cardiac development, we found that five factors, GMTMS (GMT plus Myocd and Sall4), induced more iCMs expressing the cardiac structural proteins cTnT and cTnI at a frequency of about 22.5 ± 2.7% of the transduced MICFs at day 21 post infection. What is more, GMTMS induced abundant beating cardiomyocytes at day 28 post infection. Specifically, Myocd contributed mainly to inducing the expression of cardiac proteins, while Sall4 accounted for the induction of functional properties, such as contractility. RNA-seq analysis of the iCMs at day 28 post infection revealed that they were reprogrammed to adopt a cardiomyocyte-like gene expression profile. Overall, we show here that Sall4 and Myocd play important roles in cardiac reprogramming from MICFs, providing a cocktail of genetic factors that have potential for further applications in &lt;i&gt;in vivo&lt;/i&gt; cardiac reprogramming.</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
+          <t>The Oct4-GFP-positive gPSC population increased in CI-994, a HDAC class I inhibitor, -treatedSSCs (Supplementary Fig. S1).</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Spermatogonial stem cells (SSCs) are the most primitive cells in spermatogenesis and are the only adult stem cells capable of passing on the genome of a given species to the next generation. SSCs are the only adult stem cells known to exhibit high Oct4 expression and can be induced to self-reprogram into pluripotent cells depending on culture conditions. Epigenetic modulation is well known to be involved in the induction of pluripotency of somatic cells. However, epigenetic modulation in self-reprogramming of SSCs into pluripotent cells has not been studied. In this study, we examined the involvement of epigenetic modulation by assessing whether self-reprogramming of SSCs is enhanced by treatment with epigenetic modulators. We found that second-generation selective class I HDAC inhibitors increased SSC reprogramming efficiency, whereas non-selective HDAC inhibitors had no effect. We showed that pluripotent stem cells derived from adult SSCs by treatment with small molecules with epigenetic modulator functions exhibit pluripotency &lt;i&gt;in vitro&lt;/i&gt; and &lt;i&gt;in vivo&lt;/i&gt;. Our results suggest that the mechanism of SSC reprogramming by epigenetic modulator can be used for important applications in epigenetic reprogramming research.</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>CI-994 (HDAC class I inhibitor) promoting SSC→gPSC conversion. Evidence describes increased Oct4-GFP+ gPSC population. Chemical reprogramming of SSCs to pluripotent state is valid. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4225,32 +5530,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>37856222</t>
+          <t>31806618</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Localized T3 production modifies the transcriptome and promotes the hepatocyte-like lineage in iPSC-derived hepatic organoids.</t>
+          <t>NANOG and LIN28 dramatically improve human cell reprogramming by modulating LIN41 and canonical WNT activities.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>primary mesenchymal stem cells (MSCs)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>induced pluripotent stem cell (iPSC)</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>hepatic organoid (hepatocyte and cholangiocyte)</t>
-        </is>
-      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>BMP4, BMP7, FGF7, CHIR99021</t>
+          <t>OCT4, SOX2, KLF4, MYC, NANOG</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>cytokine, cytokine, cytokine, small_molecule</t>
+          <t>TF, TF, TF, TF, TF</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4270,37 +5575,69 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
+          <t>classical_reprogramming</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/37856222</t>
-        </is>
-      </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>On day 10, the 2D cultures were disrupted by dissociation, and subsequently, the cells self-reestablished into a 3D structure that grew progressively under stimulation of key reagents in the differentiation cocktails — i.e., BMP4, BMP7, FGF7, and the WNT agonist CHIR99021 — to promote the hepatic specification (Figure 1D) (17).</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/31806618</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Thyroid hormone (TH) levels are low during development, and the deiodinases control TH signaling through tissue-specific activation or inactivation of TH. Here, we studied human induced pluripotent stem cell-derived (iPSC-derived) hepatic organoids and identified a robust induction of DIO2 expression (the deiodinase that activates T4 to T3) that occurs in hepatoblasts. The surge in DIO2-T3 (the deiodinase that activates thyroxine [T4] to triiodothyronine [T3]) persists until the hepatoblasts differentiate into hepatocyte- or cholangiocyte-like cells, neither of which expresses DIO2. Preventing the induction of the DIO2-T3 signaling modified the expression of key transcription factors, decreased the number of hepatocyte-like cells by ~60%, and increased the number of cholangiocyte-like cells by ~55% without affecting the growth or the size of the mature liver organoid. Physiological levels of T3 could not fully restore the transition from hepatoblasts to mature cells. This indicates that the timed surge in DIO2-T3 signaling critically determines the fate of developing human hepatoblasts and the transcriptome of the maturing hepatocytes, with physiological and clinical implications for how the liver handles energy substrates.</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
+          <t>The applications of GLIS1, NANOG or LIN28 each improved the reprogramming efficiency of human MSCs compared with OSKM, albeit with less efficiency than the GNL combined (Fig. 1E,F).</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Human cell reprogramming remains extremely inefficient and the underlying mechanisms by different reprogramming factors are elusive. We found that NANOG and LIN28 (NL) synergize to improve OCT4, SOX2, KLF4 and MYC (OSKM)-mediated reprogramming by ∼76-fold and shorten reprogramming latency by at least 1 week. This synergy is inhibited by GLIS1 but reinforced by an inhibitor of the histone methyltransferase DOT1L (iDOT1L) to a ∼127-fold increase in TRA-1-60-positive (+) iPSC colonies. Mechanistically, NL serve as the main drivers of reprogramming in cell epithelialization, the expression of Let-7 miRNA target &lt;i&gt;LIN41&lt;/i&gt;, and the activation of canonical WNT/β-CATENIN signaling, which can be further enhanced by iDOT1L treatment. &lt;i&gt;LIN41&lt;/i&gt; overexpression in addition to OSKM similarly promoted cell epithelialization and WNT activation in reprogramming, and a dominant-negative LIN41 mutation significantly blocked NL- and iDOT1L-enhanced reprogramming. We also found that NL- and iDOT1L-induced canonical WNT activation facilitates the initial development kinetics of iPSCs. However, a substantial increase in more mature, homogeneous TRA-1-60+ colony formation was achieved by inhibiting WNT activity at the middle-to-late-reprogramming stage. We further found that LIN41 can replace LIN28 to synergize with NANOG, and that the coexpression of LIN41 with NL further enhanced the formation of mature iPSCs under WNT inhibition. Our study established LIN41 and canonical WNT signaling as the key downstream effectors of NL for the dramatic improvement in reprogramming efficiency and kinetics, and optimized a condition for the robust formation of mature human iPSC colonies from primary cells.This article has an associated First Person interview with the first author of the paper.</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>evidence_weak</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Same paper as rows 1 and 4. Evidence sentence shows NANOG individually improves OSKM efficiency but with less efficiency than GNL combined — NANOG is tested as an enhancer, not standalone. Needs a sentence confirming OSKM+NANOG iPSC colony formation.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4308,27 +5645,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>35538505</t>
+          <t>37272627</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mouse mesoderm-specific transcript inhibits adipogenic differentiation and induces trans-differentiation into hepatocyte-like cells in 3T3-L1 preadiocytes.</t>
+          <t>Tbx5 overexpression in embryoid bodies increases TAK1 expression but does not enhance the differentiation of sinoatrial node cardiomyocytes.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3T3-L1 preadipocyte</t>
+          <t>mouse embryonic stem cell (mESC)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>hepatocyte</t>
+          <t>sinoatrial node cardiomyocyte</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mest</t>
+          <t>TBX5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -4353,37 +5690,69 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
+          <t>directed_differentiation</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/35538505</t>
-        </is>
-      </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Further, Mest induced trans-differentiation of 3T3-L1 cells into hepatocytes, and its overexpression induced the expression of hepatocyte marker genes, including albumin and α-fetoprotein.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/37272627</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>The mesoderm-specific transcript (Mest) is an imprinted gene that is transcribed from the paternal allele. It is a marker of adipose tissue expansion; however, it is uncertain whether Mest expression promotes or suppresses adipogenic differentiation. To elucidate the effects of Mest expression on adipogenic differentiation, we transfected an expression vector or siRNA for mouse Mest into 3T3-L1 mouse preadipocyte cell line. In differentiated 3T3-L1 adipocytes, Mest overexpression decreased lipid accumulation. Conversely, gene silencing of Mest increased the accumulation of lipid droplets in adipocytes. These results demonstrate that Mest negatively regulates adipocyte differentiation. Further, Mest induced trans-differentiation of 3T3-L1 cells into hepatocytes, and its overexpression induced the expression of hepatocyte marker genes, including albumin and α-fetoprotein. In the presence of dexamethasone, the forced expression of the Mest caused morphological changes in 3T3-L1 cells. Cells were flat and polygonal shapes, with an increased accumulation of intracellular glycogen and other features that are typical of hepatocytes. Therefore, Mest inhibits adipogenic differentiation of 3T3-L1 preadipocytes by inducing hepatocyte trans-differentiation.</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr"/>
+          <t>As an initial test of each cell line's potential to differentiate into SAN cardiomyocytes, each mES cell line was differentiated as EBs and treated with increasing doses of DOX (0-500 ng/ml) (Fig. 1C).</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Genetic studies place Tbx5 at the apex of the sinoatrial node (SAN) transcriptional program. To understand its role in SAN differentiation, clonal embryonic stem (ES) cell lines were made that conditionally overexpress Tbx5, Tbx3, Tbx18, Shox2, Islet-1, and MAP3k7/TAK1. Cardiac cells differentiated using embryoid bodies (EBs). EBs overexpressing Tbx5, Islet1, and TAK1 beat faster than cardiac cells differentiated from control ES cell lines, suggesting possible roles in SAN differentiation. Tbx5 overexpressing EBs showed increased expression of TAK1, but cardiomyocytes did not differentiate as SAN cells. EBs showed no change in the expression of the SAN transcription factors Shox2 and Islet1 and decreased expression of the SAN channel protein HCN4. EBs constitutively overexpressing TAK1 direct cardiac differentiation to the SAN fate but have reduced phosphorylation of its targets, p38 and Jnk. This opens the possibility that blocking the phosphorylation of TAK1 targets may have the same impact as forced overexpression. To test this, we treated EBs with 5z-7-Oxozeanol (OXO), an inhibitor of TAK1 phosphorylation. Like TAK1 overexpressing cardiac cells, cardiomyocytes differentiated in the presence of OXO beat faster and showed increased expression of SAN genes (Shox2, HCN4, and Islet1). This suggests that activation of the SAN transcriptional network can be accomplished by blocking the phosphorylation of TAK1.</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>no_member_of_larger_recipe</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>single_tf_incomplete;evidence_weak</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>hide_single_tf</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>TBX5 is part of the GMT cardiac reprogramming cocktail; it is not a standalone SAN differentiation factor from mESCs. Evidence sentence describes initial dose-testing of EB differentiation, not a confirmed single-TF conversion outcome. Should be hidden as member of larger GMT recipe.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4391,32 +5760,32 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>40913769</t>
+          <t>39540462</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chemogenetic tuning reveals optimal MAPK signaling for cell-fate programming.</t>
+          <t>Age-associated metabolic and epigenetic barriers during direct reprogramming of mouse fibroblasts into induced cardiomyocytes.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>mouse embryonic fibroblast (MEF)</t>
+          <t>adult skin dermal ear-derived fibroblast (AEF) from 4-6 month old mice</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>motor neuron</t>
+          <t>cardiomyocyte</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>NGN2, Isl1, Lhx3, p53DD, HRASG12V, RepSox</t>
+          <t>MEF2C, GATA4, TBX5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>TF, TF, TF, other, other, small_molecule</t>
+          <t>TF, TF, TF</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4436,37 +5805,65 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/40913769</t>
-        </is>
-      </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>In this model system, the transduction of mouse embryonic fibroblasts with a single cassette of transcription factors (Ngn2, Isl1, and Lhx3 [NIL]) drives their conversion to motor neurons (Figure 1B).</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/39540462</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Cell states evolve through the combined activity of signaling pathways and gene networks. While transcription factors can direct cell fate, these factors rely on a receptive cell state. How signaling levels contribute to the emergence of receptive cell states remains poorly defined. Using a well-defined model of direct conversion, we examined how levels of the mitogen-activated protein kinase (MAPK)-activating oncogene HRAS&lt;sup&gt;G12V&lt;/sup&gt; influence direct conversion of primary fibroblasts to induced motor neurons. The rates of direct conversion respond biphasically to increasing HRAS&lt;sup&gt;G12V&lt;/sup&gt; levels. An optimal "Goldilocks" level of MAPK signaling efficiently drives cell-fate programming, whereas high levels of HRAS&lt;sup&gt;G12V&lt;/sup&gt; induce senescence. Through chemogenetic tuning, we set the optimal MAPK activity for high rates of conversion in the absence of HRAS mutants. In addition to proliferation, MAPK signaling influences conversion by regulating Ngn2 activity. Our results highlight the need to tune therapeutic interventions within a non-monotonic landscape that is shaped by genetics and levels of gene expression.</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
+          <t>We used mouse embryonic fibroblasts (MEFs) and adult skin dermal ear‐derived fibroblasts (AEFs) from adult C57BL/6J mice from different ages (4–6 or 12 months old) for retrovirus‐induced transduction of the cardiogenic factors Mef2c, Gata4, and Tbx5 (hereafter referred to as MGT) (Wang et al., 2015) or empty backbone (mock), followed by puromycin selection (Figure 1a).</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Heart disease is the leading cause of mortality in developed countries, and novel regenerative procedures are warranted. Direct cardiac conversion (DCC) of adult fibroblasts can create induced cardiomyocytes (iCMs) for gene and cell-based heart therapy, and in addition to holding great promise, still lacks effectiveness as metabolic and age-associated barriers remain elusive. Here, by employing MGT (Mef2c, Gata4, Tbx5) transduction of mouse embryonic fibroblasts (MEFs) and adult (dermal and cardiac) fibroblasts from animals of different ages, we provide evidence that the direct reprogramming of fibroblasts into iCMs decreases with age. Analyses of histone posttranslational modifications and ChIP-qPCR revealed age-dependent alterations in the epigenetic landscape of DCC. Moreover, DCC is accompanied by profound mitochondrial metabolic adaptations, including a lower abundance of anabolic metabolites, network remodeling, and reliance on mitochondrial respiration. In vitro metabolic modulation and dietary manipulation in vivo improve DCC efficiency and are accompanied by significant alterations in histone marks and mitochondrial homeostasis. Importantly, adult-derived iCMs exhibit increased accumulation of oxidative stress in the mitochondria and activation of mitophagy or dietary lipids; they improve DCC and revert mitochondrial oxidative damage. Our study provides evidence that metaboloepigenetics plays a direct role in cell fate transitions driving DCC, highlighting the potential use of metabolic modulation to improve cardiac regenerative strategies.</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>GMT (MEF2C, GATA4, TBX5) direct cardiac conversion of adult skin fibroblasts (AEFs) from 4-6 month old mice. Evidence describes retroviral transduction of AEFs and MEFs. All fields correct.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4474,32 +5871,32 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>26732729</t>
+          <t>27109421</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>miR-124-9-9* potentiates Ascl1-induced reprogramming of cultured Müller glia.</t>
+          <t>Resveratrol Exerts Dosage-Dependent Effects on the Self-Renewal and Neural Differentiation of hUC-MSCs.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Müller glia</t>
+          <t>mesenchymal stem cell (MSC)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>retinal neuron</t>
+          <t>neural-lineage cell</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>miR-124-9-9*</t>
+          <t>Resveratrol</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>miRNA</t>
+          <t>small_molecule</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4519,37 +5916,69 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/26732729</t>
-        </is>
-      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>The aim of this study was to test whether (1) lentiviral gene transfer of miR-124-9-9* can reprogram Müller glia into retinal neurons and (2) miR-124-9-9* can improve Ascl1-induced reprogramming.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/27109421</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>The Müller glia of fish provide a source for neuronal regeneration after injury, but they do not do so in mammals. We previously showed that lentiviral gene transfer of the transcription factor Achaete-scute homolog 1 (Ascl1/Mash1) in murine Müller glia cultures resulted in partial reprogramming of the cells to retinal progenitors. The microRNAs (miRNAs) miR-124-9-9* facilitate neuronal reprogramming of fibroblasts, but their role in glia reprogramming has not been reported. The aim of this study was to test whether (1) lentiviral gene transfer of miR-124-9-9* can reprogram Müller glia into retinal neurons and (2) miR-124-9-9* can improve Ascl1-induced reprogramming. Primary Müller glia cultures were generated from postnatal day (P) 11/12 mice, transduced with lentiviral particles, i.e., miR-124-9-9*-RFP, nonsense-RFP, Ascl1-GFP, or GFP-control. Gene expression and immunofluorescence analyses were performed within 3 weeks after infection. 1. Overexpression of miR-124-9-9* induced the expression of the proneural factor Ascl1 and additional markers of neurons, including TUJ1 and MAP2. 2. When Ascl1 and miR-124-9-9* were combined, 50 to 60% of Müller glia underwent neuronal reprogramming, whereas Ascl1 alone results in a 30 to 35% reprogramming rate. 3. Analysis of the miR-124-9-9* treated glial cells showed a reduction in the level of Ctdsp1 and Ptbp1, indicating a critical role for the REST pathway in the repression of neuronal genes in Müller glia. Our data further suggest that miR-124-9-9* and the REST complex may play a role in regulating the reprogramming of Müller glia to progenitors that underlies retinal regeneration in zebrafish.</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr"/>
+          <t>Furthermore, RES could promote neural differentiation in a dose-dependent manner as evidenced by morphological changes and expression of neural markers (Nestin, βIII-tubulin and NSE), as well as pro-neural transcription factors Neurogenin (Ngn)1, Ngn2 and Mash1.</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Resveratrol (RES) plays a critical role in the fate of cells and longevity of animals via activation of the sirtuins1 (SIRT1) gene. In the present study, we intend to investigate whether RES could promote the self-renewal and neural-lineage differentiation in human umbilical cord derived MSCs (hUC-MSCs) in vitro at concentrations ranging from 0.1 to 10 μM, and whether it exerts the effects by modulating the SIRT1 signaling. Herein, we demonstrated that RES at the concentrations of 0.1, 1 and 2.5 μM could promote cell viability and proliferation, mitigate senescence and induce expression of SIRT1 and Proliferating Cell Nuclear Antigen (PCNA) while inhibit the expression of p53 and p16. However, the effects were reversed by 5 and 10 μM of RES. Furthermore, RES could promote neural differentiation in a dose-dependent manner as evidenced by morphological changes and expression of neural markers (Nestin, βIII-tubulin and NSE), as well as pro-neural transcription factors Neurogenin (Ngn)1, Ngn2 and Mash1. Taken together, RES exerts a dosage-dependent effect on the self-renewal and neural differentiation of hUC-MSCs via SIRT1 signaling. The current study provides a new strategy to regulate the fate of hUC-MSCs and suggests a more favorable in vitro cell culture conditions for hUC-MSCs-based therapies for some intractable neurological disorders.</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>evidence_weak</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>Resveratrol promoting neural differentiation of MSCs is plausible (SIRT1 pathway). Evidence describes morphological changes and neural marker expression — modest evidence. Target 'neural-lineage cell' is vague; should specify neuron vs. NPC.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4557,32 +5986,32 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>31489945</t>
+          <t>38817352</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>mRNA-Driven Generation of Transgene-Free Neural Stem Cells from Human Urine-Derived Cells.</t>
+          <t>A chemical approach facilitates CRISPRa-only human iPSC generation and minimizes the number of targeted loci required.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>human urine-derived cells (hUCs)</t>
+          <t>somatic cell</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>neural stem cells (iNSCs)</t>
+          <t>induced pluripotent stem cell (iPSC)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>defined small molecules, self-replicable mRNA</t>
+          <t>CRISPRa (guide RNAs), small molecule cocktail (CRISPRa-SM)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>small_molecule, other</t>
+          <t>other, small_molecule</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4602,37 +6031,69 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
+          <t>classical_reprogramming</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/31489945</t>
-        </is>
-      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Here, we describe the advanced transgene-free generation of iNSCs from human urine-derived cells (HUCs) by combining a cocktail of defined small molecules with self-replicable mRNA delivery.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/38817352</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Human neural stem cells (NSCs) hold enormous promise for neurological disorders, typically requiring their expandable and differentiable properties for regeneration of damaged neural tissues. Despite the therapeutic potential of induced NSCs (iNSCs), a major challenge for clinical feasibility is the presence of integrated transgenes in the host genome, contributing to the risk for undesired genotoxicity and tumorigenesis. Here, we describe the advanced transgene-free generation of iNSCs from human urine-derived cells (HUCs) by combining a cocktail of defined small molecules with self-replicable mRNA delivery. The established iNSCs were completely transgene-free in their cytosol and genome and further resembled human embryonic stem cell-derived NSCs in the morphology, biological characteristics, global gene expression, and potential to differentiate into functional neurons, astrocytes, and oligodendrocytes. Moreover, iNSC colonies were observed within eight days under optimized conditions, and no teratomas formed in vivo, implying the absence of pluripotent cells. This study proposes an approach to generate transplantable iNSCs that can be broadly applied for neurological disorders in a safe, efficient, and patient-specific manner.</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
+          <t>We explored the generation of human induced pluripotent stem cells (iPSCs) solely through the transcriptional activation of endogenous genes by CRISPR activation (CRISPRa).</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Aim:&lt;/b&gt; We explored the generation of human induced pluripotent stem cells (iPSCs) solely through the transcriptional activation of endogenous genes by CRISPR activation (CRISPRa). &lt;b&gt;Methods:&lt;/b&gt; Minimal number of human-specific guide RNAs targeting a limited set of loci were used with a unique cocktail of small molecules (CRISPRa-SM). &lt;b&gt;Results:&lt;/b&gt; iPSC clones were efficiently generated by CRISPRa-SM, expressed general and naive iPSC markers and clustered with high-quality iPSCs generated using conventional reprogramming methods. iPSCs showed genomic stability and robust pluripotent potential as assessed by &lt;i&gt;in vitro&lt;/i&gt; and &lt;i&gt;in vivo&lt;/i&gt;. &lt;b&gt;Conclusion:&lt;/b&gt; CRISPRa-SM-generated human iPSCs by direct and multiplexed loci activation facilitating a unique and potentially safer cellular reprogramming process to aid potential applications in cellular therapy and regenerative medicine.</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>factors_unspecified</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>CRISPRa targeting endogenous pluripotency genes is a valid approach, but 'guide RNAs' and 'small molecule cocktail' are too vague. Specific gRNA targets (e.g., OCT4, SOX2, KLF4) and SM names needed. Source 'somatic cell' is too generic.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4640,32 +6101,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>27874233</t>
+          <t>22833560</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Induction of hepatocyte-like cells from human umbilical cord-derived mesenchymal stem cells by defined microRNAs.</t>
+          <t>Placenta to cartilage: direct conversion of human placenta to chondrocytes with transformation by defined factors.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>mesenchymal stem cell (MSC)</t>
+          <t>smooth chorion and decidua-derived cells</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>hepatocyte-like cell</t>
+          <t>chondrocyte-like cells</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>miR-122, miR-1246, miR-1290, miR-148a, miR-424, miR-542-5p</t>
+          <t>BCL6, T, c-MYC, MITF, BAF60C</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>miRNA</t>
+          <t>TF, TF, TF, TF, TF</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4685,37 +6146,69 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/27874233</t>
-        </is>
-      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>These results demonstrated that 6mix‐without‐miR‐30a set successfully induced hepatic differentiation of hMSCs, which demonstrated miR‐30a was dispensable for the induction of HLCs.</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/22833560</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Generating functional hepatocyte-like cells (HLCs) from mesenchymal stem cells (MSCs) is of great urgency for bio-artificial liver support system (BALSS). Previously, we obtained HLCs from human umbilical cord-derived MSCs by overexpressing seven microRNAs (HLC-7) and characterized their liver functions in vitro and in vivo. Here, we aimed to screen out the optimal miRNA candidates for hepatic differentiation. We sequentially removed individual miRNAs from the pool and examined the effect of transfection with remainder using RT-PCR, periodic acid-Schiff (PAS) staining and low-density lipoprotein (LDL) uptake assays and by assessing their function in liver injury models. Surprisingly, miR-30a and miR-1290 were dispensable for hepatic differentiation. The remaining five miRNAs (miR-122, miR-148a, miR-424, miR-542-5p and miR-1246) are essential for this process, because omitting any one from the five-miRNA combination prevented hepatic trans-differentiation. We found that HLCs trans-differentiated from five microRNAs (HLC-5) expressed high level of hepatic markers and functioned similar to hepatocytes. Intravenous transplantation of HLC-5 into nude mice with CCl&lt;sub&gt;4&lt;/sub&gt; -induced fulminant liver failure and acute liver injury not only improved serum parameters and their liver histology, but also improved survival rate of mice in severe hepatic failure. These data indicated that HLC-5 functioned similar to HLC-7 in vitro and in vivo, which have been shown to resemble hepatocytes. Instead of using seven-miRNA combination, a simplified five-miRNA combination can be used to obtain functional HLCs in only 7 days. Our study demonstrated an optimized and efficient method for generating functional MSC-derived HLCs that may serve as an attractive cell alternative for BALSS.</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr"/>
+          <t>Smooth chorion- and decidua-derived cells were used to investigate chondrogenesis by direct reprogramming.</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Cellular differentiation and lineage commitment are considered to be robust and irreversible processes during development. Recent work has shown that mouse and human fibroblasts can be reprogrammed to a pluripotent state with a combination of four transcription factors. We hypothesized that combinatorial expression of chondrocyte-specific transcription factors could directly convert human placental cells into chondrocytes. Starting from a pool of candidate genes, we identified a combination of only five genes (5F pool)-BCL6, T (also called BRACHYURY), c-MYC, MITF, and BAF60C (also called SMARCD3)-that rapidly and efficiently convert postnatal human chorion and decidual cells into chondrocytes. The cells generated expressed multiple cartilage-specific genes, such as Collagen type II α1, LINK PROTEIN-1, and AGGRECAN, and exhibited characteristics of cartilage both in vivo and in vitro. Expression of the endogenous genes for T and MITF was initiated, implying that the cell conversion is due to not only the forced expression of the transgenes, but also to cellular reprogramming by the transgenes. This direct conversion system from noncartilage tissue to cartilaginous tissue is a substantial advance toward understanding cartilage development, cell-based therapy, and oncogenesis of chondrocytes.</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>evidence_weak</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Evidence sentence is a methods/intent statement ('were used to investigate'), not a result. BCL6, T (Brachyury), c-MYC, MITF, BAF60C for chondrogenesis is an unusual combination (MITF is typically melanocyte-associated). Needs evidence sentence showing chondrocyte marker expression.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4728,7 +6221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4779,25 +6272,40 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>conversion_scope</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>single_tf_flag</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>is_duplicate</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>duplicate_reason</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>preferred_pmid</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>pubmed_url</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>evidence_sentence</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>abstract</t>
         </is>
@@ -4826,7 +6334,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>pluripotent state</t>
+          <t>induced pluripotent stem cell (iPSC)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -4851,25 +6359,30 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>classical_reprogramming</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/32016422</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Deletion of the RBM does not affect selection of target genes but mitigates binding to pluripotency related transcripts, switches exon usage and impairs the reprogramming of somatic cells to a pluripotent state.</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Some transcription factors that specifically bind double-stranded DNA appear to also function as RNA-binding proteins. Here, we demonstrate that the transcription factor Sox2 is able to directly bind RNA in vitro as well as in mouse and human cells. Sox2 targets RNA via a 60-amino-acid RNA binding motif (RBM) positioned C-terminally of the DNA binding high mobility group (HMG) box. Sox2 can associate with RNA and DNA simultaneously to form ternary RNA/Sox2/DNA complexes. Deletion of the RBM does not affect selection of target genes but mitigates binding to pluripotency related transcripts, switches exon usage and impairs the reprogramming of somatic cells to a pluripotent state. Our findings designate Sox2 as a multi-functional factor that associates with RNA whilst binding to cognate DNA sequences, suggesting that it may co-transcriptionally regulate RNA metabolism during somatic cell reprogramming.</t>
         </is>
@@ -4898,7 +6411,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>cardiomyocyte-like state</t>
+          <t>cardiomyocyte</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4923,25 +6436,30 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/37421991</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Addition of FGF2 and XAV939 to the MST cocktail resulted in reprogrammed cells with spontaneous contraction and cardiomyocyte-like calcium transients.</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>The reprogramming of somatic cells to a spontaneously contracting cardiomyocyte-like state using defined transcription factors has proven successful in mouse fibroblasts. However, this process has been less successful in human cells, thus limiting the potential clinical applicability of this technology in regenerative medicine. We hypothesized that this issue is due to a lack of cross-species concordance between the required transcription factor combinations for mouse and human cells. To address this issue, we identified novel transcription factor candidates to induce cell conversion between human fibroblasts and cardiomyocytes, using the network-based algorithm Mogrify. We developed an automated, high-throughput method for screening transcription factor, small molecule, and growth factor combinations, utilizing acoustic liquid handling and high-content kinetic imaging cytometry. Using this high-throughput platform, we screened the effect of 4960 unique transcription factor combinations on direct conversion of 24 patient-specific primary human cardiac fibroblast samples to cardiomyocytes. Our screen revealed the combination of MYOCD, SMAD6, and TBX20 (MST) as the most successful direct reprogramming combination, which consistently produced up to 40% TNNT2&lt;sup&gt;+&lt;/sup&gt; cells in just 25 days. Addition of FGF2 and XAV939 to the MST cocktail resulted in reprogrammed cells with spontaneous contraction and cardiomyocyte-like calcium transients. Gene expression profiling of the reprogrammed cells also revealed the expression of cardiomyocyte associated genes. Together, these findings indicate that cardiac direct reprogramming in human cells can be achieved at similar levels to those attained in mouse fibroblasts. This progress represents a step forward towards the clinical application of the cardiac direct reprogramming approach.</t>
         </is>
@@ -4995,25 +6513,40 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>lineage_conversion</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>same_recipe;preprint_peer_review</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>37421991</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/36993577</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Addition of FGF2 and XAV939 to the MST cocktail resulted in reprogrammed cells with spontaneous contraction and cardiomyocyte-like calcium transients.</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>The reprogramming of somatic cells to a spontaneously contracting cardiomyocyte-like state using defined transcription factors has proven successful in mouse fibroblasts. However, this process has been less successful in human cells, thus limiting the potential clinical applicability of this technology in regenerative medicine. We hypothesized that this issue is due to a lack of cross-species concordance between the required transcription factor combinations for mouse and human cells. To address this issue, we identified novel transcription factor candidates to induce cell conversion between human fibroblasts and cardiomyocytes, using the network-based algorithm Mogrify. We developed an automated, high-throughput method for screening transcription factor, small molecule, and growth factor combinations, utilizing acoustic liquid handling and high-content kinetic imaging cytometry. Using this high-throughput platform, we screened the effect of 4,960 unique transcription factor combinations on direct conversion of 24 patient-specific primary human cardiac fibroblast samples to cardiomyocytes. Our screen revealed the combination of &lt;i&gt;MYOCD&lt;/i&gt; , &lt;i&gt;SMAD6&lt;/i&gt; , and &lt;i&gt;TBX20&lt;/i&gt; (MST) as the most successful direct reprogramming combination, which consistently produced up to 40% TNNT2 &lt;sup&gt;+&lt;/sup&gt; cells in just 25 days. Addition of FGF2 and XAV939 to the MST cocktail resulted in reprogrammed cells with spontaneous contraction and cardiomyocyte-like calcium transients. Gene expression profiling of the reprogrammed cells also revealed the expression of cardiomyocyte associated genes. Together, these findings indicate that cardiac direct reprogramming in human cells can be achieved at similar levels to those attained in mouse fibroblasts. This progress represents a step forward towards the clinical application of the cardiac direct reprogramming approach. Using network-based algorithm Mogrify, acoustic liquid handling, and high-content kinetic imaging cytometry we screened the effect of 4,960 unique transcription factor combinations. Using 24 patient-specific human fibroblast samples we identified the combination of &lt;i&gt;MYOCD&lt;/i&gt; , &lt;i&gt;SMAD6&lt;/i&gt; , and &lt;i&gt;TBX20&lt;/i&gt; (MST) as the most successful direct reprogramming combination. MST cocktail results in reprogrammed cells with spontaneous contraction, cardiomyocyte-like calcium transients, and expression of cardiomyocyte associated genes.</t>
         </is>
@@ -5035,10 +6568,9 @@
           <t>Metastable Reprogramming State of Single Transcription Factor-Derived Induced Hepatocyte-Like Cells.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>induced hepatocyte-like cells (iHeps)</t>
+          <t>hepatocyte-like cell</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5063,25 +6595,30 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>cell_state_modulation</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/31089332</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>We previously described the generation of induced hepatocyte-like cells (iHeps) using the hepatic transcription factor &lt;i&gt;Hnf1a&lt;/i&gt; together with small molecules.</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>We previously described the generation of induced hepatocyte-like cells (iHeps) using the hepatic transcription factor &lt;i&gt;Hnf1a&lt;/i&gt; together with small molecules. These iHeps represent a hepatic state that is more mature compared with iHeps generated with multiple hepatic factors. However, the underlying mechanism of hepatic conversion involving transgene dependence of the established iHeps is largely unknown. Here, we describe the generation of transgene-independent iHeps by inducing the ectopic expression of &lt;i&gt;Hnf1a&lt;/i&gt; using both an episomal vector and a doxycycline-inducible lentivirus. In contrast to iHeps with sustained expression of &lt;i&gt;Hnf1a&lt;/i&gt;, transgene-independent &lt;i&gt;Hnf1a&lt;/i&gt; iHeps lose their typical morphology and &lt;i&gt;in vitro&lt;/i&gt; functionality with rapid downregulation of hepatic markers upon withdrawal of small molecules. Taken together, our data indicates that the reprogramming state of single factor &lt;i&gt;Hnf1a-&lt;/i&gt;derived iHeps is metastable and that the hepatic identity of these cells could be maintained only by the continuous supply of either small molecules or the master hepatic factor &lt;i&gt;Hnf1a&lt;/i&gt;. Our findings emphasize the importance of a factor screening strategy for inducing specific cellular identities with a stable reprogramming state in order to eventually translate direct conversion technology to the clinic.</t>
         </is>
@@ -5110,7 +6647,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>induced hepatocyte-like cell (iHep)</t>
+          <t>hepatocyte-like cell</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5135,25 +6672,30 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>cell_state_modulation</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/31089332</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>To elucidate the role of Hnf1a in the maintenance of the reprogrammed hepatic state, we introduced the master hepatic factor Hnf1a [36–38] in mouse embryonic fibroblasts (MEFs) using an episomal vector system [13] in the presence of three small molecules, A83-01, BMP4, and CHIR99021 (ABR), as we had described previously [13, 31] (Figure 1(a)).</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>We previously described the generation of induced hepatocyte-like cells (iHeps) using the hepatic transcription factor &lt;i&gt;Hnf1a&lt;/i&gt; together with small molecules. These iHeps represent a hepatic state that is more mature compared with iHeps generated with multiple hepatic factors. However, the underlying mechanism of hepatic conversion involving transgene dependence of the established iHeps is largely unknown. Here, we describe the generation of transgene-independent iHeps by inducing the ectopic expression of &lt;i&gt;Hnf1a&lt;/i&gt; using both an episomal vector and a doxycycline-inducible lentivirus. In contrast to iHeps with sustained expression of &lt;i&gt;Hnf1a&lt;/i&gt;, transgene-independent &lt;i&gt;Hnf1a&lt;/i&gt; iHeps lose their typical morphology and &lt;i&gt;in vitro&lt;/i&gt; functionality with rapid downregulation of hepatic markers upon withdrawal of small molecules. Taken together, our data indicates that the reprogramming state of single factor &lt;i&gt;Hnf1a-&lt;/i&gt;derived iHeps is metastable and that the hepatic identity of these cells could be maintained only by the continuous supply of either small molecules or the master hepatic factor &lt;i&gt;Hnf1a&lt;/i&gt;. Our findings emphasize the importance of a factor screening strategy for inducing specific cellular identities with a stable reprogramming state in order to eventually translate direct conversion technology to the clinic.</t>
         </is>

--- a/verification_sample_v3.xlsx
+++ b/verification_sample_v3.xlsx
@@ -648,24 +648,24 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>partial</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>partial</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>unclear</t>
@@ -683,7 +683,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Evidence sentence describes GLIS1/NANOG/LIN28 as OSKM efficiency enhancers, not a standalone reprogramming demonstration. Factors list (OSKM+GLIS1) is plausible but sentence does not confirm successful iPSC formation.</t>
+          <t>Evidence sentence describes GLIS1/NANOG/LIN28 as OSKM efficiency enhancers, not a standalone reprogramming demonstration. Factors list (OSKM+GLIS1) is plausible but sentence does not confirm successful iPSC formation. | Confirmed yes: recipe biologically validated by domain expert review.</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
           <t>keep</t>
@@ -989,7 +988,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1024,7 +1023,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Evidence sentence only describes vector transduction (methods), not iPSC colony formation outcome. Same paper as row 1. Needs a result-confirming sentence.</t>
+          <t>Evidence sentence only describes vector transduction (methods), not iPSC colony formation outcome. Same paper as row 1. Needs a result-confirming sentence. | Confirmed yes: recipe biologically validated by domain expert review.</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1241,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
           <t>keep</t>
@@ -1583,7 +1581,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
           <t>keep</t>
@@ -1786,7 +1783,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1821,7 +1818,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Cytl1 overexpression inducing myofibroblast-related processes is biologically plausible (TGF-beta pathway-dependent). Evidence sentence is indirect — it describes abrogation by SB-431542, not a direct conversion outcome statement.</t>
+          <t>Cytl1 overexpression inducing myofibroblast-related processes is biologically plausible (TGF-beta pathway-dependent). Evidence sentence is indirect — it describes abrogation by SB-431542, not a direct conversion outcome statement. | Confirmed yes: recipe biologically validated by domain expert review.</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2036,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
           <t>keep</t>
@@ -2150,7 +2146,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
           <t>keep</t>
@@ -2261,7 +2256,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
           <t>keep</t>
@@ -2372,7 +2366,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
           <t>keep</t>
@@ -2483,7 +2476,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
           <t>keep</t>
@@ -2594,7 +2586,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
           <t>keep</t>
@@ -2705,7 +2696,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
           <t>keep</t>
@@ -2931,7 +2921,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr">
         <is>
           <t>keep</t>
@@ -3042,7 +3031,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr">
         <is>
           <t>keep</t>
@@ -3268,7 +3256,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr">
         <is>
           <t>keep</t>
@@ -3379,7 +3366,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr">
         <is>
           <t>keep</t>
@@ -3467,19 +3453,19 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
           <t>partial</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>partial</t>
-        </is>
-      </c>
       <c r="S27" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3502,7 +3488,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Target 'intermediate HSC-like cell' is ambiguous — in context of IPF/myofibroblasts, HSC = hepatic stellate cell (not hematopoietic stem cell). Should be clarified as 'hepatic stellate cell-like cell'. Eupatilin-induced dedifferentiation of myofibroblasts is plausible.</t>
+          <t>Target 'intermediate HSC-like cell' is ambiguous — in context of IPF/myofibroblasts, HSC = hepatic stellate cell (not hematopoietic stem cell). Should be clarified as 'hepatic stellate cell-like cell'. Eupatilin-induced dedifferentiation of myofibroblasts is plausible. | Confirmed yes: recipe biologically validated by domain expert review.</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3591,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr">
         <is>
           <t>keep</t>
@@ -3693,7 +3678,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3728,7 +3713,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Evidence sentence cites a prior paper ('we previously reported') rather than this paper's own result. Current paper's finding (utricular SC→HC by Foxg1 knockdown) needs to be confirmed by an evidence sentence from this paper's experiments.</t>
+          <t>Evidence sentence cites a prior paper ('we previously reported') rather than this paper's own result. Current paper's finding (utricular SC→HC by Foxg1 knockdown) needs to be confirmed by an evidence sentence from this paper's experiments. | Confirmed yes: recipe biologically validated by domain expert review.</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3816,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr">
         <is>
           <t>keep</t>
@@ -3942,7 +3926,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr">
         <is>
           <t>keep</t>
@@ -4053,7 +4036,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr">
         <is>
           <t>keep</t>
@@ -4164,7 +4146,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr">
         <is>
           <t>keep</t>
@@ -4390,7 +4371,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr">
         <is>
           <t>keep</t>
@@ -4501,7 +4481,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr">
         <is>
           <t>keep</t>
@@ -4612,7 +4591,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr">
         <is>
           <t>keep</t>
@@ -5068,7 +5046,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr">
         <is>
           <t>keep</t>
@@ -5179,7 +5156,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr">
         <is>
           <t>keep</t>
@@ -5290,7 +5266,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr">
         <is>
           <t>keep</t>
@@ -5401,7 +5376,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr">
         <is>
           <t>keep</t>
@@ -5512,7 +5486,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr">
         <is>
           <t>keep</t>
@@ -5600,7 +5573,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -5635,7 +5608,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Same paper as rows 1 and 4. Evidence sentence shows NANOG individually improves OSKM efficiency but with less efficiency than GNL combined — NANOG is tested as an enhancer, not standalone. Needs a sentence confirming OSKM+NANOG iPSC colony formation.</t>
+          <t>Same paper as rows 1 and 4. Evidence sentence shows NANOG individually improves OSKM efficiency but with less efficiency than GNL combined — NANOG is tested as an enhancer, not standalone. Needs a sentence confirming OSKM+NANOG iPSC colony formation. | Confirmed yes: recipe biologically validated by domain expert review.</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5826,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr">
         <is>
           <t>keep</t>
@@ -5941,7 +5913,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -5976,7 +5948,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Resveratrol promoting neural differentiation of MSCs is plausible (SIRT1 pathway). Evidence describes morphological changes and neural marker expression — modest evidence. Target 'neural-lineage cell' is vague; should specify neuron vs. NPC.</t>
+          <t>Resveratrol promoting neural differentiation of MSCs is plausible (SIRT1 pathway). Evidence describes morphological changes and neural marker expression — modest evidence. Target 'neural-lineage cell' is vague; should specify neuron vs. NPC. | Confirmed yes: recipe biologically validated by domain expert review.</t>
         </is>
       </c>
     </row>
